--- a/outputs/validation_frame_moment_release.xlsx
+++ b/outputs/validation_frame_moment_release.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>3.757925951552276</v>
+        <v>3.757925951556457</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1624422723417782</v>
+        <v>0.1624422723423497</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.03630395006709138</v>
+        <v>-0.03630395006721086</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6098064904006163</v>
+        <v>0.609806490401359</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.005111413036164057</v>
+        <v>-0.005111413036285996</v>
       </c>
       <c r="K6" t="n">
-        <v>3.761445368295371</v>
+        <v>3.761445368299572</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3.723395957223965</v>
+        <v>3.723395957228697</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1623366982634615</v>
+        <v>0.162336698264033</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.03628902410958178</v>
+        <v>-0.03628902410970122</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6753566419530859</v>
+        <v>0.6753566419540323</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.03509421220928596</v>
+        <v>-0.03509421220940796</v>
       </c>
       <c r="K7" t="n">
-        <v>3.726938275138332</v>
+        <v>3.726938275143084</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>3.723221883765729</v>
+        <v>3.723221883770459</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1923970678416461</v>
+        <v>-0.1923970678424733</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04214837918573356</v>
+        <v>0.04214837918590374</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5925544959336078</v>
+        <v>0.5925544959344536</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0251422011951866</v>
+        <v>0.0251422011950651</v>
       </c>
       <c r="K8" t="n">
-        <v>3.728194767154632</v>
+        <v>3.728194767159398</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>3.758983147792192</v>
+        <v>3.758983147796373</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1926264440283471</v>
+        <v>-0.1926264440291746</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05052610874595759</v>
+        <v>0.05052610874615139</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6101246851582274</v>
+        <v>0.6101246851589696</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.06503362791338377</v>
+        <v>-0.06503362791350591</v>
       </c>
       <c r="K9" t="n">
-        <v>3.763925524839729</v>
+        <v>3.763925524843947</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>8.658378534736178</v>
+        <v>8.658378534746893</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5437220967391151</v>
+        <v>0.5437220967409437</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01407909170153279</v>
+        <v>0.01407909170155771</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.04556477868176344</v>
+        <v>-0.04556477868193153</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5226650286341942</v>
+        <v>0.522665028634919</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1550967117141002</v>
+        <v>-0.1550967117146793</v>
       </c>
       <c r="K10" t="n">
-        <v>8.67544527906699</v>
+        <v>8.675445279077797</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03693211708712</v>
+        <v>10.03693211710211</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5436509443436122</v>
+        <v>0.5436509443454407</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009226541546886466</v>
+        <v>0.009226541546905213</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.04561220557379464</v>
+        <v>-0.04561220557396294</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8629762354412365</v>
+        <v>0.8629762354429026</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1753504665291883</v>
+        <v>-0.1753504665297493</v>
       </c>
       <c r="K11" t="n">
-        <v>10.05164900906162</v>
+        <v>10.0516490090767</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>10.03855675062735</v>
+        <v>10.03855675064235</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7997579802013167</v>
+        <v>-0.7997579802044718</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.009302974818938313</v>
+        <v>-0.00930297481895709</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>10.07036846435135</v>
+        <v>10.07036846436655</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>8.659455021339078</v>
+        <v>8.659455021349791</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7997730185668483</v>
+        <v>-0.7997730185700033</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.01400265842948097</v>
+        <v>-0.01400265842950587</v>
       </c>
       <c r="H13" t="n">
-        <v>0.09096723747714046</v>
+        <v>0.0909672374775249</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5215719617301026</v>
+        <v>0.5215719617308274</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2249576665793398</v>
+        <v>-0.2249576665799374</v>
       </c>
       <c r="K13" t="n">
-        <v>8.696320729036229</v>
+        <v>8.696320729047185</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>12.10067564645607</v>
+        <v>12.10067564647184</v>
       </c>
       <c r="F14" t="n">
-        <v>0.855601378201386</v>
+        <v>0.8556013782045796</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01645310419378794</v>
+        <v>0.0164531041938184</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.02662802448650984</v>
+        <v>-0.02662802448665153</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3041205539613382</v>
+        <v>0.3041205539618769</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2765021643922128</v>
+        <v>-0.2765021643933779</v>
       </c>
       <c r="K14" t="n">
-        <v>12.1308975563951</v>
+        <v>12.13089755641106</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>14.61043109294954</v>
+        <v>14.61043109297521</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8554961959361138</v>
+        <v>0.8554961959393073</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01137182782094663</v>
+        <v>0.01137182782097141</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02661478979054551</v>
+        <v>-0.02661478979068704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3475225990409564</v>
+        <v>0.3475225990419422</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3064720755180301</v>
+        <v>-0.306472075519195</v>
       </c>
       <c r="K15" t="n">
-        <v>14.63546035427502</v>
+        <v>14.63546035430084</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>14.61196774737462</v>
+        <v>14.61196774740029</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.299417015686306</v>
+        <v>-1.29941701569186</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.01139498107312069</v>
+        <v>-0.01139498107314529</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03319060518208777</v>
+        <v>0.03319060518225687</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3182393817608644</v>
+        <v>0.31823938176172</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.246574457134591</v>
+        <v>-0.2465744571357565</v>
       </c>
       <c r="K16" t="n">
-        <v>14.66963584676064</v>
+        <v>14.6696358467867</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>12.10178926074621</v>
+        <v>12.10178926076199</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.299472671285667</v>
+        <v>-1.29947267129122</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.01642995094161392</v>
+        <v>-0.01642995094164457</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03715388464293796</v>
+        <v>0.03715388464313682</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3085318025519207</v>
+        <v>0.3085318025524598</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3365693165703608</v>
+        <v>-0.3365693165715262</v>
       </c>
       <c r="K17" t="n">
-        <v>12.17136814323758</v>
+        <v>12.17136814325386</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>13.74971682084649</v>
+        <v>13.74971682086599</v>
       </c>
       <c r="F18" t="n">
-        <v>0.983163243548322</v>
+        <v>0.9831632435523956</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01709782427089189</v>
+        <v>0.01709782427092434</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.009077683545820888</v>
+        <v>-0.009077683545891</v>
       </c>
       <c r="I18" t="n">
-        <v>0.128253174079973</v>
+        <v>0.1282531740802902</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2961131962401839</v>
+        <v>-0.29611319624158</v>
       </c>
       <c r="K18" t="n">
-        <v>13.78483278652767</v>
+        <v>13.78483278654741</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>16.28729671562621</v>
+        <v>16.28729671565749</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9830577539201565</v>
+        <v>0.9830577539242298</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01191508433337423</v>
+        <v>0.01191508433340097</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.00908168820024597</v>
+        <v>-0.009081688200316467</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1184927986803802</v>
+        <v>0.1184927986808056</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3261226386362977</v>
+        <v>-0.3261226386376945</v>
       </c>
       <c r="K19" t="n">
-        <v>16.31694146645215</v>
+        <v>16.31694146648362</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>16.28791981014785</v>
+        <v>16.28791981017913</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.457257327504276</v>
+        <v>-1.457257327510761</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.01193004232021133</v>
+        <v>-0.01193004232023791</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01134630288189326</v>
+        <v>0.0113463028819652</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1105412483358429</v>
+        <v>0.1105412483363123</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2660564792319032</v>
+        <v>-0.2660564792332996</v>
       </c>
       <c r="K20" t="n">
-        <v>16.35298361114208</v>
+        <v>16.35298361117381</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>13.75040665788783</v>
+        <v>13.75040665790733</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.45737063857569</v>
+        <v>-1.457370638582175</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.01708286628405483</v>
+        <v>-0.01708286628408745</v>
       </c>
       <c r="H21" t="n">
-        <v>0.009916345241901936</v>
+        <v>0.009916345241963179</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1081508876107066</v>
+        <v>0.1081508876110224</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3561669580448221</v>
+        <v>-0.3561669580462182</v>
       </c>
       <c r="K21" t="n">
-        <v>13.82743303219325</v>
+        <v>13.82743303221332</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>16.35298361114208</v>
+        <v>16.35298361117381</v>
       </c>
       <c r="D2" t="n">
-        <v>16.28791981014785</v>
+        <v>16.28791981017913</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.457257327504276</v>
+        <v>-1.457257327510761</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01193004232021133</v>
+        <v>-0.01193004232023791</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>16.28791981014785</v>
+        <v>16.28791981017913</v>
       </c>
       <c r="D3" t="n">
-        <v>16.28791981014785</v>
+        <v>16.28791981017913</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.457257327504276</v>
+        <v>-1.457257327510761</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01193004232021133</v>
+        <v>-0.01193004232023791</v>
       </c>
     </row>
     <row r="4">
@@ -1289,16 +1289,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.45737063857569</v>
+        <v>-1.457370638582175</v>
       </c>
       <c r="D4" t="n">
-        <v>13.75040665788783</v>
+        <v>13.75040665790733</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.45737063857569</v>
+        <v>-1.457370638582175</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01708286628405483</v>
+        <v>-0.01708286628408745</v>
       </c>
     </row>
     <row r="5">
@@ -1311,16 +1311,16 @@
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01709782427089189</v>
+        <v>0.01709782427092434</v>
       </c>
       <c r="D5" t="n">
-        <v>13.74971682084649</v>
+        <v>13.74971682086599</v>
       </c>
       <c r="E5" t="n">
-        <v>0.983163243548322</v>
+        <v>0.9831632435523956</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01709782427089189</v>
+        <v>0.01709782427092434</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-475.6982651531055</v>
+        <v>-475.6982651535872</v>
       </c>
       <c r="C2" t="n">
-        <v>-13.20417079465767</v>
+        <v>-13.20417079471022</v>
       </c>
       <c r="D2" t="n">
-        <v>-1380.213673753829</v>
+        <v>-1380.213673756154</v>
       </c>
       <c r="E2" t="n">
-        <v>66.4774354336206</v>
+        <v>66.47743543386669</v>
       </c>
       <c r="F2" t="n">
-        <v>-1878.351598355772</v>
+        <v>-1878.351598357767</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01454786787215924</v>
+        <v>0.0145478678725063</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-418.6737544032946</v>
+        <v>-418.6737544037614</v>
       </c>
       <c r="C3" t="n">
-        <v>-13.18917439722999</v>
+        <v>-13.18917439728258</v>
       </c>
       <c r="D3" t="n">
-        <v>-977.1609122504613</v>
+        <v>-977.1609122522647</v>
       </c>
       <c r="E3" t="n">
-        <v>66.42140103278049</v>
+        <v>66.42140103302664</v>
       </c>
       <c r="F3" t="n">
-        <v>-1755.785178255167</v>
+        <v>-1755.785178257268</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0998835270571985</v>
+        <v>0.0998835270575457</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-554.9044043380102</v>
+        <v>-554.9044043385509</v>
       </c>
       <c r="C4" t="n">
-        <v>16.26814280349655</v>
+        <v>16.26814280357464</v>
       </c>
       <c r="D4" t="n">
-        <v>979.0184522729362</v>
+        <v>979.0184522747155</v>
       </c>
       <c r="E4" t="n">
-        <v>-79.99422900793247</v>
+        <v>-79.99422900829268</v>
       </c>
       <c r="F4" t="n">
-        <v>-1953.2035400049</v>
+        <v>-1953.203540007148</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.07155857263245415</v>
+        <v>-0.07155857263210837</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-550.7235761049859</v>
+        <v>-550.7235761054679</v>
       </c>
       <c r="C5" t="n">
-        <v>10.12520238831702</v>
+        <v>10.12520238837771</v>
       </c>
       <c r="D5" t="n">
-        <v>1378.356133731357</v>
+        <v>1378.356133733707</v>
       </c>
       <c r="E5" t="n">
-        <v>-67.76492763695965</v>
+        <v>-67.76492763728514</v>
       </c>
       <c r="F5" t="n">
-        <v>-1953.662995332046</v>
+        <v>-1953.662995334041</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1850957102150153</v>
+        <v>0.1850957102153629</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001455921596786739</v>
+        <v>0.001455921596789192</v>
       </c>
       <c r="H2" t="n">
-        <v>1380.213673753829</v>
+        <v>1380.213673756154</v>
       </c>
       <c r="I2" t="n">
-        <v>291184.3193573478</v>
+        <v>291184.3193578384</v>
       </c>
       <c r="J2" t="n">
-        <v>-1380.213673753829</v>
+        <v>-1380.213673756154</v>
       </c>
       <c r="K2" t="n">
-        <v>-13.20417079465767</v>
+        <v>-13.20417079471022</v>
       </c>
       <c r="L2" t="n">
-        <v>475.6982651531055</v>
+        <v>475.6982651535872</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01454786787215924</v>
+        <v>0.0145478678725063</v>
       </c>
       <c r="N2" t="n">
-        <v>-1878.351598355772</v>
+        <v>-1878.351598357767</v>
       </c>
       <c r="O2" t="n">
-        <v>-66.4774354336206</v>
+        <v>-66.47743543386669</v>
       </c>
       <c r="P2" t="n">
-        <v>1380.213673753829</v>
+        <v>1380.213673756154</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.20417079465767</v>
+        <v>13.20417079471022</v>
       </c>
       <c r="R2" t="n">
-        <v>-475.6982651531055</v>
+        <v>-475.6982651535872</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01454786787215924</v>
+        <v>-0.0145478678725063</v>
       </c>
       <c r="T2" t="n">
-        <v>-975.8379925628601</v>
+        <v>-975.8379925637557</v>
       </c>
       <c r="U2" t="n">
-        <v>-12.74758933432537</v>
+        <v>-12.74758933439462</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001030760455960402</v>
+        <v>0.001030760455962304</v>
       </c>
       <c r="H3" t="n">
-        <v>977.1609122504611</v>
+        <v>977.1609122522644</v>
       </c>
       <c r="I3" t="n">
-        <v>206152.0911920804</v>
+        <v>206152.0911924609</v>
       </c>
       <c r="J3" t="n">
-        <v>-977.1609122504613</v>
+        <v>-977.1609122522647</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.18917439722999</v>
+        <v>-13.18917439728258</v>
       </c>
       <c r="L3" t="n">
-        <v>418.6737544032946</v>
+        <v>418.6737544037614</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0998835270571985</v>
+        <v>0.0998835270575457</v>
       </c>
       <c r="N3" t="n">
-        <v>-1755.785178255167</v>
+        <v>-1755.785178257268</v>
       </c>
       <c r="O3" t="n">
-        <v>-66.42140103278049</v>
+        <v>-66.42140103302664</v>
       </c>
       <c r="P3" t="n">
-        <v>977.1609122504613</v>
+        <v>977.1609122522647</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.18917439722999</v>
+        <v>13.18917439728258</v>
       </c>
       <c r="R3" t="n">
-        <v>-418.6737544032946</v>
+        <v>-418.6737544037614</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0998835270571985</v>
+        <v>-0.0998835270575457</v>
       </c>
       <c r="T3" t="n">
-        <v>-756.2573481646002</v>
+        <v>-756.2573481653003</v>
       </c>
       <c r="U3" t="n">
-        <v>-12.71364535059946</v>
+        <v>-12.71364535066883</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001032719886363857</v>
+        <v>-0.001032719886365733</v>
       </c>
       <c r="H4" t="n">
-        <v>-979.018452272936</v>
+        <v>-979.0184522747154</v>
       </c>
       <c r="I4" t="n">
-        <v>-206543.9772727713</v>
+        <v>-206543.9772731467</v>
       </c>
       <c r="J4" t="n">
-        <v>979.0184522729362</v>
+        <v>979.0184522747155</v>
       </c>
       <c r="K4" t="n">
-        <v>16.26814280349655</v>
+        <v>16.26814280357464</v>
       </c>
       <c r="L4" t="n">
-        <v>554.9044043380102</v>
+        <v>554.9044043385509</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07155857263245415</v>
+        <v>-0.07155857263210837</v>
       </c>
       <c r="N4" t="n">
-        <v>-1953.2035400049</v>
+        <v>-1953.203540007148</v>
       </c>
       <c r="O4" t="n">
-        <v>79.99422900793247</v>
+        <v>79.99422900829268</v>
       </c>
       <c r="P4" t="n">
-        <v>-979.0184522729362</v>
+        <v>-979.0184522747155</v>
       </c>
       <c r="Q4" t="n">
-        <v>-16.26814280349655</v>
+        <v>-16.26814280357464</v>
       </c>
       <c r="R4" t="n">
-        <v>-404.9044043380101</v>
+        <v>-404.9044043385508</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07155857263245415</v>
+        <v>0.07155857263210837</v>
       </c>
       <c r="T4" t="n">
-        <v>-926.2228860231605</v>
+        <v>-926.2228860241569</v>
       </c>
       <c r="U4" t="n">
-        <v>17.61462781304681</v>
+        <v>17.61462781315514</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001453962166383287</v>
+        <v>-0.001453962166385767</v>
       </c>
       <c r="H5" t="n">
-        <v>-1378.356133731356</v>
+        <v>-1378.356133733707</v>
       </c>
       <c r="I5" t="n">
-        <v>-290792.4332766574</v>
+        <v>-290792.4332771534</v>
       </c>
       <c r="J5" t="n">
-        <v>1378.356133731357</v>
+        <v>1378.356133733707</v>
       </c>
       <c r="K5" t="n">
-        <v>10.12520238831702</v>
+        <v>10.12520238837771</v>
       </c>
       <c r="L5" t="n">
-        <v>550.7235761049859</v>
+        <v>550.7235761054679</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1850957102150153</v>
+        <v>0.1850957102153629</v>
       </c>
       <c r="N5" t="n">
-        <v>-1953.662995332046</v>
+        <v>-1953.662995334041</v>
       </c>
       <c r="O5" t="n">
-        <v>67.76492763695965</v>
+        <v>67.76492763728514</v>
       </c>
       <c r="P5" t="n">
-        <v>-1378.356133731357</v>
+        <v>-1378.356133733707</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.12520238831702</v>
+        <v>-10.12520238837771</v>
       </c>
       <c r="R5" t="n">
-        <v>-400.7235761049859</v>
+        <v>-400.7235761054679</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1850957102150153</v>
+        <v>-0.1850957102153629</v>
       </c>
       <c r="T5" t="n">
-        <v>-900.678461297869</v>
+        <v>-900.6784612987663</v>
       </c>
       <c r="U5" t="n">
-        <v>-7.013713307057571</v>
+        <v>-7.013713307018918</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005343562120812355</v>
+        <v>0.005343562120822556</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008905936868020591</v>
+        <v>0.0008905936868037594</v>
       </c>
       <c r="H6" t="n">
-        <v>844.282815088352</v>
+        <v>844.2828150899639</v>
       </c>
       <c r="I6" t="n">
-        <v>178118.7373604118</v>
+        <v>178118.7373607519</v>
       </c>
       <c r="J6" t="n">
-        <v>-844.2828150883522</v>
+        <v>-844.2828150899641</v>
       </c>
       <c r="K6" t="n">
-        <v>-33.46616407719057</v>
+        <v>-33.46616407728784</v>
       </c>
       <c r="L6" t="n">
-        <v>370.7493797662693</v>
+        <v>370.7493797667951</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4268812346987415</v>
+        <v>0.4268812347000424</v>
       </c>
       <c r="N6" t="n">
-        <v>-1047.763457591656</v>
+        <v>-1047.763457593219</v>
       </c>
       <c r="O6" t="n">
-        <v>-107.251505406429</v>
+        <v>-107.2515054067568</v>
       </c>
       <c r="P6" t="n">
-        <v>844.2828150883522</v>
+        <v>844.2828150899641</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.46616407719057</v>
+        <v>33.46616407728784</v>
       </c>
       <c r="R6" t="n">
-        <v>-370.7493797662693</v>
+        <v>-370.7493797667951</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4268812346987415</v>
+        <v>-0.4268812347000424</v>
       </c>
       <c r="T6" t="n">
-        <v>-1176.73282100596</v>
+        <v>-1176.732821007551</v>
       </c>
       <c r="U6" t="n">
-        <v>-93.54547905671429</v>
+        <v>-93.54547905697024</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003041978811124054</v>
+        <v>0.003041978811131388</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005069964685206757</v>
+        <v>0.0005069964685218979</v>
       </c>
       <c r="H7" t="n">
-        <v>480.6326521576005</v>
+        <v>480.6326521587592</v>
       </c>
       <c r="I7" t="n">
-        <v>101399.2937041351</v>
+        <v>101399.2937043796</v>
       </c>
       <c r="J7" t="n">
-        <v>-480.6326521576007</v>
+        <v>-480.6326521587592</v>
       </c>
       <c r="K7" t="n">
-        <v>-33.45060406740529</v>
+        <v>-33.45060406750243</v>
       </c>
       <c r="L7" t="n">
-        <v>418.9725901611122</v>
+        <v>418.9725901617112</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3991908776797221</v>
+        <v>0.3991908776809715</v>
       </c>
       <c r="N7" t="n">
-        <v>-1395.756269664567</v>
+        <v>-1395.756269666897</v>
       </c>
       <c r="O7" t="n">
-        <v>-107.2509664857333</v>
+        <v>-107.2509664860609</v>
       </c>
       <c r="P7" t="n">
-        <v>480.6326521576007</v>
+        <v>480.6326521587592</v>
       </c>
       <c r="Q7" t="n">
-        <v>33.45060406740529</v>
+        <v>33.45060406750243</v>
       </c>
       <c r="R7" t="n">
-        <v>-418.9725901611122</v>
+        <v>-418.9725901617112</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3991908776797221</v>
+        <v>-0.3991908776809715</v>
       </c>
       <c r="T7" t="n">
-        <v>-1118.079271302104</v>
+        <v>-1118.07927130337</v>
       </c>
       <c r="U7" t="n">
-        <v>-93.45265791869829</v>
+        <v>-93.45265791895361</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.003106655500755174</v>
+        <v>-0.003106655500762689</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.000517775916792529</v>
+        <v>-0.0005177759167937815</v>
       </c>
       <c r="H8" t="n">
-        <v>-490.8515691193175</v>
+        <v>-490.8515691205048</v>
       </c>
       <c r="I8" t="n">
-        <v>-103555.1833585058</v>
+        <v>-103555.1833587563</v>
       </c>
       <c r="J8" t="n">
-        <v>490.8515691193177</v>
+        <v>490.8515691205049</v>
       </c>
       <c r="K8" t="n">
-        <v>118.6258911179426</v>
+        <v>118.6258911183909</v>
       </c>
       <c r="L8" t="n">
-        <v>1194.292273501664</v>
+        <v>1194.29227350357</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07155857263245415</v>
+        <v>0.07155857263210837</v>
       </c>
       <c r="N8" t="n">
-        <v>-2994.386493514121</v>
+        <v>-2994.386493519215</v>
       </c>
       <c r="O8" t="n">
-        <v>324.687872756385</v>
+        <v>324.6878727576038</v>
       </c>
       <c r="P8" t="n">
-        <v>-490.8515691193177</v>
+        <v>-490.8515691205049</v>
       </c>
       <c r="Q8" t="n">
-        <v>-118.6258911179426</v>
+        <v>-118.6258911183909</v>
       </c>
       <c r="R8" t="n">
-        <v>-1044.292273501664</v>
+        <v>-1044.29227350357</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07155857263245415</v>
+        <v>-0.07155857263210837</v>
       </c>
       <c r="T8" t="n">
-        <v>-3721.36714749586</v>
+        <v>-3721.367147502207</v>
       </c>
       <c r="U8" t="n">
-        <v>387.0674739512706</v>
+        <v>387.0674739527414</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.005278885431181244</v>
+        <v>-0.005278885431191272</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0008798142385302073</v>
+        <v>-0.0008798142385318787</v>
       </c>
       <c r="H9" t="n">
-        <v>-834.0638981266366</v>
+        <v>-834.063898128221</v>
       </c>
       <c r="I9" t="n">
-        <v>-175962.8477060414</v>
+        <v>-175962.8477063757</v>
       </c>
       <c r="J9" t="n">
-        <v>834.0638981266368</v>
+        <v>834.0638981282214</v>
       </c>
       <c r="K9" t="n">
-        <v>45.05774551440441</v>
+        <v>45.0577455145506</v>
       </c>
       <c r="L9" t="n">
-        <v>446.3275434442011</v>
+        <v>446.3275434447266</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4551684177415671</v>
+        <v>0.4551684177429204</v>
       </c>
       <c r="N9" t="n">
-        <v>-1123.453614995791</v>
+        <v>-1123.453614997354</v>
       </c>
       <c r="O9" t="n">
-        <v>165.0996718042885</v>
+        <v>165.0996718048683</v>
       </c>
       <c r="P9" t="n">
-        <v>-834.0638981266368</v>
+        <v>-834.0638981282214</v>
       </c>
       <c r="Q9" t="n">
-        <v>-45.05774551440441</v>
+        <v>-45.0577455145506</v>
       </c>
       <c r="R9" t="n">
-        <v>-296.3275434442011</v>
+        <v>-296.3275434447266</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4551684177415671</v>
+        <v>-0.4551684177429204</v>
       </c>
       <c r="T9" t="n">
-        <v>-1104.511645669415</v>
+        <v>-1104.511645671005</v>
       </c>
       <c r="U9" t="n">
-        <v>105.246801282138</v>
+        <v>105.2468012824354</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002374012492255152</v>
+        <v>0.002374012492260691</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003956687487091919</v>
+        <v>0.0003956687487101151</v>
       </c>
       <c r="H10" t="n">
-        <v>375.0939737763139</v>
+        <v>375.0939737771891</v>
       </c>
       <c r="I10" t="n">
-        <v>79133.74974183837</v>
+        <v>79133.74974202301</v>
       </c>
       <c r="J10" t="n">
-        <v>-375.0939737763142</v>
+        <v>-375.0939737771891</v>
       </c>
       <c r="K10" t="n">
-        <v>-23.50754841617129</v>
+        <v>-23.50754841627872</v>
       </c>
       <c r="L10" t="n">
-        <v>237.2786231035455</v>
+        <v>237.2786231038581</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3455385960838586</v>
+        <v>0.3455385960855267</v>
       </c>
       <c r="N10" t="n">
-        <v>-550.1129580527219</v>
+        <v>-550.1129580535226</v>
       </c>
       <c r="O10" t="n">
-        <v>-56.50944714402618</v>
+        <v>-56.50944714432887</v>
       </c>
       <c r="P10" t="n">
-        <v>375.0939737763142</v>
+        <v>375.0939737771891</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.50754841617129</v>
+        <v>23.50754841627872</v>
       </c>
       <c r="R10" t="n">
-        <v>-237.2786231035455</v>
+        <v>-237.2786231038581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3455385960838586</v>
+        <v>-0.3455385960855267</v>
       </c>
       <c r="T10" t="n">
-        <v>-873.5587805685493</v>
+        <v>-873.558780569625</v>
       </c>
       <c r="U10" t="n">
-        <v>-84.53584335300144</v>
+        <v>-84.5358433533433</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002145286274060163</v>
+        <v>0.002145286274066197</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003575477123433605</v>
+        <v>0.0003575477123443661</v>
       </c>
       <c r="H11" t="n">
-        <v>338.9552313015058</v>
+        <v>338.955231302459</v>
       </c>
       <c r="I11" t="n">
-        <v>71509.54246867209</v>
+        <v>71509.5424688732</v>
       </c>
       <c r="J11" t="n">
-        <v>-338.9552313015058</v>
+        <v>-338.9552313024592</v>
       </c>
       <c r="K11" t="n">
-        <v>-23.4738521565387</v>
+        <v>-23.4738521566461</v>
       </c>
       <c r="L11" t="n">
-        <v>232.360609862576</v>
+        <v>232.3606098632458</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3731922717374728</v>
+        <v>0.3731922717391915</v>
       </c>
       <c r="N11" t="n">
-        <v>-315.6461386515213</v>
+        <v>-315.6461386530264</v>
       </c>
       <c r="O11" t="n">
-        <v>-56.36346879001178</v>
+        <v>-56.36346879031407</v>
       </c>
       <c r="P11" t="n">
-        <v>338.9552313015058</v>
+        <v>338.9552313024592</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.4738521565387</v>
+        <v>23.4738521566461</v>
       </c>
       <c r="R11" t="n">
-        <v>-232.360609862576</v>
+        <v>-232.3606098632458</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3731922717374728</v>
+        <v>-0.3731922717391915</v>
       </c>
       <c r="T11" t="n">
-        <v>-1078.517520523936</v>
+        <v>-1078.51752052645</v>
       </c>
       <c r="U11" t="n">
-        <v>-84.47964414922058</v>
+        <v>-84.47964414956243</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.002092006254182372</v>
+        <v>-0.002092006254188197</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0003486677090303953</v>
+        <v>-0.0003486677090313662</v>
       </c>
       <c r="H12" t="n">
-        <v>-330.5369881608148</v>
+        <v>-330.5369881617351</v>
       </c>
       <c r="I12" t="n">
-        <v>-69733.54180607905</v>
+        <v>-69733.54180627322</v>
       </c>
       <c r="J12" t="n">
-        <v>330.5369881608146</v>
+        <v>330.5369881617353</v>
       </c>
       <c r="K12" t="n">
-        <v>98.68818091821899</v>
+        <v>98.68818091868567</v>
       </c>
       <c r="L12" t="n">
-        <v>967.6109033612859</v>
+        <v>967.6109033632856</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7017888395369127</v>
+        <v>0.7017888395402301</v>
       </c>
       <c r="N12" t="n">
-        <v>-2988.329852586897</v>
+        <v>-2988.32985259353</v>
       </c>
       <c r="O12" t="n">
-        <v>320.6255905894019</v>
+        <v>320.6255905909271</v>
       </c>
       <c r="P12" t="n">
-        <v>-330.5369881608146</v>
+        <v>-330.5369881617353</v>
       </c>
       <c r="Q12" t="n">
-        <v>-98.68818091821899</v>
+        <v>-98.68818091868567</v>
       </c>
       <c r="R12" t="n">
-        <v>-817.6109033612859</v>
+        <v>-817.6109033632856</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7017888395369127</v>
+        <v>-0.7017888395402301</v>
       </c>
       <c r="T12" t="n">
-        <v>-2367.335567580818</v>
+        <v>-2367.335567586184</v>
       </c>
       <c r="U12" t="n">
-        <v>271.503494919912</v>
+        <v>271.5034949211869</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002427292512132957</v>
+        <v>-0.002427292512138695</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0004045487520221595</v>
+        <v>-0.0004045487520231159</v>
       </c>
       <c r="H13" t="n">
-        <v>-383.5122169170072</v>
+        <v>-383.5122169179139</v>
       </c>
       <c r="I13" t="n">
-        <v>-80909.75040443189</v>
+        <v>-80909.75040462318</v>
       </c>
       <c r="J13" t="n">
-        <v>383.5122169170072</v>
+        <v>383.512216917914</v>
       </c>
       <c r="K13" t="n">
-        <v>28.44961730178392</v>
+        <v>28.44961730194387</v>
       </c>
       <c r="L13" t="n">
-        <v>309.8323268183962</v>
+        <v>309.8323268187096</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3176639268975212</v>
+        <v>0.3176639268991371</v>
       </c>
       <c r="N13" t="n">
-        <v>-621.8472626633337</v>
+        <v>-621.847262664136</v>
       </c>
       <c r="O13" t="n">
-        <v>45.52697080804194</v>
+        <v>45.52697080838436</v>
       </c>
       <c r="P13" t="n">
-        <v>-383.5122169170072</v>
+        <v>-383.512216917914</v>
       </c>
       <c r="Q13" t="n">
-        <v>-28.44961730178392</v>
+        <v>-28.44961730194387</v>
       </c>
       <c r="R13" t="n">
-        <v>-159.8323268183962</v>
+        <v>-159.8323268187096</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3176639268975212</v>
+        <v>-0.3176639268991371</v>
       </c>
       <c r="T13" t="n">
-        <v>-787.1466982470427</v>
+        <v>-787.1466982481188</v>
       </c>
       <c r="U13" t="n">
-        <v>125.1707330026616</v>
+        <v>125.1707330032788</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0006447200771039496</v>
+        <v>0.0006447200771059376</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001074533461839916</v>
+        <v>0.0001074533461843229</v>
       </c>
       <c r="H14" t="n">
-        <v>101.865772182424</v>
+        <v>101.8657721827381</v>
       </c>
       <c r="I14" t="n">
-        <v>21490.66923679832</v>
+        <v>21490.66923686459</v>
       </c>
       <c r="J14" t="n">
-        <v>-101.8657721824238</v>
+        <v>-101.8657721827385</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.043036174986128</v>
+        <v>-5.043036175046467</v>
       </c>
       <c r="L14" t="n">
-        <v>86.80693093240026</v>
+        <v>86.80693093268656</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05581601372114864</v>
+        <v>0.05581601372180611</v>
       </c>
       <c r="N14" t="n">
-        <v>-130.2789316849898</v>
+        <v>-130.2789316856852</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.14185622884861</v>
+        <v>-2.141856228976621</v>
       </c>
       <c r="P14" t="n">
-        <v>101.8657721824238</v>
+        <v>101.8657721827385</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.043036174986128</v>
+        <v>5.043036175046467</v>
       </c>
       <c r="R14" t="n">
-        <v>-86.80693093240026</v>
+        <v>-86.80693093268656</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.05581601372114864</v>
+        <v>-0.05581601372180611</v>
       </c>
       <c r="T14" t="n">
-        <v>-390.5626539094091</v>
+        <v>-390.5626539104323</v>
       </c>
       <c r="U14" t="n">
-        <v>-28.11636082106827</v>
+        <v>-28.11636082130212</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0005432565124276027</v>
+        <v>0.0005432565124295595</v>
       </c>
       <c r="G15" t="n">
-        <v>9.054275207126712e-05</v>
+        <v>9.054275207159325e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>85.83452896356123</v>
+        <v>85.8345289638704</v>
       </c>
       <c r="I15" t="n">
-        <v>18108.55041425342</v>
+        <v>18108.55041431865</v>
       </c>
       <c r="J15" t="n">
-        <v>-85.8345289635613</v>
+        <v>-85.8345289638703</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.049790589544841</v>
+        <v>-5.049790589604982</v>
       </c>
       <c r="L15" t="n">
-        <v>68.77545927978912</v>
+        <v>68.77545928012933</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05592852579814611</v>
+        <v>0.05592852579880625</v>
       </c>
       <c r="N15" t="n">
-        <v>-36.84432557254138</v>
+        <v>-36.84432557314722</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.174876591812904</v>
+        <v>-2.174876591940688</v>
       </c>
       <c r="P15" t="n">
-        <v>85.8345289635613</v>
+        <v>85.8345289638703</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.049790589544841</v>
+        <v>5.049790589604982</v>
       </c>
       <c r="R15" t="n">
-        <v>-68.77545927978912</v>
+        <v>-68.77545928012933</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.05592852579814611</v>
+        <v>-0.05592852579880625</v>
       </c>
       <c r="T15" t="n">
-        <v>-375.8084301061951</v>
+        <v>-375.8084301076287</v>
       </c>
       <c r="U15" t="n">
-        <v>-28.12386694545614</v>
+        <v>-28.12386694568909</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005350612470906464</v>
+        <v>-0.0005350612470926223</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.917687451510774e-05</v>
+        <v>-8.917687451543705e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>-84.53967704032213</v>
+        <v>-84.53967704063432</v>
       </c>
       <c r="I16" t="n">
-        <v>-17835.37490302155</v>
+        <v>-17835.37490308741</v>
       </c>
       <c r="J16" t="n">
-        <v>84.5396770403222</v>
+        <v>84.53967704063439</v>
       </c>
       <c r="K16" t="n">
-        <v>5.976631614420171</v>
+        <v>5.976631614471387</v>
       </c>
       <c r="L16" t="n">
-        <v>171.1038425458343</v>
+        <v>171.1038425462361</v>
       </c>
       <c r="M16" t="n">
-        <v>0.05544883212311946</v>
+        <v>0.05544883212377627</v>
       </c>
       <c r="N16" t="n">
-        <v>-209.6149089029861</v>
+        <v>-209.6149089039063</v>
       </c>
       <c r="O16" t="n">
-        <v>1.765111141116449</v>
+        <v>1.765111141198304</v>
       </c>
       <c r="P16" t="n">
-        <v>-84.5396770403222</v>
+        <v>-84.53967704063439</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.976631614420171</v>
+        <v>-5.976631614471387</v>
       </c>
       <c r="R16" t="n">
-        <v>-21.10384254583424</v>
+        <v>-21.10384254623614</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.05544883212311946</v>
+        <v>-0.05544883212377627</v>
       </c>
       <c r="T16" t="n">
-        <v>-367.0081463720166</v>
+        <v>-367.0081463735096</v>
       </c>
       <c r="U16" t="n">
-        <v>34.09467854540435</v>
+        <v>34.0946785456299</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0006529153424409059</v>
+        <v>-0.00065291534244288</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.000108819223740151</v>
+        <v>-0.00010881922374048</v>
       </c>
       <c r="H17" t="n">
-        <v>-103.1606241056631</v>
+        <v>-103.160624105975</v>
       </c>
       <c r="I17" t="n">
-        <v>-21763.84474803019</v>
+        <v>-21763.844748096</v>
       </c>
       <c r="J17" t="n">
-        <v>103.1606241056634</v>
+        <v>103.1606241059749</v>
       </c>
       <c r="K17" t="n">
-        <v>4.116195150090789</v>
+        <v>4.116195150128135</v>
       </c>
       <c r="L17" t="n">
-        <v>173.3137672412556</v>
+        <v>173.3137672415419</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05577790265808225</v>
+        <v>0.05577790265873905</v>
       </c>
       <c r="N17" t="n">
-        <v>-221.6594246672689</v>
+        <v>-221.6594246679597</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.807193706494331</v>
+        <v>-7.807193706483986</v>
       </c>
       <c r="P17" t="n">
-        <v>-103.1606241056634</v>
+        <v>-103.1606241059749</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.116195150090789</v>
+        <v>-4.116195150128135</v>
       </c>
       <c r="R17" t="n">
-        <v>-23.3137672412556</v>
+        <v>-23.31376724154188</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.05577790265808225</v>
+        <v>-0.05577790265873905</v>
       </c>
       <c r="T17" t="n">
-        <v>-368.2231787802656</v>
+        <v>-368.2231787812889</v>
       </c>
       <c r="U17" t="n">
-        <v>32.50436460703907</v>
+        <v>32.50436460725291</v>
       </c>
     </row>
     <row r="18">
@@ -2693,37 +2693,37 @@
         <v>12.51052828051979</v>
       </c>
       <c r="K18" t="n">
-        <v>-20.32886904320844</v>
+        <v>-20.32886904325267</v>
       </c>
       <c r="L18" t="n">
-        <v>-29.95136551373676</v>
+        <v>-29.95136551383587</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1399243619677715</v>
+        <v>-0.1399243619682065</v>
       </c>
       <c r="N18" t="n">
-        <v>119.8137459613649</v>
+        <v>119.8137459617613</v>
       </c>
       <c r="O18" t="n">
-        <v>-64.67502263175106</v>
+        <v>-64.67502263192773</v>
       </c>
       <c r="P18" t="n">
         <v>-12.51052828051979</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.32886904320844</v>
+        <v>20.32886904325267</v>
       </c>
       <c r="R18" t="n">
-        <v>29.95136551373676</v>
+        <v>29.95136551383587</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1399243619677715</v>
+        <v>0.1399243619682065</v>
       </c>
       <c r="T18" t="n">
-        <v>119.7971781485292</v>
+        <v>119.7971781489256</v>
       </c>
       <c r="U18" t="n">
-        <v>-97.95592971391648</v>
+        <v>-97.95592971409337</v>
       </c>
     </row>
     <row r="19">
@@ -2745,52 +2745,52 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0001740734582367232</v>
+        <v>-0.0001740734582384995</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.175918227959039e-05</v>
+        <v>-2.175918227981244e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-20.62770480105169</v>
+        <v>-20.62770480126219</v>
       </c>
       <c r="I19" t="n">
-        <v>-4351.836455918078</v>
+        <v>-4351.836455962487</v>
       </c>
       <c r="J19" t="n">
-        <v>20.62770480103791</v>
+        <v>20.62770480127074</v>
       </c>
       <c r="K19" t="n">
-        <v>32.77195795069392</v>
+        <v>32.77195795073811</v>
       </c>
       <c r="L19" t="n">
-        <v>-526.4796256065976</v>
+        <v>-526.4796256073413</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1674336878034616</v>
+        <v>-0.1674336878040798</v>
       </c>
       <c r="N19" t="n">
-        <v>2151.8736934672</v>
+        <v>2151.873693470231</v>
       </c>
       <c r="O19" t="n">
-        <v>97.65662236329339</v>
+        <v>97.65662236346988</v>
       </c>
       <c r="P19" t="n">
-        <v>-20.62770480103791</v>
+        <v>-20.62770480127074</v>
       </c>
       <c r="Q19" t="n">
-        <v>-32.77195795069392</v>
+        <v>-32.77195795073811</v>
       </c>
       <c r="R19" t="n">
-        <v>526.4796256065976</v>
+        <v>526.4796256073413</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1674336878034616</v>
+        <v>0.1674336878040798</v>
       </c>
       <c r="T19" t="n">
-        <v>2059.96331138558</v>
+        <v>2059.963311388499</v>
       </c>
       <c r="U19" t="n">
-        <v>164.5190412422579</v>
+        <v>164.519041242435</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0002293761867009914</v>
+        <v>0.0002293761867013244</v>
       </c>
       <c r="G20" t="n">
-        <v>2.867202333762392e-05</v>
+        <v>2.867202333766555e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>27.18107812406748</v>
+        <v>27.18107812410694</v>
       </c>
       <c r="I20" t="n">
-        <v>5734.404667524784</v>
+        <v>5734.40466753311</v>
       </c>
       <c r="J20" t="n">
-        <v>-27.18107812406743</v>
+        <v>-27.18107812410744</v>
       </c>
       <c r="K20" t="n">
-        <v>-120.3262129092034</v>
+        <v>-120.3262129092477</v>
       </c>
       <c r="L20" t="n">
-        <v>-38.31274245297931</v>
+        <v>-38.31274245313044</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03750559622947636</v>
+        <v>0.0375055962292552</v>
       </c>
       <c r="N20" t="n">
-        <v>148.6013299059929</v>
+        <v>148.6013299065843</v>
       </c>
       <c r="O20" t="n">
-        <v>-164.5905998148902</v>
+        <v>-164.5905998150671</v>
       </c>
       <c r="P20" t="n">
-        <v>27.18107812406743</v>
+        <v>27.18107812410744</v>
       </c>
       <c r="Q20" t="n">
-        <v>-79.67378709079662</v>
+        <v>-79.67378709075228</v>
       </c>
       <c r="R20" t="n">
-        <v>38.31274245297931</v>
+        <v>38.31274245313044</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.03750559622947636</v>
+        <v>-0.0375055962292552</v>
       </c>
       <c r="T20" t="n">
-        <v>157.9006097178416</v>
+        <v>157.9006097184592</v>
       </c>
       <c r="U20" t="n">
-        <v>1.980896541263149</v>
+        <v>1.980896541085798</v>
       </c>
     </row>
     <row r="21">
@@ -2894,37 +2894,37 @@
         <v>-125.2777544300188</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.751465002016882</v>
+        <v>-7.751465002060866</v>
       </c>
       <c r="L21" t="n">
-        <v>-505.9794931517395</v>
+        <v>-505.9794931523545</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.185348779389393</v>
+        <v>-0.1853487793900617</v>
       </c>
       <c r="N21" t="n">
-        <v>2024.094570697432</v>
+        <v>2024.094570699891</v>
       </c>
       <c r="O21" t="n">
-        <v>2.250969248789389</v>
+        <v>2.250969248613565</v>
       </c>
       <c r="P21" t="n">
         <v>125.2777544300188</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.751465002016882</v>
+        <v>7.751465002060866</v>
       </c>
       <c r="R21" t="n">
-        <v>505.9794931517395</v>
+        <v>505.9794931523545</v>
       </c>
       <c r="S21" t="n">
-        <v>0.185348779389393</v>
+        <v>0.1853487793900617</v>
       </c>
       <c r="T21" t="n">
-        <v>2023.741374516484</v>
+        <v>2023.741374518944</v>
       </c>
       <c r="U21" t="n">
-        <v>-64.26268926492449</v>
+        <v>-64.26268926510053</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.115239550292696e-05</v>
+        <v>-7.115239550303798e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.89404943786587e-06</v>
+        <v>-8.894049437879747e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.431558867096845</v>
+        <v>-8.431558867110001</v>
       </c>
       <c r="I22" t="n">
-        <v>-1778.809887573174</v>
+        <v>-1778.809887575949</v>
       </c>
       <c r="J22" t="n">
-        <v>8.431558867094282</v>
+        <v>8.431558867116109</v>
       </c>
       <c r="K22" t="n">
-        <v>5.907094219625492</v>
+        <v>5.907094219596843</v>
       </c>
       <c r="L22" t="n">
-        <v>-37.44745119590817</v>
+        <v>-37.44745119604755</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7264335376073403</v>
+        <v>-0.7264335376093496</v>
       </c>
       <c r="N22" t="n">
-        <v>149.7634828585553</v>
+        <v>149.7634828591127</v>
       </c>
       <c r="O22" t="n">
-        <v>34.86921080087586</v>
+        <v>34.86921080075126</v>
       </c>
       <c r="P22" t="n">
-        <v>-8.431558867094282</v>
+        <v>-8.431558867116109</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.907094219625492</v>
+        <v>-5.907094219596843</v>
       </c>
       <c r="R22" t="n">
-        <v>37.44745119590817</v>
+        <v>37.44745119604755</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7264335376073403</v>
+        <v>0.7264335376093496</v>
       </c>
       <c r="T22" t="n">
-        <v>149.81612670871</v>
+        <v>149.8161267092676</v>
       </c>
       <c r="U22" t="n">
-        <v>12.38754295612807</v>
+        <v>12.38754295602348</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00162463354023501</v>
+        <v>0.001624633540233233</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0002030791925293762</v>
+        <v>0.0002030791925291542</v>
       </c>
       <c r="H23" t="n">
-        <v>192.5190745178487</v>
+        <v>192.5190745176382</v>
       </c>
       <c r="I23" t="n">
-        <v>40615.83850587524</v>
+        <v>40615.83850583083</v>
       </c>
       <c r="J23" t="n">
-        <v>-192.5190745177679</v>
+        <v>-192.519074517535</v>
       </c>
       <c r="K23" t="n">
-        <v>66.80885951768202</v>
+        <v>66.80885951796712</v>
       </c>
       <c r="L23" t="n">
-        <v>-357.2856302055961</v>
+        <v>-357.2856302062857</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.09736451574406163</v>
+        <v>-0.09736451574442088</v>
       </c>
       <c r="N23" t="n">
-        <v>1908.094331492271</v>
+        <v>1908.094331495953</v>
       </c>
       <c r="O23" t="n">
-        <v>169.9159291470286</v>
+        <v>169.9159291478577</v>
       </c>
       <c r="P23" t="n">
-        <v>192.5190745177679</v>
+        <v>192.519074517535</v>
       </c>
       <c r="Q23" t="n">
-        <v>-66.80885951768202</v>
+        <v>-66.80885951796712</v>
       </c>
       <c r="R23" t="n">
-        <v>357.2856302055961</v>
+        <v>357.2856302062857</v>
       </c>
       <c r="S23" t="n">
-        <v>0.09736451574406163</v>
+        <v>0.09736451574442088</v>
       </c>
       <c r="T23" t="n">
-        <v>950.1907101524979</v>
+        <v>950.1907101543316</v>
       </c>
       <c r="U23" t="n">
-        <v>364.5549469944276</v>
+        <v>364.5549469958794</v>
       </c>
     </row>
     <row r="24">
@@ -3080,52 +3080,52 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>1.503836553162774e-05</v>
+        <v>1.503836553151672e-05</v>
       </c>
       <c r="G24" t="n">
-        <v>1.879795691453467e-06</v>
+        <v>1.87979569143959e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>1.782046315497887</v>
+        <v>1.782046315484731</v>
       </c>
       <c r="I24" t="n">
-        <v>375.9591382906935</v>
+        <v>375.9591382879179</v>
       </c>
       <c r="J24" t="n">
         <v>-1.782046315493062</v>
       </c>
       <c r="K24" t="n">
-        <v>-50.12585500958915</v>
+        <v>-50.12585500939213</v>
       </c>
       <c r="L24" t="n">
-        <v>-37.37605177413763</v>
+        <v>-37.37605177429701</v>
       </c>
       <c r="M24" t="n">
-        <v>1.113355533693104</v>
+        <v>1.113355533694651</v>
       </c>
       <c r="N24" t="n">
-        <v>99.01739029673753</v>
+        <v>99.01739029716171</v>
       </c>
       <c r="O24" t="n">
-        <v>191.0147515798436</v>
+        <v>191.0147515809632</v>
       </c>
       <c r="P24" t="n">
         <v>1.782046315493062</v>
       </c>
       <c r="Q24" t="n">
-        <v>-149.8741449904109</v>
+        <v>-149.8741449906079</v>
       </c>
       <c r="R24" t="n">
-        <v>37.37605177413763</v>
+        <v>37.37605177429701</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.113355533693104</v>
+        <v>-1.113355533694651</v>
       </c>
       <c r="T24" t="n">
-        <v>199.9910238963635</v>
+        <v>199.9910238972143</v>
       </c>
       <c r="U24" t="n">
-        <v>207.9784083434427</v>
+        <v>207.9784083438993</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.001076486602899607</v>
+        <v>0.00107648660289783</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001345608253624508</v>
+        <v>0.0001345608253622288</v>
       </c>
       <c r="H25" t="n">
-        <v>127.5636624436034</v>
+        <v>127.5636624433929</v>
       </c>
       <c r="I25" t="n">
-        <v>26912.16507249017</v>
+        <v>26912.16507244576</v>
       </c>
       <c r="J25" t="n">
-        <v>-127.5636624436593</v>
+        <v>-127.5636624434264</v>
       </c>
       <c r="K25" t="n">
-        <v>18.3901745281176</v>
+        <v>18.39017452808879</v>
       </c>
       <c r="L25" t="n">
-        <v>-431.74139011613</v>
+        <v>-431.7413901167282</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2914433421853525</v>
+        <v>-0.291443342186532</v>
       </c>
       <c r="N25" t="n">
-        <v>1726.358908332749</v>
+        <v>1726.358908335142</v>
       </c>
       <c r="O25" t="n">
-        <v>112.3335280626782</v>
+        <v>112.3335280625733</v>
       </c>
       <c r="P25" t="n">
-        <v>127.5636624436593</v>
+        <v>127.5636624434264</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.3901745281176</v>
+        <v>-18.39017452808879</v>
       </c>
       <c r="R25" t="n">
-        <v>431.74139011613</v>
+        <v>431.7413901167282</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2914433421853525</v>
+        <v>0.291443342186532</v>
       </c>
       <c r="T25" t="n">
-        <v>1727.57221259629</v>
+        <v>1727.572212598684</v>
       </c>
       <c r="U25" t="n">
-        <v>34.78786816226227</v>
+        <v>34.78786816213679</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0001051822652722301</v>
+        <v>-0.0001051822652723411</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.314778315902876e-05</v>
+        <v>-1.314778315904264e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.46409843475926</v>
+        <v>-12.46409843477242</v>
       </c>
       <c r="I26" t="n">
-        <v>-2629.556631805752</v>
+        <v>-2629.556631808527</v>
       </c>
       <c r="J26" t="n">
-        <v>12.46409843476431</v>
+        <v>12.46409843477886</v>
       </c>
       <c r="K26" t="n">
-        <v>18.50839878808893</v>
+        <v>18.50839878814895</v>
       </c>
       <c r="L26" t="n">
-        <v>-21.63355112027549</v>
+        <v>-21.6335511203928</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0926466731507235</v>
+        <v>-0.09264667315167774</v>
       </c>
       <c r="N26" t="n">
-        <v>86.54154973736216</v>
+        <v>86.54154973783145</v>
       </c>
       <c r="O26" t="n">
-        <v>90.66689582718391</v>
+        <v>90.66689582742492</v>
       </c>
       <c r="P26" t="n">
-        <v>-12.46409843476431</v>
+        <v>-12.46409843477886</v>
       </c>
       <c r="Q26" t="n">
-        <v>-18.50839878808893</v>
+        <v>-18.50839878814895</v>
       </c>
       <c r="R26" t="n">
-        <v>21.63355112027549</v>
+        <v>21.6335511203928</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0926466731507235</v>
+        <v>0.09264667315167774</v>
       </c>
       <c r="T26" t="n">
-        <v>86.52685922484176</v>
+        <v>86.52685922531087</v>
       </c>
       <c r="U26" t="n">
-        <v>57.40029447752659</v>
+        <v>57.4002944777676</v>
       </c>
     </row>
     <row r="27">
@@ -3281,52 +3281,52 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>0.001536654425072115</v>
+        <v>0.001536654425073891</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0001920818031340144</v>
+        <v>0.0001920818031342364</v>
       </c>
       <c r="H27" t="n">
-        <v>182.0935493710456</v>
+        <v>182.0935493712561</v>
       </c>
       <c r="I27" t="n">
-        <v>38416.36062680287</v>
+        <v>38416.36062684728</v>
       </c>
       <c r="J27" t="n">
-        <v>-182.0935493709985</v>
+        <v>-182.0935493712313</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.959963132195512</v>
+        <v>-5.959963132255233</v>
       </c>
       <c r="L27" t="n">
-        <v>-274.7542534582191</v>
+        <v>-274.7542534589803</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1276615161915826</v>
+        <v>-0.1276615161922457</v>
       </c>
       <c r="N27" t="n">
-        <v>1115.269199423327</v>
+        <v>1115.269199426445</v>
       </c>
       <c r="O27" t="n">
-        <v>-57.08303073159067</v>
+        <v>-57.08303073182913</v>
       </c>
       <c r="P27" t="n">
-        <v>182.0935493709985</v>
+        <v>182.0935493712313</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.959963132195512</v>
+        <v>5.959963132255233</v>
       </c>
       <c r="R27" t="n">
-        <v>274.7542534582191</v>
+        <v>274.7542534589803</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1276615161915826</v>
+        <v>0.1276615161922457</v>
       </c>
       <c r="T27" t="n">
-        <v>1082.764828242425</v>
+        <v>1082.764828245398</v>
       </c>
       <c r="U27" t="n">
-        <v>9.403325674026803</v>
+        <v>9.403325673787522</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>5.565559936138165e-05</v>
+        <v>5.565559936049347e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>6.956949920172706e-06</v>
+        <v>6.956949920061684e-06</v>
       </c>
       <c r="H28" t="n">
-        <v>6.595188524323725</v>
+        <v>6.595188524218476</v>
       </c>
       <c r="I28" t="n">
-        <v>1391.389984034541</v>
+        <v>1391.389984012337</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.595188524341211</v>
+        <v>-6.595188524224795</v>
       </c>
       <c r="K28" t="n">
-        <v>-81.51814703991795</v>
+        <v>-81.51814703985838</v>
       </c>
       <c r="L28" t="n">
-        <v>-28.75694233772689</v>
+        <v>-28.75694233787942</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0207219479267835</v>
+        <v>-0.02072194792745929</v>
       </c>
       <c r="N28" t="n">
-        <v>112.8281492501357</v>
+        <v>112.8281492507293</v>
       </c>
       <c r="O28" t="n">
-        <v>-9.458774506152935</v>
+        <v>-9.458774505914647</v>
       </c>
       <c r="P28" t="n">
-        <v>6.595188524341211</v>
+        <v>6.595188524224795</v>
       </c>
       <c r="Q28" t="n">
-        <v>-118.4818529600821</v>
+        <v>-118.4818529601416</v>
       </c>
       <c r="R28" t="n">
-        <v>28.75694233772689</v>
+        <v>28.75694233787942</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0207219479267835</v>
+        <v>0.02072194792745929</v>
       </c>
       <c r="T28" t="n">
-        <v>117.2273894516794</v>
+        <v>117.227389452306</v>
       </c>
       <c r="U28" t="n">
-        <v>157.3135981868093</v>
+        <v>157.3135981870485</v>
       </c>
     </row>
     <row r="29">
@@ -3427,40 +3427,40 @@
         <v>27840.35725365008</v>
       </c>
       <c r="J29" t="n">
-        <v>-131.9632933821995</v>
+        <v>-131.9632933824323</v>
       </c>
       <c r="K29" t="n">
-        <v>30.92861067592477</v>
+        <v>30.92861067598463</v>
       </c>
       <c r="L29" t="n">
-        <v>-251.5946504736163</v>
+        <v>-251.5946504740586</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1361498444878597</v>
+        <v>-0.1361498444885867</v>
       </c>
       <c r="N29" t="n">
-        <v>1008.826844862238</v>
+        <v>1008.826844864008</v>
       </c>
       <c r="O29" t="n">
-        <v>157.0517121625711</v>
+        <v>157.0517121628106</v>
       </c>
       <c r="P29" t="n">
-        <v>131.9632933821995</v>
+        <v>131.9632933824323</v>
       </c>
       <c r="Q29" t="n">
-        <v>-30.92861067592477</v>
+        <v>-30.92861067598463</v>
       </c>
       <c r="R29" t="n">
-        <v>251.5946504736163</v>
+        <v>251.5946504740586</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1361498444878597</v>
+        <v>0.1361498444885867</v>
       </c>
       <c r="T29" t="n">
-        <v>1003.930358926692</v>
+        <v>1003.930358928461</v>
       </c>
       <c r="U29" t="n">
-        <v>90.37717324482674</v>
+        <v>90.37717324506605</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001054896281654782</v>
+        <v>-0.0001054896281658113</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.318620352068478e-05</v>
+        <v>-1.318620352072641e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.50052093760917</v>
+        <v>-12.50052093764864</v>
       </c>
       <c r="I30" t="n">
-        <v>-2637.240704136956</v>
+        <v>-2637.240704145283</v>
       </c>
       <c r="J30" t="n">
-        <v>12.50052093761042</v>
+        <v>12.50052093763952</v>
       </c>
       <c r="K30" t="n">
-        <v>5.061241533179555</v>
+        <v>5.061241533242764</v>
       </c>
       <c r="L30" t="n">
-        <v>-7.019509614552399</v>
+        <v>-7.019509614610334</v>
       </c>
       <c r="M30" t="n">
-        <v>0.02083464748759228</v>
+        <v>0.02083464748736136</v>
       </c>
       <c r="N30" t="n">
-        <v>28.07581587500367</v>
+        <v>28.0758158752352</v>
       </c>
       <c r="O30" t="n">
-        <v>36.90020666256169</v>
+        <v>36.90020666281453</v>
       </c>
       <c r="P30" t="n">
-        <v>-12.50052093761042</v>
+        <v>-12.50052093763952</v>
       </c>
       <c r="Q30" t="n">
-        <v>-5.061241533179555</v>
+        <v>-5.061241533242764</v>
       </c>
       <c r="R30" t="n">
-        <v>7.019509614552399</v>
+        <v>7.019509614610334</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.02083464748759228</v>
+        <v>-0.02083464748736136</v>
       </c>
       <c r="T30" t="n">
-        <v>28.08026104141551</v>
+        <v>28.08026104164746</v>
       </c>
       <c r="U30" t="n">
-        <v>3.589725602874751</v>
+        <v>3.5897256031285</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0006230945216358919</v>
+        <v>0.0006230945216323391</v>
       </c>
       <c r="G31" t="n">
-        <v>7.788681520448648e-05</v>
+        <v>7.788681520404239e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>73.83670081385318</v>
+        <v>73.83670081343219</v>
       </c>
       <c r="I31" t="n">
-        <v>15577.36304089729</v>
+        <v>15577.36304080848</v>
       </c>
       <c r="J31" t="n">
-        <v>-73.8367008138448</v>
+        <v>-73.83670081337914</v>
       </c>
       <c r="K31" t="n">
-        <v>7.450730348091383</v>
+        <v>7.450730348027498</v>
       </c>
       <c r="L31" t="n">
-        <v>-92.85403857811413</v>
+        <v>-92.85403857848101</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.04360590404072028</v>
+        <v>-0.04360590404102432</v>
       </c>
       <c r="N31" t="n">
-        <v>375.8292647536747</v>
+        <v>375.8292647551177</v>
       </c>
       <c r="O31" t="n">
-        <v>-3.533797077073132</v>
+        <v>-3.533797077329041</v>
       </c>
       <c r="P31" t="n">
-        <v>73.8367008138448</v>
+        <v>73.83670081337914</v>
       </c>
       <c r="Q31" t="n">
-        <v>-7.450730348091383</v>
+        <v>-7.450730348027498</v>
       </c>
       <c r="R31" t="n">
-        <v>92.85403857811413</v>
+        <v>92.85403857848101</v>
       </c>
       <c r="S31" t="n">
-        <v>0.04360590404072028</v>
+        <v>0.04360590404102432</v>
       </c>
       <c r="T31" t="n">
-        <v>367.0030438712382</v>
+        <v>367.0030438727302</v>
       </c>
       <c r="U31" t="n">
-        <v>63.13963986180471</v>
+        <v>63.13963986154931</v>
       </c>
     </row>
     <row r="32">
@@ -3631,37 +3631,37 @@
         <v>-13.42736196250189</v>
       </c>
       <c r="K32" t="n">
-        <v>-94.94054335937926</v>
+        <v>-94.9405433593156</v>
       </c>
       <c r="L32" t="n">
-        <v>-8.314361537792287</v>
+        <v>-8.314361537847095</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.005102500778656233</v>
+        <v>-0.005102500778984165</v>
       </c>
       <c r="N32" t="n">
-        <v>34.05107264136433</v>
+        <v>34.0510726415895</v>
       </c>
       <c r="O32" t="n">
-        <v>-63.08419102967977</v>
+        <v>-63.08419102942511</v>
       </c>
       <c r="P32" t="n">
         <v>13.42736196250189</v>
       </c>
       <c r="Q32" t="n">
-        <v>-105.0594566406207</v>
+        <v>-105.0594566406844</v>
       </c>
       <c r="R32" t="n">
-        <v>8.314361537792287</v>
+        <v>8.314361537847095</v>
       </c>
       <c r="S32" t="n">
-        <v>0.005102500778656233</v>
+        <v>0.005102500778984165</v>
       </c>
       <c r="T32" t="n">
-        <v>32.46381966097396</v>
+        <v>32.46381966118725</v>
       </c>
       <c r="U32" t="n">
-        <v>103.5598441546466</v>
+        <v>103.5598441549012</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0006898370413459531</v>
+        <v>0.0006898370413406241</v>
       </c>
       <c r="G33" t="n">
-        <v>8.622963016824414e-05</v>
+        <v>8.622963016757801e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>81.74568939949545</v>
+        <v>81.74568939886396</v>
       </c>
       <c r="I33" t="n">
-        <v>17245.92603364883</v>
+        <v>17245.9260335156</v>
       </c>
       <c r="J33" t="n">
-        <v>-81.74568939954042</v>
+        <v>-81.74568939884193</v>
       </c>
       <c r="K33" t="n">
-        <v>17.54355711260374</v>
+        <v>17.54355711266726</v>
       </c>
       <c r="L33" t="n">
-        <v>-94.84626256787126</v>
+        <v>-94.84626256812794</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.04054494606610064</v>
+        <v>-0.04054494606638104</v>
       </c>
       <c r="N33" t="n">
-        <v>368.2282812810421</v>
+        <v>368.2282812820681</v>
       </c>
       <c r="O33" t="n">
-        <v>103.504066251989</v>
+        <v>103.5040662522431</v>
       </c>
       <c r="P33" t="n">
-        <v>81.74568939954042</v>
+        <v>81.74568939884193</v>
       </c>
       <c r="Q33" t="n">
-        <v>-17.54355711260374</v>
+        <v>-17.54355711266726</v>
       </c>
       <c r="R33" t="n">
-        <v>94.84626256787126</v>
+        <v>94.84626256812794</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04054494606610064</v>
+        <v>0.04054494606638104</v>
       </c>
       <c r="T33" t="n">
-        <v>390.5418192619279</v>
+        <v>390.5418192629554</v>
       </c>
       <c r="U33" t="n">
-        <v>36.84439064884054</v>
+        <v>36.84439064909469</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001455921596786739</v>
+        <v>0.001455921596789192</v>
       </c>
       <c r="H2" t="n">
-        <v>1380.213673753829</v>
+        <v>1380.213673756154</v>
       </c>
       <c r="I2" t="n">
-        <v>291184.3193573478</v>
+        <v>291184.3193578384</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.757925951552276</v>
+        <v>3.757925951556457</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1624422723417782</v>
+        <v>0.1624422723423497</v>
       </c>
       <c r="R2" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03630395006709138</v>
+        <v>-0.03630395006721086</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6098064904006163</v>
+        <v>0.609806490401359</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.005111413036164057</v>
+        <v>-0.005111413036285996</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1624422723417782</v>
+        <v>0.1624422723423497</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3.757925951552276</v>
+        <v>-3.757925951556457</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.005111413036164057</v>
+        <v>-0.005111413036285996</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.6098064904006163</v>
+        <v>0.609806490401359</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.03630395006709138</v>
+        <v>0.03630395006721086</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1380.213673753829</v>
+        <v>-1380.213673756154</v>
       </c>
       <c r="AI2" t="n">
-        <v>-13.20417079465767</v>
+        <v>-13.20417079471022</v>
       </c>
       <c r="AJ2" t="n">
-        <v>475.6982651531055</v>
+        <v>475.6982651535872</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01454786787215924</v>
+        <v>0.0145478678725063</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1878.351598355772</v>
+        <v>-1878.351598357767</v>
       </c>
       <c r="AM2" t="n">
-        <v>-66.4774354336206</v>
+        <v>-66.47743543386669</v>
       </c>
       <c r="AN2" t="n">
-        <v>1380.213673753829</v>
+        <v>1380.213673756154</v>
       </c>
       <c r="AO2" t="n">
-        <v>13.20417079465767</v>
+        <v>13.20417079471022</v>
       </c>
       <c r="AP2" t="n">
-        <v>-475.6982651531055</v>
+        <v>-475.6982651535872</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.01454786787215924</v>
+        <v>-0.0145478678725063</v>
       </c>
       <c r="AR2" t="n">
-        <v>-975.8379925628601</v>
+        <v>-975.8379925637557</v>
       </c>
       <c r="AS2" t="n">
-        <v>-12.74758933432537</v>
+        <v>-12.74758933439462</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001030760455960402</v>
+        <v>0.001030760455962304</v>
       </c>
       <c r="H3" t="n">
-        <v>977.1609122504611</v>
+        <v>977.1609122522644</v>
       </c>
       <c r="I3" t="n">
-        <v>206152.0911920804</v>
+        <v>206152.0911924609</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.723395957223965</v>
+        <v>3.723395957228697</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1623366982634615</v>
+        <v>0.162336698264033</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03628902410958178</v>
+        <v>-0.03628902410970122</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6753566419530859</v>
+        <v>0.6753566419540323</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.03509421220928596</v>
+        <v>-0.03509421220940796</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1623366982634615</v>
+        <v>0.162336698264033</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3.723395957223965</v>
+        <v>-3.723395957228697</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.03509421220928596</v>
+        <v>-0.03509421220940796</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6753566419530859</v>
+        <v>0.6753566419540323</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.03628902410958178</v>
+        <v>0.03628902410970122</v>
       </c>
       <c r="AH3" t="n">
-        <v>-977.1609122504613</v>
+        <v>-977.1609122522647</v>
       </c>
       <c r="AI3" t="n">
-        <v>-13.18917439722999</v>
+        <v>-13.18917439728258</v>
       </c>
       <c r="AJ3" t="n">
-        <v>418.6737544032946</v>
+        <v>418.6737544037614</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0998835270571985</v>
+        <v>0.0998835270575457</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1755.785178255167</v>
+        <v>-1755.785178257268</v>
       </c>
       <c r="AM3" t="n">
-        <v>-66.42140103278049</v>
+        <v>-66.42140103302664</v>
       </c>
       <c r="AN3" t="n">
-        <v>977.1609122504613</v>
+        <v>977.1609122522647</v>
       </c>
       <c r="AO3" t="n">
-        <v>13.18917439722999</v>
+        <v>13.18917439728258</v>
       </c>
       <c r="AP3" t="n">
-        <v>-418.6737544032946</v>
+        <v>-418.6737544037614</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0998835270571985</v>
+        <v>-0.0998835270575457</v>
       </c>
       <c r="AR3" t="n">
-        <v>-756.2573481646002</v>
+        <v>-756.2573481653003</v>
       </c>
       <c r="AS3" t="n">
-        <v>-12.71364535059946</v>
+        <v>-12.71364535066883</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001032719886363857</v>
+        <v>-0.001032719886365733</v>
       </c>
       <c r="H4" t="n">
-        <v>-979.018452272936</v>
+        <v>-979.0184522747154</v>
       </c>
       <c r="I4" t="n">
-        <v>-206543.9772727713</v>
+        <v>-206543.9772731467</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.723221883765729</v>
+        <v>3.723221883770459</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1923970678416461</v>
+        <v>-0.1923970678424733</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04214837918573356</v>
+        <v>0.04214837918590374</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5925544959336078</v>
+        <v>0.5925544959344536</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0251422011951866</v>
+        <v>0.0251422011950651</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.1923970678416461</v>
+        <v>-0.1923970678424733</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3.723221883765729</v>
+        <v>-3.723221883770459</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0251422011951866</v>
+        <v>0.0251422011950651</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5925544959336078</v>
+        <v>0.5925544959344536</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.04214837918573356</v>
+        <v>-0.04214837918590374</v>
       </c>
       <c r="AH4" t="n">
-        <v>979.0184522729362</v>
+        <v>979.0184522747155</v>
       </c>
       <c r="AI4" t="n">
-        <v>16.26814280349655</v>
+        <v>16.26814280357464</v>
       </c>
       <c r="AJ4" t="n">
-        <v>554.9044043380102</v>
+        <v>554.9044043385509</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.07155857263245415</v>
+        <v>-0.07155857263210837</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1953.2035400049</v>
+        <v>-1953.203540007148</v>
       </c>
       <c r="AM4" t="n">
-        <v>79.99422900793247</v>
+        <v>79.99422900829268</v>
       </c>
       <c r="AN4" t="n">
-        <v>-979.0184522729362</v>
+        <v>-979.0184522747155</v>
       </c>
       <c r="AO4" t="n">
-        <v>-16.26814280349655</v>
+        <v>-16.26814280357464</v>
       </c>
       <c r="AP4" t="n">
-        <v>-404.9044043380101</v>
+        <v>-404.9044043385508</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.07155857263245415</v>
+        <v>0.07155857263210837</v>
       </c>
       <c r="AR4" t="n">
-        <v>-926.2228860231605</v>
+        <v>-926.2228860241569</v>
       </c>
       <c r="AS4" t="n">
-        <v>17.61462781304681</v>
+        <v>17.61462781315514</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001453962166383287</v>
+        <v>-0.001453962166385767</v>
       </c>
       <c r="H5" t="n">
-        <v>-1378.356133731356</v>
+        <v>-1378.356133733707</v>
       </c>
       <c r="I5" t="n">
-        <v>-290792.4332766574</v>
+        <v>-290792.4332771534</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.758983147792192</v>
+        <v>3.758983147796373</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1926264440283471</v>
+        <v>-0.1926264440291746</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05052610874595759</v>
+        <v>0.05052610874615139</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6101246851582274</v>
+        <v>0.6101246851589696</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06503362791338377</v>
+        <v>-0.06503362791350591</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1926264440283471</v>
+        <v>-0.1926264440291746</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3.758983147792192</v>
+        <v>-3.758983147796373</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.06503362791338377</v>
+        <v>-0.06503362791350591</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6101246851582274</v>
+        <v>0.6101246851589696</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.05052610874595759</v>
+        <v>-0.05052610874615139</v>
       </c>
       <c r="AH5" t="n">
-        <v>1378.356133731357</v>
+        <v>1378.356133733707</v>
       </c>
       <c r="AI5" t="n">
-        <v>10.12520238831702</v>
+        <v>10.12520238837771</v>
       </c>
       <c r="AJ5" t="n">
-        <v>550.7235761049859</v>
+        <v>550.7235761054679</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1850957102150153</v>
+        <v>0.1850957102153629</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1953.662995332046</v>
+        <v>-1953.662995334041</v>
       </c>
       <c r="AM5" t="n">
-        <v>67.76492763695965</v>
+        <v>67.76492763728514</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1378.356133731357</v>
+        <v>-1378.356133733707</v>
       </c>
       <c r="AO5" t="n">
-        <v>-10.12520238831702</v>
+        <v>-10.12520238837771</v>
       </c>
       <c r="AP5" t="n">
-        <v>-400.7235761049859</v>
+        <v>-400.7235761054679</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.1850957102150153</v>
+        <v>-0.1850957102153629</v>
       </c>
       <c r="AR5" t="n">
-        <v>-900.678461297869</v>
+        <v>-900.6784612987663</v>
       </c>
       <c r="AS5" t="n">
-        <v>-7.013713307057571</v>
+        <v>-7.013713307018918</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005343562120812355</v>
+        <v>0.005343562120822556</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008905936868020591</v>
+        <v>0.0008905936868037594</v>
       </c>
       <c r="H6" t="n">
-        <v>844.282815088352</v>
+        <v>844.2828150899639</v>
       </c>
       <c r="I6" t="n">
-        <v>178118.7373604118</v>
+        <v>178118.7373607519</v>
       </c>
       <c r="J6" t="n">
-        <v>3.757925951552276</v>
+        <v>3.757925951556457</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1624422723417782</v>
+        <v>0.1624422723423497</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03630395006709138</v>
+        <v>-0.03630395006721086</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6098064904006163</v>
+        <v>0.609806490401359</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.005111413036164057</v>
+        <v>-0.005111413036285996</v>
       </c>
       <c r="P6" t="n">
-        <v>8.658378534736178</v>
+        <v>8.658378534746893</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5437220967391151</v>
+        <v>0.5437220967409437</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01407909170153279</v>
+        <v>0.01407909170155771</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.04556477868176344</v>
+        <v>-0.04556477868193153</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5226650286341942</v>
+        <v>0.522665028634919</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1550967117141002</v>
+        <v>-0.1550967117146793</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1624422723417782</v>
+        <v>0.1624422723423497</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.757925951552276</v>
+        <v>-3.757925951556457</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.005111413036164057</v>
+        <v>-0.005111413036285996</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6098064904006163</v>
+        <v>0.609806490401359</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03630395006709138</v>
+        <v>0.03630395006721086</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01407909170153279</v>
+        <v>0.01407909170155771</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5437220967391151</v>
+        <v>0.5437220967409437</v>
       </c>
       <c r="AD6" t="n">
-        <v>-8.658378534736178</v>
+        <v>-8.658378534746893</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.1550967117141002</v>
+        <v>-0.1550967117146793</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.5226650286341942</v>
+        <v>0.522665028634919</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.04556477868176344</v>
+        <v>0.04556477868193153</v>
       </c>
       <c r="AH6" t="n">
-        <v>-844.2828150883522</v>
+        <v>-844.2828150899641</v>
       </c>
       <c r="AI6" t="n">
-        <v>-33.46616407719057</v>
+        <v>-33.46616407728784</v>
       </c>
       <c r="AJ6" t="n">
-        <v>370.7493797662693</v>
+        <v>370.7493797667951</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.4268812346987415</v>
+        <v>0.4268812347000424</v>
       </c>
       <c r="AL6" t="n">
-        <v>-1047.763457591656</v>
+        <v>-1047.763457593219</v>
       </c>
       <c r="AM6" t="n">
-        <v>-107.251505406429</v>
+        <v>-107.2515054067568</v>
       </c>
       <c r="AN6" t="n">
-        <v>844.2828150883522</v>
+        <v>844.2828150899641</v>
       </c>
       <c r="AO6" t="n">
-        <v>33.46616407719057</v>
+        <v>33.46616407728784</v>
       </c>
       <c r="AP6" t="n">
-        <v>-370.7493797662693</v>
+        <v>-370.7493797667951</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.4268812346987415</v>
+        <v>-0.4268812347000424</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1176.73282100596</v>
+        <v>-1176.732821007551</v>
       </c>
       <c r="AS6" t="n">
-        <v>-93.54547905671429</v>
+        <v>-93.54547905697024</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003041978811124054</v>
+        <v>0.003041978811131388</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005069964685206757</v>
+        <v>0.0005069964685218979</v>
       </c>
       <c r="H7" t="n">
-        <v>480.6326521576005</v>
+        <v>480.6326521587592</v>
       </c>
       <c r="I7" t="n">
-        <v>101399.2937041351</v>
+        <v>101399.2937043796</v>
       </c>
       <c r="J7" t="n">
-        <v>3.723395957223965</v>
+        <v>3.723395957228697</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1623366982634615</v>
+        <v>0.162336698264033</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03628902410958178</v>
+        <v>-0.03628902410970122</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6753566419530859</v>
+        <v>0.6753566419540323</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.03509421220928596</v>
+        <v>-0.03509421220940796</v>
       </c>
       <c r="P7" t="n">
-        <v>10.03693211708712</v>
+        <v>10.03693211710211</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5436509443436122</v>
+        <v>0.5436509443454407</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009226541546886466</v>
+        <v>0.009226541546905213</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.04561220557379464</v>
+        <v>-0.04561220557396294</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8629762354412365</v>
+        <v>0.8629762354429026</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1753504665291883</v>
+        <v>-0.1753504665297493</v>
       </c>
       <c r="V7" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1623366982634615</v>
+        <v>0.162336698264033</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.723395957223965</v>
+        <v>-3.723395957228697</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.03509421220928596</v>
+        <v>-0.03509421220940796</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6753566419530859</v>
+        <v>0.6753566419540323</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03628902410958178</v>
+        <v>0.03628902410970122</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.009226541546886466</v>
+        <v>0.009226541546905213</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5436509443436122</v>
+        <v>0.5436509443454407</v>
       </c>
       <c r="AD7" t="n">
-        <v>-10.03693211708712</v>
+        <v>-10.03693211710211</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.1753504665291883</v>
+        <v>-0.1753504665297493</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.8629762354412365</v>
+        <v>0.8629762354429026</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.04561220557379464</v>
+        <v>0.04561220557396294</v>
       </c>
       <c r="AH7" t="n">
-        <v>-480.6326521576007</v>
+        <v>-480.6326521587592</v>
       </c>
       <c r="AI7" t="n">
-        <v>-33.45060406740529</v>
+        <v>-33.45060406750243</v>
       </c>
       <c r="AJ7" t="n">
-        <v>418.9725901611122</v>
+        <v>418.9725901617112</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.3991908776797221</v>
+        <v>0.3991908776809715</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1395.756269664567</v>
+        <v>-1395.756269666897</v>
       </c>
       <c r="AM7" t="n">
-        <v>-107.2509664857333</v>
+        <v>-107.2509664860609</v>
       </c>
       <c r="AN7" t="n">
-        <v>480.6326521576007</v>
+        <v>480.6326521587592</v>
       </c>
       <c r="AO7" t="n">
-        <v>33.45060406740529</v>
+        <v>33.45060406750243</v>
       </c>
       <c r="AP7" t="n">
-        <v>-418.9725901611122</v>
+        <v>-418.9725901617112</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.3991908776797221</v>
+        <v>-0.3991908776809715</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1118.079271302104</v>
+        <v>-1118.07927130337</v>
       </c>
       <c r="AS7" t="n">
-        <v>-93.45265791869829</v>
+        <v>-93.45265791895361</v>
       </c>
     </row>
     <row r="8">
@@ -4825,43 +4825,43 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.003106655500755174</v>
+        <v>-0.003106655500762689</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.000517775916792529</v>
+        <v>-0.0005177759167937815</v>
       </c>
       <c r="H8" t="n">
-        <v>-490.8515691193175</v>
+        <v>-490.8515691205048</v>
       </c>
       <c r="I8" t="n">
-        <v>-103555.1833585058</v>
+        <v>-103555.1833587563</v>
       </c>
       <c r="J8" t="n">
-        <v>3.723221883765729</v>
+        <v>3.723221883770459</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1923970678416461</v>
+        <v>-0.1923970678424733</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04214837918573356</v>
+        <v>0.04214837918590374</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5925544959336078</v>
+        <v>0.5925544959344536</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0251422011951866</v>
+        <v>0.0251422011950651</v>
       </c>
       <c r="P8" t="n">
-        <v>10.03855675062735</v>
+        <v>10.03855675064235</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.7997579802013167</v>
+        <v>-0.7997579802044718</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.009302974818938313</v>
+        <v>-0.00930297481895709</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -4873,31 +4873,31 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1923970678416461</v>
+        <v>-0.1923970678424733</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.723221883765729</v>
+        <v>-3.723221883770459</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0251422011951866</v>
+        <v>0.0251422011950651</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5925544959336078</v>
+        <v>0.5925544959344536</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.04214837918573356</v>
+        <v>-0.04214837918590374</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.009302974818938313</v>
+        <v>-0.00930297481895709</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.7997579802013167</v>
+        <v>-0.7997579802044718</v>
       </c>
       <c r="AD8" t="n">
-        <v>-10.03855675062735</v>
+        <v>-10.03855675064235</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -4909,40 +4909,40 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>490.8515691193177</v>
+        <v>490.8515691205049</v>
       </c>
       <c r="AI8" t="n">
-        <v>118.6258911179426</v>
+        <v>118.6258911183909</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1194.292273501664</v>
+        <v>1194.29227350357</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.07155857263245415</v>
+        <v>0.07155857263210837</v>
       </c>
       <c r="AL8" t="n">
-        <v>-2994.386493514121</v>
+        <v>-2994.386493519215</v>
       </c>
       <c r="AM8" t="n">
-        <v>324.687872756385</v>
+        <v>324.6878727576038</v>
       </c>
       <c r="AN8" t="n">
-        <v>-490.8515691193177</v>
+        <v>-490.8515691205049</v>
       </c>
       <c r="AO8" t="n">
-        <v>-118.6258911179426</v>
+        <v>-118.6258911183909</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1044.292273501664</v>
+        <v>-1044.29227350357</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.07155857263245415</v>
+        <v>-0.07155857263210837</v>
       </c>
       <c r="AR8" t="n">
-        <v>-3721.36714749586</v>
+        <v>-3721.367147502207</v>
       </c>
       <c r="AS8" t="n">
-        <v>387.0674739512706</v>
+        <v>387.0674739527414</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.005278885431181244</v>
+        <v>-0.005278885431191272</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0008798142385302073</v>
+        <v>-0.0008798142385318787</v>
       </c>
       <c r="H9" t="n">
-        <v>-834.0638981266366</v>
+        <v>-834.063898128221</v>
       </c>
       <c r="I9" t="n">
-        <v>-175962.8477060414</v>
+        <v>-175962.8477063757</v>
       </c>
       <c r="J9" t="n">
-        <v>3.758983147792192</v>
+        <v>3.758983147796373</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1926264440283471</v>
+        <v>-0.1926264440291746</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05052610874595759</v>
+        <v>0.05052610874615139</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6101246851582274</v>
+        <v>0.6101246851589696</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06503362791338377</v>
+        <v>-0.06503362791350591</v>
       </c>
       <c r="P9" t="n">
-        <v>8.659455021339078</v>
+        <v>8.659455021349791</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.7997730185668483</v>
+        <v>-0.7997730185700033</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.01400265842948097</v>
+        <v>-0.01400265842950587</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09096723747714046</v>
+        <v>0.0909672374775249</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5215719617301026</v>
+        <v>0.5215719617308274</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2249576665793398</v>
+        <v>-0.2249576665799374</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1926264440283471</v>
+        <v>-0.1926264440291746</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.758983147792192</v>
+        <v>-3.758983147796373</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.06503362791338377</v>
+        <v>-0.06503362791350591</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6101246851582274</v>
+        <v>0.6101246851589696</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.05052610874595759</v>
+        <v>-0.05052610874615139</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.01400265842948097</v>
+        <v>-0.01400265842950587</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.7997730185668483</v>
+        <v>-0.7997730185700033</v>
       </c>
       <c r="AD9" t="n">
-        <v>-8.659455021339078</v>
+        <v>-8.659455021349791</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.2249576665793398</v>
+        <v>-0.2249576665799374</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.5215719617301026</v>
+        <v>0.5215719617308274</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.09096723747714046</v>
+        <v>-0.0909672374775249</v>
       </c>
       <c r="AH9" t="n">
-        <v>834.0638981266368</v>
+        <v>834.0638981282214</v>
       </c>
       <c r="AI9" t="n">
-        <v>45.05774551440441</v>
+        <v>45.0577455145506</v>
       </c>
       <c r="AJ9" t="n">
-        <v>446.3275434442011</v>
+        <v>446.3275434447266</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.4551684177415671</v>
+        <v>0.4551684177429204</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1123.453614995791</v>
+        <v>-1123.453614997354</v>
       </c>
       <c r="AM9" t="n">
-        <v>165.0996718042885</v>
+        <v>165.0996718048683</v>
       </c>
       <c r="AN9" t="n">
-        <v>-834.0638981266368</v>
+        <v>-834.0638981282214</v>
       </c>
       <c r="AO9" t="n">
-        <v>-45.05774551440441</v>
+        <v>-45.0577455145506</v>
       </c>
       <c r="AP9" t="n">
-        <v>-296.3275434442011</v>
+        <v>-296.3275434447266</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.4551684177415671</v>
+        <v>-0.4551684177429204</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1104.511645669415</v>
+        <v>-1104.511645671005</v>
       </c>
       <c r="AS9" t="n">
-        <v>105.246801282138</v>
+        <v>105.2468012824354</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002374012492255152</v>
+        <v>0.002374012492260691</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003956687487091919</v>
+        <v>0.0003956687487101151</v>
       </c>
       <c r="H10" t="n">
-        <v>375.0939737763139</v>
+        <v>375.0939737771891</v>
       </c>
       <c r="I10" t="n">
-        <v>79133.74974183837</v>
+        <v>79133.74974202301</v>
       </c>
       <c r="J10" t="n">
-        <v>8.658378534736178</v>
+        <v>8.658378534746893</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5437220967391151</v>
+        <v>0.5437220967409437</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01407909170153279</v>
+        <v>0.01407909170155771</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04556477868176344</v>
+        <v>-0.04556477868193153</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5226650286341942</v>
+        <v>0.522665028634919</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1550967117141002</v>
+        <v>-0.1550967117146793</v>
       </c>
       <c r="P10" t="n">
-        <v>12.10067564645607</v>
+        <v>12.10067564647184</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.855601378201386</v>
+        <v>0.8556013782045796</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01645310419378794</v>
+        <v>0.0164531041938184</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02662802448650984</v>
+        <v>-0.02662802448665153</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3041205539613382</v>
+        <v>0.3041205539618769</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2765021643922128</v>
+        <v>-0.2765021643933779</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01407909170153279</v>
+        <v>0.01407909170155771</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5437220967391151</v>
+        <v>0.5437220967409437</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.658378534736178</v>
+        <v>-8.658378534746893</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.1550967117141002</v>
+        <v>-0.1550967117146793</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5226650286341942</v>
+        <v>0.522665028634919</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04556477868176344</v>
+        <v>0.04556477868193153</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01645310419378794</v>
+        <v>0.0164531041938184</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.855601378201386</v>
+        <v>0.8556013782045796</v>
       </c>
       <c r="AD10" t="n">
-        <v>-12.10067564645607</v>
+        <v>-12.10067564647184</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.2765021643922128</v>
+        <v>-0.2765021643933779</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3041205539613382</v>
+        <v>0.3041205539618769</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.02662802448650984</v>
+        <v>0.02662802448665153</v>
       </c>
       <c r="AH10" t="n">
-        <v>-375.0939737763142</v>
+        <v>-375.0939737771891</v>
       </c>
       <c r="AI10" t="n">
-        <v>-23.50754841617129</v>
+        <v>-23.50754841627872</v>
       </c>
       <c r="AJ10" t="n">
-        <v>237.2786231035455</v>
+        <v>237.2786231038581</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.3455385960838586</v>
+        <v>0.3455385960855267</v>
       </c>
       <c r="AL10" t="n">
-        <v>-550.1129580527219</v>
+        <v>-550.1129580535226</v>
       </c>
       <c r="AM10" t="n">
-        <v>-56.50944714402618</v>
+        <v>-56.50944714432887</v>
       </c>
       <c r="AN10" t="n">
-        <v>375.0939737763142</v>
+        <v>375.0939737771891</v>
       </c>
       <c r="AO10" t="n">
-        <v>23.50754841617129</v>
+        <v>23.50754841627872</v>
       </c>
       <c r="AP10" t="n">
-        <v>-237.2786231035455</v>
+        <v>-237.2786231038581</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.3455385960838586</v>
+        <v>-0.3455385960855267</v>
       </c>
       <c r="AR10" t="n">
-        <v>-873.5587805685493</v>
+        <v>-873.558780569625</v>
       </c>
       <c r="AS10" t="n">
-        <v>-84.53584335300144</v>
+        <v>-84.5358433533433</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002145286274060163</v>
+        <v>0.002145286274066197</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003575477123433605</v>
+        <v>0.0003575477123443661</v>
       </c>
       <c r="H11" t="n">
-        <v>338.9552313015058</v>
+        <v>338.955231302459</v>
       </c>
       <c r="I11" t="n">
-        <v>71509.54246867209</v>
+        <v>71509.5424688732</v>
       </c>
       <c r="J11" t="n">
-        <v>10.03693211708712</v>
+        <v>10.03693211710211</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5436509443436122</v>
+        <v>0.5436509443454407</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009226541546886466</v>
+        <v>0.009226541546905213</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.04561220557379464</v>
+        <v>-0.04561220557396294</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8629762354412365</v>
+        <v>0.8629762354429026</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1753504665291883</v>
+        <v>-0.1753504665297493</v>
       </c>
       <c r="P11" t="n">
-        <v>14.61043109294954</v>
+        <v>14.61043109297521</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8554961959361138</v>
+        <v>0.8554961959393073</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01137182782094663</v>
+        <v>0.01137182782097141</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02661478979054551</v>
+        <v>-0.02661478979068704</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3475225990409564</v>
+        <v>0.3475225990419422</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3064720755180301</v>
+        <v>-0.306472075519195</v>
       </c>
       <c r="V11" t="n">
-        <v>0.009226541546886466</v>
+        <v>0.009226541546905213</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5436509443436122</v>
+        <v>0.5436509443454407</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.03693211708712</v>
+        <v>-10.03693211710211</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.1753504665291883</v>
+        <v>-0.1753504665297493</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.8629762354412365</v>
+        <v>0.8629762354429026</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.04561220557379464</v>
+        <v>0.04561220557396294</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01137182782094663</v>
+        <v>0.01137182782097141</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8554961959361138</v>
+        <v>0.8554961959393073</v>
       </c>
       <c r="AD11" t="n">
-        <v>-14.61043109294954</v>
+        <v>-14.61043109297521</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.3064720755180301</v>
+        <v>-0.306472075519195</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.3475225990409564</v>
+        <v>0.3475225990419422</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02661478979054551</v>
+        <v>0.02661478979068704</v>
       </c>
       <c r="AH11" t="n">
-        <v>-338.9552313015058</v>
+        <v>-338.9552313024592</v>
       </c>
       <c r="AI11" t="n">
-        <v>-23.4738521565387</v>
+        <v>-23.4738521566461</v>
       </c>
       <c r="AJ11" t="n">
-        <v>232.360609862576</v>
+        <v>232.3606098632458</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.3731922717374728</v>
+        <v>0.3731922717391915</v>
       </c>
       <c r="AL11" t="n">
-        <v>-315.6461386515213</v>
+        <v>-315.6461386530264</v>
       </c>
       <c r="AM11" t="n">
-        <v>-56.36346879001178</v>
+        <v>-56.36346879031407</v>
       </c>
       <c r="AN11" t="n">
-        <v>338.9552313015058</v>
+        <v>338.9552313024592</v>
       </c>
       <c r="AO11" t="n">
-        <v>23.4738521565387</v>
+        <v>23.4738521566461</v>
       </c>
       <c r="AP11" t="n">
-        <v>-232.360609862576</v>
+        <v>-232.3606098632458</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.3731922717374728</v>
+        <v>-0.3731922717391915</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1078.517520523936</v>
+        <v>-1078.51752052645</v>
       </c>
       <c r="AS11" t="n">
-        <v>-84.47964414922058</v>
+        <v>-84.47964414956243</v>
       </c>
     </row>
     <row r="12">
@@ -5381,25 +5381,25 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.002092006254182372</v>
+        <v>-0.002092006254188197</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0003486677090303953</v>
+        <v>-0.0003486677090313662</v>
       </c>
       <c r="H12" t="n">
-        <v>-330.5369881608148</v>
+        <v>-330.5369881617351</v>
       </c>
       <c r="I12" t="n">
-        <v>-69733.54180607905</v>
+        <v>-69733.54180627322</v>
       </c>
       <c r="J12" t="n">
-        <v>10.03855675062735</v>
+        <v>10.03855675064235</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7997579802013167</v>
+        <v>-0.7997579802044718</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.009302974818938313</v>
+        <v>-0.00930297481895709</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -5411,31 +5411,31 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14.61196774737462</v>
+        <v>14.61196774740029</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.299417015686306</v>
+        <v>-1.29941701569186</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.01139498107312069</v>
+        <v>-0.01139498107314529</v>
       </c>
       <c r="S12" t="n">
-        <v>0.03319060518208777</v>
+        <v>0.03319060518225687</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3182393817608644</v>
+        <v>0.31823938176172</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.246574457134591</v>
+        <v>-0.2465744571357565</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.009302974818938313</v>
+        <v>-0.00930297481895709</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7997579802013167</v>
+        <v>-0.7997579802044718</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.03855675062735</v>
+        <v>-10.03855675064235</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -5447,58 +5447,58 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.01139498107312069</v>
+        <v>-0.01139498107314529</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.299417015686306</v>
+        <v>-1.29941701569186</v>
       </c>
       <c r="AD12" t="n">
-        <v>-14.61196774737462</v>
+        <v>-14.61196774740029</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.246574457134591</v>
+        <v>-0.2465744571357565</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.3182393817608644</v>
+        <v>0.31823938176172</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.03319060518208777</v>
+        <v>-0.03319060518225687</v>
       </c>
       <c r="AH12" t="n">
-        <v>330.5369881608146</v>
+        <v>330.5369881617353</v>
       </c>
       <c r="AI12" t="n">
-        <v>98.68818091821899</v>
+        <v>98.68818091868567</v>
       </c>
       <c r="AJ12" t="n">
-        <v>967.6109033612859</v>
+        <v>967.6109033632856</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.7017888395369127</v>
+        <v>0.7017888395402301</v>
       </c>
       <c r="AL12" t="n">
-        <v>-2988.329852586897</v>
+        <v>-2988.32985259353</v>
       </c>
       <c r="AM12" t="n">
-        <v>320.6255905894019</v>
+        <v>320.6255905909271</v>
       </c>
       <c r="AN12" t="n">
-        <v>-330.5369881608146</v>
+        <v>-330.5369881617353</v>
       </c>
       <c r="AO12" t="n">
-        <v>-98.68818091821899</v>
+        <v>-98.68818091868567</v>
       </c>
       <c r="AP12" t="n">
-        <v>-817.6109033612859</v>
+        <v>-817.6109033632856</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.7017888395369127</v>
+        <v>-0.7017888395402301</v>
       </c>
       <c r="AR12" t="n">
-        <v>-2367.335567580818</v>
+        <v>-2367.335567586184</v>
       </c>
       <c r="AS12" t="n">
-        <v>271.503494919912</v>
+        <v>271.5034949211869</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002427292512132957</v>
+        <v>-0.002427292512138695</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0004045487520221595</v>
+        <v>-0.0004045487520231159</v>
       </c>
       <c r="H13" t="n">
-        <v>-383.5122169170072</v>
+        <v>-383.5122169179139</v>
       </c>
       <c r="I13" t="n">
-        <v>-80909.75040443189</v>
+        <v>-80909.75040462318</v>
       </c>
       <c r="J13" t="n">
-        <v>8.659455021339078</v>
+        <v>8.659455021349791</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7997730185668483</v>
+        <v>-0.7997730185700033</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.01400265842948097</v>
+        <v>-0.01400265842950587</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09096723747714046</v>
+        <v>0.0909672374775249</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5215719617301026</v>
+        <v>0.5215719617308274</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2249576665793398</v>
+        <v>-0.2249576665799374</v>
       </c>
       <c r="P13" t="n">
-        <v>12.10178926074621</v>
+        <v>12.10178926076199</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.299472671285667</v>
+        <v>-1.29947267129122</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.01642995094161392</v>
+        <v>-0.01642995094164457</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03715388464293796</v>
+        <v>0.03715388464313682</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3085318025519207</v>
+        <v>0.3085318025524598</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3365693165703608</v>
+        <v>-0.3365693165715262</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.01400265842948097</v>
+        <v>-0.01400265842950587</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.7997730185668483</v>
+        <v>-0.7997730185700033</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.659455021339078</v>
+        <v>-8.659455021349791</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.2249576665793398</v>
+        <v>-0.2249576665799374</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.5215719617301026</v>
+        <v>0.5215719617308274</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.09096723747714046</v>
+        <v>-0.0909672374775249</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.01642995094161392</v>
+        <v>-0.01642995094164457</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.299472671285667</v>
+        <v>-1.29947267129122</v>
       </c>
       <c r="AD13" t="n">
-        <v>-12.10178926074621</v>
+        <v>-12.10178926076199</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.3365693165703608</v>
+        <v>-0.3365693165715262</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.3085318025519207</v>
+        <v>0.3085318025524598</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.03715388464293796</v>
+        <v>-0.03715388464313682</v>
       </c>
       <c r="AH13" t="n">
-        <v>383.5122169170072</v>
+        <v>383.512216917914</v>
       </c>
       <c r="AI13" t="n">
-        <v>28.44961730178392</v>
+        <v>28.44961730194387</v>
       </c>
       <c r="AJ13" t="n">
-        <v>309.8323268183962</v>
+        <v>309.8323268187096</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.3176639268975212</v>
+        <v>0.3176639268991371</v>
       </c>
       <c r="AL13" t="n">
-        <v>-621.8472626633337</v>
+        <v>-621.847262664136</v>
       </c>
       <c r="AM13" t="n">
-        <v>45.52697080804194</v>
+        <v>45.52697080838436</v>
       </c>
       <c r="AN13" t="n">
-        <v>-383.5122169170072</v>
+        <v>-383.512216917914</v>
       </c>
       <c r="AO13" t="n">
-        <v>-28.44961730178392</v>
+        <v>-28.44961730194387</v>
       </c>
       <c r="AP13" t="n">
-        <v>-159.8323268183962</v>
+        <v>-159.8323268187096</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.3176639268975212</v>
+        <v>-0.3176639268991371</v>
       </c>
       <c r="AR13" t="n">
-        <v>-787.1466982470427</v>
+        <v>-787.1466982481188</v>
       </c>
       <c r="AS13" t="n">
-        <v>125.1707330026616</v>
+        <v>125.1707330032788</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0006447200771039496</v>
+        <v>0.0006447200771059376</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001074533461839916</v>
+        <v>0.0001074533461843229</v>
       </c>
       <c r="H14" t="n">
-        <v>101.865772182424</v>
+        <v>101.8657721827381</v>
       </c>
       <c r="I14" t="n">
-        <v>21490.66923679832</v>
+        <v>21490.66923686459</v>
       </c>
       <c r="J14" t="n">
-        <v>12.10067564645607</v>
+        <v>12.10067564647184</v>
       </c>
       <c r="K14" t="n">
-        <v>0.855601378201386</v>
+        <v>0.8556013782045796</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01645310419378794</v>
+        <v>0.0164531041938184</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.02662802448650984</v>
+        <v>-0.02662802448665153</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3041205539613382</v>
+        <v>0.3041205539618769</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2765021643922128</v>
+        <v>-0.2765021643933779</v>
       </c>
       <c r="P14" t="n">
-        <v>13.74971682084649</v>
+        <v>13.74971682086599</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.983163243548322</v>
+        <v>0.9831632435523956</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01709782427089189</v>
+        <v>0.01709782427092434</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.009077683545820888</v>
+        <v>-0.009077683545891</v>
       </c>
       <c r="T14" t="n">
-        <v>0.128253174079973</v>
+        <v>0.1282531740802902</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2961131962401839</v>
+        <v>-0.29611319624158</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01645310419378794</v>
+        <v>0.0164531041938184</v>
       </c>
       <c r="W14" t="n">
-        <v>0.855601378201386</v>
+        <v>0.8556013782045796</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.10067564645607</v>
+        <v>-12.10067564647184</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.2765021643922128</v>
+        <v>-0.2765021643933779</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.3041205539613382</v>
+        <v>0.3041205539618769</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.02662802448650984</v>
+        <v>0.02662802448665153</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.01709782427089189</v>
+        <v>0.01709782427092434</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.983163243548322</v>
+        <v>0.9831632435523956</v>
       </c>
       <c r="AD14" t="n">
-        <v>-13.74971682084649</v>
+        <v>-13.74971682086599</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.2961131962401839</v>
+        <v>-0.29611319624158</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.128253174079973</v>
+        <v>0.1282531740802902</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.009077683545820888</v>
+        <v>0.009077683545891</v>
       </c>
       <c r="AH14" t="n">
-        <v>-101.8657721824238</v>
+        <v>-101.8657721827385</v>
       </c>
       <c r="AI14" t="n">
-        <v>-5.043036174986128</v>
+        <v>-5.043036175046467</v>
       </c>
       <c r="AJ14" t="n">
-        <v>86.80693093240026</v>
+        <v>86.80693093268656</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.05581601372114864</v>
+        <v>0.05581601372180611</v>
       </c>
       <c r="AL14" t="n">
-        <v>-130.2789316849898</v>
+        <v>-130.2789316856852</v>
       </c>
       <c r="AM14" t="n">
-        <v>-2.14185622884861</v>
+        <v>-2.141856228976621</v>
       </c>
       <c r="AN14" t="n">
-        <v>101.8657721824238</v>
+        <v>101.8657721827385</v>
       </c>
       <c r="AO14" t="n">
-        <v>5.043036174986128</v>
+        <v>5.043036175046467</v>
       </c>
       <c r="AP14" t="n">
-        <v>-86.80693093240026</v>
+        <v>-86.80693093268656</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.05581601372114864</v>
+        <v>-0.05581601372180611</v>
       </c>
       <c r="AR14" t="n">
-        <v>-390.5626539094091</v>
+        <v>-390.5626539104323</v>
       </c>
       <c r="AS14" t="n">
-        <v>-28.11636082106827</v>
+        <v>-28.11636082130212</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0005432565124276027</v>
+        <v>0.0005432565124295595</v>
       </c>
       <c r="G15" t="n">
-        <v>9.054275207126712e-05</v>
+        <v>9.054275207159325e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>85.83452896356123</v>
+        <v>85.8345289638704</v>
       </c>
       <c r="I15" t="n">
-        <v>18108.55041425342</v>
+        <v>18108.55041431865</v>
       </c>
       <c r="J15" t="n">
-        <v>14.61043109294954</v>
+        <v>14.61043109297521</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8554961959361138</v>
+        <v>0.8554961959393073</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01137182782094663</v>
+        <v>0.01137182782097141</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.02661478979054551</v>
+        <v>-0.02661478979068704</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3475225990409564</v>
+        <v>0.3475225990419422</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3064720755180301</v>
+        <v>-0.306472075519195</v>
       </c>
       <c r="P15" t="n">
-        <v>16.28729671562621</v>
+        <v>16.28729671565749</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9830577539201565</v>
+        <v>0.9830577539242298</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01191508433337423</v>
+        <v>0.01191508433340097</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.00908168820024597</v>
+        <v>-0.009081688200316467</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1184927986803802</v>
+        <v>0.1184927986808056</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3261226386362977</v>
+        <v>-0.3261226386376945</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01137182782094663</v>
+        <v>0.01137182782097141</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8554961959361138</v>
+        <v>0.8554961959393073</v>
       </c>
       <c r="X15" t="n">
-        <v>-14.61043109294954</v>
+        <v>-14.61043109297521</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.3064720755180301</v>
+        <v>-0.306472075519195</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.3475225990409564</v>
+        <v>0.3475225990419422</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.02661478979054551</v>
+        <v>0.02661478979068704</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.01191508433337423</v>
+        <v>0.01191508433340097</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9830577539201565</v>
+        <v>0.9830577539242298</v>
       </c>
       <c r="AD15" t="n">
-        <v>-16.28729671562621</v>
+        <v>-16.28729671565749</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.3261226386362977</v>
+        <v>-0.3261226386376945</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1184927986803802</v>
+        <v>0.1184927986808056</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.00908168820024597</v>
+        <v>0.009081688200316467</v>
       </c>
       <c r="AH15" t="n">
-        <v>-85.8345289635613</v>
+        <v>-85.8345289638703</v>
       </c>
       <c r="AI15" t="n">
-        <v>-5.049790589544841</v>
+        <v>-5.049790589604982</v>
       </c>
       <c r="AJ15" t="n">
-        <v>68.77545927978912</v>
+        <v>68.77545928012933</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.05592852579814611</v>
+        <v>0.05592852579880625</v>
       </c>
       <c r="AL15" t="n">
-        <v>-36.84432557254138</v>
+        <v>-36.84432557314722</v>
       </c>
       <c r="AM15" t="n">
-        <v>-2.174876591812904</v>
+        <v>-2.174876591940688</v>
       </c>
       <c r="AN15" t="n">
-        <v>85.8345289635613</v>
+        <v>85.8345289638703</v>
       </c>
       <c r="AO15" t="n">
-        <v>5.049790589544841</v>
+        <v>5.049790589604982</v>
       </c>
       <c r="AP15" t="n">
-        <v>-68.77545927978912</v>
+        <v>-68.77545928012933</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.05592852579814611</v>
+        <v>-0.05592852579880625</v>
       </c>
       <c r="AR15" t="n">
-        <v>-375.8084301061951</v>
+        <v>-375.8084301076287</v>
       </c>
       <c r="AS15" t="n">
-        <v>-28.12386694545614</v>
+        <v>-28.12386694568909</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005350612470906464</v>
+        <v>-0.0005350612470926223</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.917687451510774e-05</v>
+        <v>-8.917687451543705e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>-84.53967704032213</v>
+        <v>-84.53967704063432</v>
       </c>
       <c r="I16" t="n">
-        <v>-17835.37490302155</v>
+        <v>-17835.37490308741</v>
       </c>
       <c r="J16" t="n">
-        <v>14.61196774737462</v>
+        <v>14.61196774740029</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.299417015686306</v>
+        <v>-1.29941701569186</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01139498107312069</v>
+        <v>-0.01139498107314529</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03319060518208777</v>
+        <v>0.03319060518225687</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3182393817608644</v>
+        <v>0.31823938176172</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.246574457134591</v>
+        <v>-0.2465744571357565</v>
       </c>
       <c r="P16" t="n">
-        <v>16.28791981014785</v>
+        <v>16.28791981017913</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.457257327504276</v>
+        <v>-1.457257327510761</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.01193004232021133</v>
+        <v>-0.01193004232023791</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01134630288189326</v>
+        <v>0.0113463028819652</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1105412483358429</v>
+        <v>0.1105412483363123</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2660564792319032</v>
+        <v>-0.2660564792332996</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.01139498107312069</v>
+        <v>-0.01139498107314529</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.299417015686306</v>
+        <v>-1.29941701569186</v>
       </c>
       <c r="X16" t="n">
-        <v>-14.61196774737462</v>
+        <v>-14.61196774740029</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.246574457134591</v>
+        <v>-0.2465744571357565</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.3182393817608644</v>
+        <v>0.31823938176172</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.03319060518208777</v>
+        <v>-0.03319060518225687</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.01193004232021133</v>
+        <v>-0.01193004232023791</v>
       </c>
       <c r="AC16" t="n">
-        <v>-1.457257327504276</v>
+        <v>-1.457257327510761</v>
       </c>
       <c r="AD16" t="n">
-        <v>-16.28791981014785</v>
+        <v>-16.28791981017913</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.2660564792319032</v>
+        <v>-0.2660564792332996</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1105412483358429</v>
+        <v>0.1105412483363123</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.01134630288189326</v>
+        <v>-0.0113463028819652</v>
       </c>
       <c r="AH16" t="n">
-        <v>84.5396770403222</v>
+        <v>84.53967704063439</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.976631614420171</v>
+        <v>5.976631614471387</v>
       </c>
       <c r="AJ16" t="n">
-        <v>171.1038425458343</v>
+        <v>171.1038425462361</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.05544883212311946</v>
+        <v>0.05544883212377627</v>
       </c>
       <c r="AL16" t="n">
-        <v>-209.6149089029861</v>
+        <v>-209.6149089039063</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.765111141116449</v>
+        <v>1.765111141198304</v>
       </c>
       <c r="AN16" t="n">
-        <v>-84.5396770403222</v>
+        <v>-84.53967704063439</v>
       </c>
       <c r="AO16" t="n">
-        <v>-5.976631614420171</v>
+        <v>-5.976631614471387</v>
       </c>
       <c r="AP16" t="n">
-        <v>-21.10384254583424</v>
+        <v>-21.10384254623614</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.05544883212311946</v>
+        <v>-0.05544883212377627</v>
       </c>
       <c r="AR16" t="n">
-        <v>-367.0081463720166</v>
+        <v>-367.0081463735096</v>
       </c>
       <c r="AS16" t="n">
-        <v>34.09467854540435</v>
+        <v>34.0946785456299</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0006529153424409059</v>
+        <v>-0.00065291534244288</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.000108819223740151</v>
+        <v>-0.00010881922374048</v>
       </c>
       <c r="H17" t="n">
-        <v>-103.1606241056631</v>
+        <v>-103.160624105975</v>
       </c>
       <c r="I17" t="n">
-        <v>-21763.84474803019</v>
+        <v>-21763.844748096</v>
       </c>
       <c r="J17" t="n">
-        <v>12.10178926074621</v>
+        <v>12.10178926076199</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.299472671285667</v>
+        <v>-1.29947267129122</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01642995094161392</v>
+        <v>-0.01642995094164457</v>
       </c>
       <c r="M17" t="n">
-        <v>0.03715388464293796</v>
+        <v>0.03715388464313682</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3085318025519207</v>
+        <v>0.3085318025524598</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3365693165703608</v>
+        <v>-0.3365693165715262</v>
       </c>
       <c r="P17" t="n">
-        <v>13.75040665788783</v>
+        <v>13.75040665790733</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.45737063857569</v>
+        <v>-1.457370638582175</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.01708286628405483</v>
+        <v>-0.01708286628408745</v>
       </c>
       <c r="S17" t="n">
-        <v>0.009916345241901936</v>
+        <v>0.009916345241963179</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1081508876107066</v>
+        <v>0.1081508876110224</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3561669580448221</v>
+        <v>-0.3561669580462182</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.01642995094161392</v>
+        <v>-0.01642995094164457</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.299472671285667</v>
+        <v>-1.29947267129122</v>
       </c>
       <c r="X17" t="n">
-        <v>-12.10178926074621</v>
+        <v>-12.10178926076199</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.3365693165703608</v>
+        <v>-0.3365693165715262</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.3085318025519207</v>
+        <v>0.3085318025524598</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.03715388464293796</v>
+        <v>-0.03715388464313682</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.01708286628405483</v>
+        <v>-0.01708286628408745</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.45737063857569</v>
+        <v>-1.457370638582175</v>
       </c>
       <c r="AD17" t="n">
-        <v>-13.75040665788783</v>
+        <v>-13.75040665790733</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.3561669580448221</v>
+        <v>-0.3561669580462182</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1081508876107066</v>
+        <v>0.1081508876110224</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.009916345241901936</v>
+        <v>-0.009916345241963179</v>
       </c>
       <c r="AH17" t="n">
-        <v>103.1606241056634</v>
+        <v>103.1606241059749</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.116195150090789</v>
+        <v>4.116195150128135</v>
       </c>
       <c r="AJ17" t="n">
-        <v>173.3137672412556</v>
+        <v>173.3137672415419</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.05577790265808225</v>
+        <v>0.05577790265873905</v>
       </c>
       <c r="AL17" t="n">
-        <v>-221.6594246672689</v>
+        <v>-221.6594246679597</v>
       </c>
       <c r="AM17" t="n">
-        <v>-7.807193706494331</v>
+        <v>-7.807193706483986</v>
       </c>
       <c r="AN17" t="n">
-        <v>-103.1606241056634</v>
+        <v>-103.1606241059749</v>
       </c>
       <c r="AO17" t="n">
-        <v>-4.116195150090789</v>
+        <v>-4.116195150128135</v>
       </c>
       <c r="AP17" t="n">
-        <v>-23.3137672412556</v>
+        <v>-23.31376724154188</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.05577790265808225</v>
+        <v>-0.05577790265873905</v>
       </c>
       <c r="AR17" t="n">
-        <v>-368.2231787802656</v>
+        <v>-368.2231787812889</v>
       </c>
       <c r="AS17" t="n">
-        <v>32.50436460703907</v>
+        <v>32.50436460725291</v>
       </c>
     </row>
     <row r="18">
@@ -6227,112 +6227,112 @@
         <v>-2639.351957915703</v>
       </c>
       <c r="J18" t="n">
-        <v>3.757925951552276</v>
+        <v>3.757925951556457</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1624422723417782</v>
+        <v>0.1624422723423497</v>
       </c>
       <c r="L18" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.03630395006709138</v>
+        <v>-0.03630395006721086</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6098064904006163</v>
+        <v>0.609806490401359</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.005111413036164057</v>
+        <v>-0.005111413036285996</v>
       </c>
       <c r="P18" t="n">
-        <v>3.723395957223965</v>
+        <v>3.723395957228697</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1623366982634615</v>
+        <v>0.162336698264033</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.03628902410958178</v>
+        <v>-0.03628902410970122</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6753566419530859</v>
+        <v>0.6753566419540323</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.03509421220928596</v>
+        <v>-0.03509421220940796</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1624422723417782</v>
+        <v>0.1624422723423497</v>
       </c>
       <c r="W18" t="n">
-        <v>-3.757925951552276</v>
+        <v>-3.757925951556457</v>
       </c>
       <c r="X18" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.6098064904006163</v>
+        <v>0.609806490401359</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.03630395006709138</v>
+        <v>0.03630395006721086</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.005111413036164057</v>
+        <v>-0.005111413036285996</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.1623366982634615</v>
+        <v>0.162336698264033</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.723395957223965</v>
+        <v>-3.723395957228697</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.6753566419530859</v>
+        <v>0.6753566419540323</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.03628902410958178</v>
+        <v>0.03628902410970122</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.03509421220928596</v>
+        <v>-0.03509421220940796</v>
       </c>
       <c r="AH18" t="n">
         <v>12.51052828051979</v>
       </c>
       <c r="AI18" t="n">
-        <v>-20.32886904320844</v>
+        <v>-20.32886904325267</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-29.95136551373676</v>
+        <v>-29.95136551383587</v>
       </c>
       <c r="AK18" t="n">
-        <v>-0.1399243619677715</v>
+        <v>-0.1399243619682065</v>
       </c>
       <c r="AL18" t="n">
-        <v>119.8137459613649</v>
+        <v>119.8137459617613</v>
       </c>
       <c r="AM18" t="n">
-        <v>-64.67502263175106</v>
+        <v>-64.67502263192773</v>
       </c>
       <c r="AN18" t="n">
         <v>-12.51052828051979</v>
       </c>
       <c r="AO18" t="n">
-        <v>20.32886904320844</v>
+        <v>20.32886904325267</v>
       </c>
       <c r="AP18" t="n">
-        <v>29.95136551373676</v>
+        <v>29.95136551383587</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.1399243619677715</v>
+        <v>0.1399243619682065</v>
       </c>
       <c r="AR18" t="n">
-        <v>119.7971781485292</v>
+        <v>119.7971781489256</v>
       </c>
       <c r="AS18" t="n">
-        <v>-97.95592971391648</v>
+        <v>-97.95592971409337</v>
       </c>
     </row>
     <row r="19">
@@ -6354,124 +6354,124 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0001740734582367232</v>
+        <v>-0.0001740734582384995</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.175918227959039e-05</v>
+        <v>-2.175918227981244e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-20.62770480105169</v>
+        <v>-20.62770480126219</v>
       </c>
       <c r="I19" t="n">
-        <v>-4351.836455918078</v>
+        <v>-4351.836455962487</v>
       </c>
       <c r="J19" t="n">
-        <v>3.723395957223965</v>
+        <v>3.723395957228697</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1623366982634615</v>
+        <v>0.162336698264033</v>
       </c>
       <c r="L19" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.03628902410958178</v>
+        <v>-0.03628902410970122</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6753566419530859</v>
+        <v>0.6753566419540323</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.03509421220928596</v>
+        <v>-0.03509421220940796</v>
       </c>
       <c r="P19" t="n">
-        <v>3.723221883765729</v>
+        <v>3.723221883770459</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1923970678416461</v>
+        <v>-0.1923970678424733</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="S19" t="n">
-        <v>0.04214837918573356</v>
+        <v>0.04214837918590374</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5925544959336078</v>
+        <v>0.5925544959344536</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0251422011951866</v>
+        <v>0.0251422011950651</v>
       </c>
       <c r="V19" t="n">
-        <v>3.723395957223965</v>
+        <v>3.723395957228697</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1623366982634615</v>
+        <v>0.162336698264033</v>
       </c>
       <c r="X19" t="n">
-        <v>0.006184562735762412</v>
+        <v>0.006184562735773826</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.03628902410958178</v>
+        <v>-0.03628902410970122</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.6753566419530859</v>
+        <v>0.6753566419540323</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.03509421220928596</v>
+        <v>-0.03509421220940796</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.723221883765729</v>
+        <v>3.723221883770459</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.1923970678416461</v>
+        <v>-0.1923970678424733</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.04214837918573356</v>
+        <v>0.04214837918590374</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5925544959336078</v>
+        <v>0.5925544959344536</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.0251422011951866</v>
+        <v>0.0251422011950651</v>
       </c>
       <c r="AH19" t="n">
-        <v>20.62770480103791</v>
+        <v>20.62770480127074</v>
       </c>
       <c r="AI19" t="n">
-        <v>32.77195795069392</v>
+        <v>32.77195795073811</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-526.4796256065976</v>
+        <v>-526.4796256073413</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.1674336878034616</v>
+        <v>-0.1674336878040798</v>
       </c>
       <c r="AL19" t="n">
-        <v>2151.8736934672</v>
+        <v>2151.873693470231</v>
       </c>
       <c r="AM19" t="n">
-        <v>97.65662236329339</v>
+        <v>97.65662236346988</v>
       </c>
       <c r="AN19" t="n">
-        <v>-20.62770480103791</v>
+        <v>-20.62770480127074</v>
       </c>
       <c r="AO19" t="n">
-        <v>-32.77195795069392</v>
+        <v>-32.77195795073811</v>
       </c>
       <c r="AP19" t="n">
-        <v>526.4796256065976</v>
+        <v>526.4796256073413</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.1674336878034616</v>
+        <v>0.1674336878040798</v>
       </c>
       <c r="AR19" t="n">
-        <v>2059.96331138558</v>
+        <v>2059.963311388499</v>
       </c>
       <c r="AS19" t="n">
-        <v>164.5190412422579</v>
+        <v>164.519041242435</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0002293761867009914</v>
+        <v>0.0002293761867013244</v>
       </c>
       <c r="G20" t="n">
-        <v>2.867202333762392e-05</v>
+        <v>2.867202333766555e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>27.18107812406748</v>
+        <v>27.18107812410694</v>
       </c>
       <c r="I20" t="n">
-        <v>5734.404667524784</v>
+        <v>5734.40466753311</v>
       </c>
       <c r="J20" t="n">
-        <v>3.723221883765729</v>
+        <v>3.723221883770459</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1923970678416461</v>
+        <v>-0.1923970678424733</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="M20" t="n">
-        <v>0.04214837918573356</v>
+        <v>0.04214837918590374</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5925544959336078</v>
+        <v>0.5925544959344536</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0251422011951866</v>
+        <v>0.0251422011950651</v>
       </c>
       <c r="P20" t="n">
-        <v>3.758983147792192</v>
+        <v>3.758983147796373</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1926264440283471</v>
+        <v>-0.1926264440291746</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="S20" t="n">
-        <v>0.05052610874595759</v>
+        <v>0.05052610874615139</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6101246851582274</v>
+        <v>0.6101246851589696</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06503362791338377</v>
+        <v>-0.06503362791350591</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1923970678416461</v>
+        <v>0.1923970678424733</v>
       </c>
       <c r="W20" t="n">
-        <v>3.723221883765729</v>
+        <v>3.723221883770459</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.006196319318183139</v>
+        <v>-0.006196319318194401</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.5925544959336078</v>
+        <v>-0.5925544959344536</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.04214837918573356</v>
+        <v>0.04214837918590374</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.0251422011951866</v>
+        <v>0.0251422011950651</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1926264440283471</v>
+        <v>0.1926264440291746</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.758983147792192</v>
+        <v>3.758983147796373</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.6101246851582274</v>
+        <v>-0.6101246851589696</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.05052610874595759</v>
+        <v>0.05052610874615139</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.06503362791338377</v>
+        <v>-0.06503362791350591</v>
       </c>
       <c r="AH20" t="n">
-        <v>-27.18107812406743</v>
+        <v>-27.18107812410744</v>
       </c>
       <c r="AI20" t="n">
-        <v>-120.3262129092034</v>
+        <v>-120.3262129092477</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-38.31274245297931</v>
+        <v>-38.31274245313044</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.03750559622947636</v>
+        <v>0.0375055962292552</v>
       </c>
       <c r="AL20" t="n">
-        <v>148.6013299059929</v>
+        <v>148.6013299065843</v>
       </c>
       <c r="AM20" t="n">
-        <v>-164.5905998148902</v>
+        <v>-164.5905998150671</v>
       </c>
       <c r="AN20" t="n">
-        <v>27.18107812406743</v>
+        <v>27.18107812410744</v>
       </c>
       <c r="AO20" t="n">
-        <v>-79.67378709079662</v>
+        <v>-79.67378709075228</v>
       </c>
       <c r="AP20" t="n">
-        <v>38.31274245297931</v>
+        <v>38.31274245313044</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.03750559622947636</v>
+        <v>-0.0375055962292552</v>
       </c>
       <c r="AR20" t="n">
-        <v>157.9006097178416</v>
+        <v>157.9006097184592</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.980896541263149</v>
+        <v>1.980896541085798</v>
       </c>
     </row>
     <row r="21">
@@ -6644,112 +6644,112 @@
         <v>26429.90599789341</v>
       </c>
       <c r="J21" t="n">
-        <v>3.758983147792192</v>
+        <v>3.758983147796373</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1926264440283471</v>
+        <v>-0.1926264440291746</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.008723772998299724</v>
+        <v>-0.008723772998314602</v>
       </c>
       <c r="M21" t="n">
-        <v>0.05052610874595759</v>
+        <v>0.05052610874615139</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6101246851582274</v>
+        <v>0.6101246851589696</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.06503362791338377</v>
+        <v>-0.06503362791350591</v>
       </c>
       <c r="P21" t="n">
-        <v>3.757925951552276</v>
+        <v>3.757925951556457</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1624422723417782</v>
+        <v>0.1624422723423497</v>
       </c>
       <c r="R21" t="n">
-        <v>0.008735529580720434</v>
+        <v>0.008735529580735151</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.03630395006709138</v>
+        <v>-0.03630395006721086</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6098064904006163</v>
+        <v>0.609806490401359</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.005111413036164057</v>
+        <v>-0.005111413036285996</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.758983147792192</v>
+        <v>-3.758983147796373</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1926264440283471</v>
+        <v>-0.1926264440291746</v>
       </c>
       <c r="X21" t="n">
-        <v>0.008723772998299724</v>
+        <v>0.008723772998314602</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.05052610874595759</v>
+        <v>-0.05052610874615139</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.6101246851582274</v>
+        <v>0.6101246851589696</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.06503362791338377</v>
+        <v>0.06503362791350591</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.757925951552276</v>
+        <v>-3.757925951556457</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.1624422723417782</v>
+        <v>0.1624422723423497</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.008735529580720434</v>
+        <v>-0.008735529580735151</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.03630395006709138</v>
+        <v>0.03630395006721086</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.6098064904006163</v>
+        <v>0.609806490401359</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.005111413036164057</v>
+        <v>0.005111413036285996</v>
       </c>
       <c r="AH21" t="n">
         <v>-125.2777544300188</v>
       </c>
       <c r="AI21" t="n">
-        <v>-7.751465002016882</v>
+        <v>-7.751465002060866</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-505.9794931517395</v>
+        <v>-505.9794931523545</v>
       </c>
       <c r="AK21" t="n">
-        <v>-0.185348779389393</v>
+        <v>-0.1853487793900617</v>
       </c>
       <c r="AL21" t="n">
-        <v>2024.094570697432</v>
+        <v>2024.094570699891</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.250969248789389</v>
+        <v>2.250969248613565</v>
       </c>
       <c r="AN21" t="n">
         <v>125.2777544300188</v>
       </c>
       <c r="AO21" t="n">
-        <v>7.751465002016882</v>
+        <v>7.751465002060866</v>
       </c>
       <c r="AP21" t="n">
-        <v>505.9794931517395</v>
+        <v>505.9794931523545</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.185348779389393</v>
+        <v>0.1853487793900617</v>
       </c>
       <c r="AR21" t="n">
-        <v>2023.741374516484</v>
+        <v>2023.741374518944</v>
       </c>
       <c r="AS21" t="n">
-        <v>-64.26268926492449</v>
+        <v>-64.26268926510053</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.115239550292696e-05</v>
+        <v>-7.115239550303798e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.89404943786587e-06</v>
+        <v>-8.894049437879747e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.431558867096845</v>
+        <v>-8.431558867110001</v>
       </c>
       <c r="I22" t="n">
-        <v>-1778.809887573174</v>
+        <v>-1778.809887575949</v>
       </c>
       <c r="J22" t="n">
-        <v>8.658378534736178</v>
+        <v>8.658378534746893</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5437220967391151</v>
+        <v>0.5437220967409437</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01407909170153279</v>
+        <v>0.01407909170155771</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.04556477868176344</v>
+        <v>-0.04556477868193153</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5226650286341942</v>
+        <v>0.522665028634919</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1550967117141002</v>
+        <v>-0.1550967117146793</v>
       </c>
       <c r="P22" t="n">
-        <v>10.03693211708712</v>
+        <v>10.03693211710211</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.5436509443436122</v>
+        <v>0.5436509443454407</v>
       </c>
       <c r="R22" t="n">
-        <v>0.009226541546886466</v>
+        <v>0.009226541546905213</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.04561220557379464</v>
+        <v>-0.04561220557396294</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8629762354412365</v>
+        <v>0.8629762354429026</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1753504665291883</v>
+        <v>-0.1753504665297493</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5437220967391151</v>
+        <v>0.5437220967409437</v>
       </c>
       <c r="W22" t="n">
-        <v>-8.658378534736178</v>
+        <v>-8.658378534746893</v>
       </c>
       <c r="X22" t="n">
-        <v>0.01407909170153279</v>
+        <v>0.01407909170155771</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5226650286341942</v>
+        <v>0.522665028634919</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.04556477868176344</v>
+        <v>0.04556477868193153</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.1550967117141002</v>
+        <v>-0.1550967117146793</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.5436509443436122</v>
+        <v>0.5436509443454407</v>
       </c>
       <c r="AC22" t="n">
-        <v>-10.03693211708712</v>
+        <v>-10.03693211710211</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.009226541546886466</v>
+        <v>0.009226541546905213</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.8629762354412365</v>
+        <v>0.8629762354429026</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.04561220557379464</v>
+        <v>0.04561220557396294</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.1753504665291883</v>
+        <v>-0.1753504665297493</v>
       </c>
       <c r="AH22" t="n">
-        <v>8.431558867094282</v>
+        <v>8.431558867116109</v>
       </c>
       <c r="AI22" t="n">
-        <v>5.907094219625492</v>
+        <v>5.907094219596843</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-37.44745119590817</v>
+        <v>-37.44745119604755</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.7264335376073403</v>
+        <v>-0.7264335376093496</v>
       </c>
       <c r="AL22" t="n">
-        <v>149.7634828585553</v>
+        <v>149.7634828591127</v>
       </c>
       <c r="AM22" t="n">
-        <v>34.86921080087586</v>
+        <v>34.86921080075126</v>
       </c>
       <c r="AN22" t="n">
-        <v>-8.431558867094282</v>
+        <v>-8.431558867116109</v>
       </c>
       <c r="AO22" t="n">
-        <v>-5.907094219625492</v>
+        <v>-5.907094219596843</v>
       </c>
       <c r="AP22" t="n">
-        <v>37.44745119590817</v>
+        <v>37.44745119604755</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.7264335376073403</v>
+        <v>0.7264335376093496</v>
       </c>
       <c r="AR22" t="n">
-        <v>149.81612670871</v>
+        <v>149.8161267092676</v>
       </c>
       <c r="AS22" t="n">
-        <v>12.38754295612807</v>
+        <v>12.38754295602348</v>
       </c>
     </row>
     <row r="23">
@@ -6910,43 +6910,43 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00162463354023501</v>
+        <v>0.001624633540233233</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0002030791925293762</v>
+        <v>0.0002030791925291542</v>
       </c>
       <c r="H23" t="n">
-        <v>192.5190745178487</v>
+        <v>192.5190745176382</v>
       </c>
       <c r="I23" t="n">
-        <v>40615.83850587524</v>
+        <v>40615.83850583083</v>
       </c>
       <c r="J23" t="n">
-        <v>10.03693211708712</v>
+        <v>10.03693211710211</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5436509443436122</v>
+        <v>0.5436509443454407</v>
       </c>
       <c r="L23" t="n">
-        <v>0.009226541546886466</v>
+        <v>0.009226541546905213</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.04561220557379464</v>
+        <v>-0.04561220557396294</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8629762354412365</v>
+        <v>0.8629762354429026</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1753504665291883</v>
+        <v>-0.1753504665297493</v>
       </c>
       <c r="P23" t="n">
-        <v>10.03855675062735</v>
+        <v>10.03855675064235</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.7997579802013167</v>
+        <v>-0.7997579802044718</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.009302974818938313</v>
+        <v>-0.00930297481895709</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6958,31 +6958,31 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>10.03693211708712</v>
+        <v>10.03693211710211</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5436509443436122</v>
+        <v>0.5436509443454407</v>
       </c>
       <c r="X23" t="n">
-        <v>0.009226541546886466</v>
+        <v>0.009226541546905213</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.04561220557379464</v>
+        <v>-0.04561220557396294</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.8629762354412365</v>
+        <v>0.8629762354429026</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.1753504665291883</v>
+        <v>-0.1753504665297493</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.03855675062735</v>
+        <v>10.03855675064235</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.7997579802013167</v>
+        <v>-0.7997579802044718</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.009302974818938313</v>
+        <v>-0.00930297481895709</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -6994,40 +6994,40 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>-192.5190745177679</v>
+        <v>-192.519074517535</v>
       </c>
       <c r="AI23" t="n">
-        <v>66.80885951768202</v>
+        <v>66.80885951796712</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-357.2856302055961</v>
+        <v>-357.2856302062857</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.09736451574406163</v>
+        <v>-0.09736451574442088</v>
       </c>
       <c r="AL23" t="n">
-        <v>1908.094331492271</v>
+        <v>1908.094331495953</v>
       </c>
       <c r="AM23" t="n">
-        <v>169.9159291470286</v>
+        <v>169.9159291478577</v>
       </c>
       <c r="AN23" t="n">
-        <v>192.5190745177679</v>
+        <v>192.519074517535</v>
       </c>
       <c r="AO23" t="n">
-        <v>-66.80885951768202</v>
+        <v>-66.80885951796712</v>
       </c>
       <c r="AP23" t="n">
-        <v>357.2856302055961</v>
+        <v>357.2856302062857</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.09736451574406163</v>
+        <v>0.09736451574442088</v>
       </c>
       <c r="AR23" t="n">
-        <v>950.1907101524979</v>
+        <v>950.1907101543316</v>
       </c>
       <c r="AS23" t="n">
-        <v>364.5549469944276</v>
+        <v>364.5549469958794</v>
       </c>
     </row>
     <row r="24">
@@ -7049,25 +7049,25 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>1.503836553162774e-05</v>
+        <v>1.503836553151672e-05</v>
       </c>
       <c r="G24" t="n">
-        <v>1.879795691453467e-06</v>
+        <v>1.87979569143959e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>1.782046315497887</v>
+        <v>1.782046315484731</v>
       </c>
       <c r="I24" t="n">
-        <v>375.9591382906935</v>
+        <v>375.9591382879179</v>
       </c>
       <c r="J24" t="n">
-        <v>10.03855675062735</v>
+        <v>10.03855675064235</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7997579802013167</v>
+        <v>-0.7997579802044718</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.009302974818938313</v>
+        <v>-0.00930297481895709</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -7079,31 +7079,31 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>8.659455021339078</v>
+        <v>8.659455021349791</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.7997730185668483</v>
+        <v>-0.7997730185700033</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.01400265842948097</v>
+        <v>-0.01400265842950587</v>
       </c>
       <c r="S24" t="n">
-        <v>0.09096723747714046</v>
+        <v>0.0909672374775249</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5215719617301026</v>
+        <v>0.5215719617308274</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2249576665793398</v>
+        <v>-0.2249576665799374</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7997579802013167</v>
+        <v>0.7997579802044718</v>
       </c>
       <c r="W24" t="n">
-        <v>10.03855675062735</v>
+        <v>10.03855675064235</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.009302974818938313</v>
+        <v>-0.00930297481895709</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -7115,58 +7115,58 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.7997730185668483</v>
+        <v>0.7997730185700033</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.659455021339078</v>
+        <v>8.659455021349791</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.01400265842948097</v>
+        <v>-0.01400265842950587</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.5215719617301026</v>
+        <v>-0.5215719617308274</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.09096723747714046</v>
+        <v>0.0909672374775249</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.2249576665793398</v>
+        <v>-0.2249576665799374</v>
       </c>
       <c r="AH24" t="n">
         <v>-1.782046315493062</v>
       </c>
       <c r="AI24" t="n">
-        <v>-50.12585500958915</v>
+        <v>-50.12585500939213</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-37.37605177413763</v>
+        <v>-37.37605177429701</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.113355533693104</v>
+        <v>1.113355533694651</v>
       </c>
       <c r="AL24" t="n">
-        <v>99.01739029673753</v>
+        <v>99.01739029716171</v>
       </c>
       <c r="AM24" t="n">
-        <v>191.0147515798436</v>
+        <v>191.0147515809632</v>
       </c>
       <c r="AN24" t="n">
         <v>1.782046315493062</v>
       </c>
       <c r="AO24" t="n">
-        <v>-149.8741449904109</v>
+        <v>-149.8741449906079</v>
       </c>
       <c r="AP24" t="n">
-        <v>37.37605177413763</v>
+        <v>37.37605177429701</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-1.113355533693104</v>
+        <v>-1.113355533694651</v>
       </c>
       <c r="AR24" t="n">
-        <v>199.9910238963635</v>
+        <v>199.9910238972143</v>
       </c>
       <c r="AS24" t="n">
-        <v>207.9784083434427</v>
+        <v>207.9784083438993</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.001076486602899607</v>
+        <v>0.00107648660289783</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001345608253624508</v>
+        <v>0.0001345608253622288</v>
       </c>
       <c r="H25" t="n">
-        <v>127.5636624436034</v>
+        <v>127.5636624433929</v>
       </c>
       <c r="I25" t="n">
-        <v>26912.16507249017</v>
+        <v>26912.16507244576</v>
       </c>
       <c r="J25" t="n">
-        <v>8.659455021339078</v>
+        <v>8.659455021349791</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7997730185668483</v>
+        <v>-0.7997730185700033</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.01400265842948097</v>
+        <v>-0.01400265842950587</v>
       </c>
       <c r="M25" t="n">
-        <v>0.09096723747714046</v>
+        <v>0.0909672374775249</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5215719617301026</v>
+        <v>0.5215719617308274</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2249576665793398</v>
+        <v>-0.2249576665799374</v>
       </c>
       <c r="P25" t="n">
-        <v>8.658378534736178</v>
+        <v>8.658378534746893</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5437220967391151</v>
+        <v>0.5437220967409437</v>
       </c>
       <c r="R25" t="n">
-        <v>0.01407909170153279</v>
+        <v>0.01407909170155771</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.04556477868176344</v>
+        <v>-0.04556477868193153</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5226650286341942</v>
+        <v>0.522665028634919</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1550967117141002</v>
+        <v>-0.1550967117146793</v>
       </c>
       <c r="V25" t="n">
-        <v>-8.659455021339078</v>
+        <v>-8.659455021349791</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.7997730185668483</v>
+        <v>-0.7997730185700033</v>
       </c>
       <c r="X25" t="n">
-        <v>0.01400265842948097</v>
+        <v>0.01400265842950587</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.09096723747714046</v>
+        <v>-0.0909672374775249</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.5215719617301026</v>
+        <v>0.5215719617308274</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.2249576665793398</v>
+        <v>0.2249576665799374</v>
       </c>
       <c r="AB25" t="n">
-        <v>-8.658378534736178</v>
+        <v>-8.658378534746893</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.5437220967391151</v>
+        <v>0.5437220967409437</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.01407909170153279</v>
+        <v>-0.01407909170155771</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.04556477868176344</v>
+        <v>0.04556477868193153</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.5226650286341942</v>
+        <v>0.522665028634919</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.1550967117141002</v>
+        <v>0.1550967117146793</v>
       </c>
       <c r="AH25" t="n">
-        <v>-127.5636624436593</v>
+        <v>-127.5636624434264</v>
       </c>
       <c r="AI25" t="n">
-        <v>18.3901745281176</v>
+        <v>18.39017452808879</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-431.74139011613</v>
+        <v>-431.7413901167282</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.2914433421853525</v>
+        <v>-0.291443342186532</v>
       </c>
       <c r="AL25" t="n">
-        <v>1726.358908332749</v>
+        <v>1726.358908335142</v>
       </c>
       <c r="AM25" t="n">
-        <v>112.3335280626782</v>
+        <v>112.3335280625733</v>
       </c>
       <c r="AN25" t="n">
-        <v>127.5636624436593</v>
+        <v>127.5636624434264</v>
       </c>
       <c r="AO25" t="n">
-        <v>-18.3901745281176</v>
+        <v>-18.39017452808879</v>
       </c>
       <c r="AP25" t="n">
-        <v>431.74139011613</v>
+        <v>431.7413901167282</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.2914433421853525</v>
+        <v>0.291443342186532</v>
       </c>
       <c r="AR25" t="n">
-        <v>1727.57221259629</v>
+        <v>1727.572212598684</v>
       </c>
       <c r="AS25" t="n">
-        <v>34.78786816226227</v>
+        <v>34.78786816213679</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0001051822652722301</v>
+        <v>-0.0001051822652723411</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.314778315902876e-05</v>
+        <v>-1.314778315904264e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.46409843475926</v>
+        <v>-12.46409843477242</v>
       </c>
       <c r="I26" t="n">
-        <v>-2629.556631805752</v>
+        <v>-2629.556631808527</v>
       </c>
       <c r="J26" t="n">
-        <v>12.10067564645607</v>
+        <v>12.10067564647184</v>
       </c>
       <c r="K26" t="n">
-        <v>0.855601378201386</v>
+        <v>0.8556013782045796</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01645310419378794</v>
+        <v>0.0164531041938184</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.02662802448650984</v>
+        <v>-0.02662802448665153</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3041205539613382</v>
+        <v>0.3041205539618769</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2765021643922128</v>
+        <v>-0.2765021643933779</v>
       </c>
       <c r="P26" t="n">
-        <v>14.61043109294954</v>
+        <v>14.61043109297521</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8554961959361138</v>
+        <v>0.8554961959393073</v>
       </c>
       <c r="R26" t="n">
-        <v>0.01137182782094663</v>
+        <v>0.01137182782097141</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.02661478979054551</v>
+        <v>-0.02661478979068704</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3475225990409564</v>
+        <v>0.3475225990419422</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3064720755180301</v>
+        <v>-0.306472075519195</v>
       </c>
       <c r="V26" t="n">
-        <v>0.855601378201386</v>
+        <v>0.8556013782045796</v>
       </c>
       <c r="W26" t="n">
-        <v>-12.10067564645607</v>
+        <v>-12.10067564647184</v>
       </c>
       <c r="X26" t="n">
-        <v>0.01645310419378794</v>
+        <v>0.0164531041938184</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.3041205539613382</v>
+        <v>0.3041205539618769</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.02662802448650984</v>
+        <v>0.02662802448665153</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.2765021643922128</v>
+        <v>-0.2765021643933779</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.8554961959361138</v>
+        <v>0.8554961959393073</v>
       </c>
       <c r="AC26" t="n">
-        <v>-14.61043109294954</v>
+        <v>-14.61043109297521</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.01137182782094663</v>
+        <v>0.01137182782097141</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.3475225990409564</v>
+        <v>0.3475225990419422</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.02661478979054551</v>
+        <v>0.02661478979068704</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.3064720755180301</v>
+        <v>-0.306472075519195</v>
       </c>
       <c r="AH26" t="n">
-        <v>12.46409843476431</v>
+        <v>12.46409843477886</v>
       </c>
       <c r="AI26" t="n">
-        <v>18.50839878808893</v>
+        <v>18.50839878814895</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-21.63355112027549</v>
+        <v>-21.6335511203928</v>
       </c>
       <c r="AK26" t="n">
-        <v>-0.0926466731507235</v>
+        <v>-0.09264667315167774</v>
       </c>
       <c r="AL26" t="n">
-        <v>86.54154973736216</v>
+        <v>86.54154973783145</v>
       </c>
       <c r="AM26" t="n">
-        <v>90.66689582718391</v>
+        <v>90.66689582742492</v>
       </c>
       <c r="AN26" t="n">
-        <v>-12.46409843476431</v>
+        <v>-12.46409843477886</v>
       </c>
       <c r="AO26" t="n">
-        <v>-18.50839878808893</v>
+        <v>-18.50839878814895</v>
       </c>
       <c r="AP26" t="n">
-        <v>21.63355112027549</v>
+        <v>21.6335511203928</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.0926466731507235</v>
+        <v>0.09264667315167774</v>
       </c>
       <c r="AR26" t="n">
-        <v>86.52685922484176</v>
+        <v>86.52685922531087</v>
       </c>
       <c r="AS26" t="n">
-        <v>57.40029447752659</v>
+        <v>57.4002944777676</v>
       </c>
     </row>
     <row r="27">
@@ -7466,124 +7466,124 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>0.001536654425072115</v>
+        <v>0.001536654425073891</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0001920818031340144</v>
+        <v>0.0001920818031342364</v>
       </c>
       <c r="H27" t="n">
-        <v>182.0935493710456</v>
+        <v>182.0935493712561</v>
       </c>
       <c r="I27" t="n">
-        <v>38416.36062680287</v>
+        <v>38416.36062684728</v>
       </c>
       <c r="J27" t="n">
-        <v>14.61043109294954</v>
+        <v>14.61043109297521</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8554961959361138</v>
+        <v>0.8554961959393073</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01137182782094663</v>
+        <v>0.01137182782097141</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.02661478979054551</v>
+        <v>-0.02661478979068704</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3475225990409564</v>
+        <v>0.3475225990419422</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.3064720755180301</v>
+        <v>-0.306472075519195</v>
       </c>
       <c r="P27" t="n">
-        <v>14.61196774737462</v>
+        <v>14.61196774740029</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.299417015686306</v>
+        <v>-1.29941701569186</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.01139498107312069</v>
+        <v>-0.01139498107314529</v>
       </c>
       <c r="S27" t="n">
-        <v>0.03319060518208777</v>
+        <v>0.03319060518225687</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3182393817608644</v>
+        <v>0.31823938176172</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.246574457134591</v>
+        <v>-0.2465744571357565</v>
       </c>
       <c r="V27" t="n">
-        <v>14.61043109294954</v>
+        <v>14.61043109297521</v>
       </c>
       <c r="W27" t="n">
-        <v>0.8554961959361138</v>
+        <v>0.8554961959393073</v>
       </c>
       <c r="X27" t="n">
-        <v>0.01137182782094663</v>
+        <v>0.01137182782097141</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.02661478979054551</v>
+        <v>-0.02661478979068704</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.3475225990409564</v>
+        <v>0.3475225990419422</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.3064720755180301</v>
+        <v>-0.306472075519195</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.61196774737462</v>
+        <v>14.61196774740029</v>
       </c>
       <c r="AC27" t="n">
-        <v>-1.299417015686306</v>
+        <v>-1.29941701569186</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.01139498107312069</v>
+        <v>-0.01139498107314529</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.03319060518208777</v>
+        <v>0.03319060518225687</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.3182393817608644</v>
+        <v>0.31823938176172</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.246574457134591</v>
+        <v>-0.2465744571357565</v>
       </c>
       <c r="AH27" t="n">
-        <v>-182.0935493709985</v>
+        <v>-182.0935493712313</v>
       </c>
       <c r="AI27" t="n">
-        <v>-5.959963132195512</v>
+        <v>-5.959963132255233</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-274.7542534582191</v>
+        <v>-274.7542534589803</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.1276615161915826</v>
+        <v>-0.1276615161922457</v>
       </c>
       <c r="AL27" t="n">
-        <v>1115.269199423327</v>
+        <v>1115.269199426445</v>
       </c>
       <c r="AM27" t="n">
-        <v>-57.08303073159067</v>
+        <v>-57.08303073182913</v>
       </c>
       <c r="AN27" t="n">
-        <v>182.0935493709985</v>
+        <v>182.0935493712313</v>
       </c>
       <c r="AO27" t="n">
-        <v>5.959963132195512</v>
+        <v>5.959963132255233</v>
       </c>
       <c r="AP27" t="n">
-        <v>274.7542534582191</v>
+        <v>274.7542534589803</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.1276615161915826</v>
+        <v>0.1276615161922457</v>
       </c>
       <c r="AR27" t="n">
-        <v>1082.764828242425</v>
+        <v>1082.764828245398</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.403325674026803</v>
+        <v>9.403325673787522</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>5.565559936138165e-05</v>
+        <v>5.565559936049347e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>6.956949920172706e-06</v>
+        <v>6.956949920061684e-06</v>
       </c>
       <c r="H28" t="n">
-        <v>6.595188524323725</v>
+        <v>6.595188524218476</v>
       </c>
       <c r="I28" t="n">
-        <v>1391.389984034541</v>
+        <v>1391.389984012337</v>
       </c>
       <c r="J28" t="n">
-        <v>14.61196774737462</v>
+        <v>14.61196774740029</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.299417015686306</v>
+        <v>-1.29941701569186</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.01139498107312069</v>
+        <v>-0.01139498107314529</v>
       </c>
       <c r="M28" t="n">
-        <v>0.03319060518208777</v>
+        <v>0.03319060518225687</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3182393817608644</v>
+        <v>0.31823938176172</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.246574457134591</v>
+        <v>-0.2465744571357565</v>
       </c>
       <c r="P28" t="n">
-        <v>12.10178926074621</v>
+        <v>12.10178926076199</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.299472671285667</v>
+        <v>-1.29947267129122</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.01642995094161392</v>
+        <v>-0.01642995094164457</v>
       </c>
       <c r="S28" t="n">
-        <v>0.03715388464293796</v>
+        <v>0.03715388464313682</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3085318025519207</v>
+        <v>0.3085318025524598</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3365693165703608</v>
+        <v>-0.3365693165715262</v>
       </c>
       <c r="V28" t="n">
-        <v>1.299417015686306</v>
+        <v>1.29941701569186</v>
       </c>
       <c r="W28" t="n">
-        <v>14.61196774737462</v>
+        <v>14.61196774740029</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.01139498107312069</v>
+        <v>-0.01139498107314529</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.3182393817608644</v>
+        <v>-0.31823938176172</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.03319060518208777</v>
+        <v>0.03319060518225687</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.246574457134591</v>
+        <v>-0.2465744571357565</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.299472671285667</v>
+        <v>1.29947267129122</v>
       </c>
       <c r="AC28" t="n">
-        <v>12.10178926074621</v>
+        <v>12.10178926076199</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.01642995094161392</v>
+        <v>-0.01642995094164457</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.3085318025519207</v>
+        <v>-0.3085318025524598</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.03715388464293796</v>
+        <v>0.03715388464313682</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.3365693165703608</v>
+        <v>-0.3365693165715262</v>
       </c>
       <c r="AH28" t="n">
-        <v>-6.595188524341211</v>
+        <v>-6.595188524224795</v>
       </c>
       <c r="AI28" t="n">
-        <v>-81.51814703991795</v>
+        <v>-81.51814703985838</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-28.75694233772689</v>
+        <v>-28.75694233787942</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.0207219479267835</v>
+        <v>-0.02072194792745929</v>
       </c>
       <c r="AL28" t="n">
-        <v>112.8281492501357</v>
+        <v>112.8281492507293</v>
       </c>
       <c r="AM28" t="n">
-        <v>-9.458774506152935</v>
+        <v>-9.458774505914647</v>
       </c>
       <c r="AN28" t="n">
-        <v>6.595188524341211</v>
+        <v>6.595188524224795</v>
       </c>
       <c r="AO28" t="n">
-        <v>-118.4818529600821</v>
+        <v>-118.4818529601416</v>
       </c>
       <c r="AP28" t="n">
-        <v>28.75694233772689</v>
+        <v>28.75694233787942</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.0207219479267835</v>
+        <v>0.02072194792745929</v>
       </c>
       <c r="AR28" t="n">
-        <v>117.2273894516794</v>
+        <v>117.227389452306</v>
       </c>
       <c r="AS28" t="n">
-        <v>157.3135981868093</v>
+        <v>157.3135981870485</v>
       </c>
     </row>
     <row r="29">
@@ -7756,112 +7756,112 @@
         <v>27840.35725365008</v>
       </c>
       <c r="J29" t="n">
-        <v>12.10178926074621</v>
+        <v>12.10178926076199</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.299472671285667</v>
+        <v>-1.29947267129122</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01642995094161392</v>
+        <v>-0.01642995094164457</v>
       </c>
       <c r="M29" t="n">
-        <v>0.03715388464293796</v>
+        <v>0.03715388464313682</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3085318025519207</v>
+        <v>0.3085318025524598</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.3365693165703608</v>
+        <v>-0.3365693165715262</v>
       </c>
       <c r="P29" t="n">
-        <v>12.10067564645607</v>
+        <v>12.10067564647184</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.855601378201386</v>
+        <v>0.8556013782045796</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01645310419378794</v>
+        <v>0.0164531041938184</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.02662802448650984</v>
+        <v>-0.02662802448665153</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3041205539613382</v>
+        <v>0.3041205539618769</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.2765021643922128</v>
+        <v>-0.2765021643933779</v>
       </c>
       <c r="V29" t="n">
-        <v>-12.10178926074621</v>
+        <v>-12.10178926076199</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.299472671285667</v>
+        <v>-1.29947267129122</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01642995094161392</v>
+        <v>0.01642995094164457</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.03715388464293796</v>
+        <v>-0.03715388464313682</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.3085318025519207</v>
+        <v>0.3085318025524598</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.3365693165703608</v>
+        <v>0.3365693165715262</v>
       </c>
       <c r="AB29" t="n">
-        <v>-12.10067564645607</v>
+        <v>-12.10067564647184</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.855601378201386</v>
+        <v>0.8556013782045796</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.01645310419378794</v>
+        <v>-0.0164531041938184</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.02662802448650984</v>
+        <v>0.02662802448665153</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.3041205539613382</v>
+        <v>0.3041205539618769</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2765021643922128</v>
+        <v>0.2765021643933779</v>
       </c>
       <c r="AH29" t="n">
-        <v>-131.9632933821995</v>
+        <v>-131.9632933824323</v>
       </c>
       <c r="AI29" t="n">
-        <v>30.92861067592477</v>
+        <v>30.92861067598463</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-251.5946504736163</v>
+        <v>-251.5946504740586</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.1361498444878597</v>
+        <v>-0.1361498444885867</v>
       </c>
       <c r="AL29" t="n">
-        <v>1008.826844862238</v>
+        <v>1008.826844864008</v>
       </c>
       <c r="AM29" t="n">
-        <v>157.0517121625711</v>
+        <v>157.0517121628106</v>
       </c>
       <c r="AN29" t="n">
-        <v>131.9632933821995</v>
+        <v>131.9632933824323</v>
       </c>
       <c r="AO29" t="n">
-        <v>-30.92861067592477</v>
+        <v>-30.92861067598463</v>
       </c>
       <c r="AP29" t="n">
-        <v>251.5946504736163</v>
+        <v>251.5946504740586</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.1361498444878597</v>
+        <v>0.1361498444885867</v>
       </c>
       <c r="AR29" t="n">
-        <v>1003.930358926692</v>
+        <v>1003.930358928461</v>
       </c>
       <c r="AS29" t="n">
-        <v>90.37717324482674</v>
+        <v>90.37717324506605</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001054896281654782</v>
+        <v>-0.0001054896281658113</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.318620352068478e-05</v>
+        <v>-1.318620352072641e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.50052093760917</v>
+        <v>-12.50052093764864</v>
       </c>
       <c r="I30" t="n">
-        <v>-2637.240704136956</v>
+        <v>-2637.240704145283</v>
       </c>
       <c r="J30" t="n">
-        <v>13.74971682084649</v>
+        <v>13.74971682086599</v>
       </c>
       <c r="K30" t="n">
-        <v>0.983163243548322</v>
+        <v>0.9831632435523956</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01709782427089189</v>
+        <v>0.01709782427092434</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.009077683545820888</v>
+        <v>-0.009077683545891</v>
       </c>
       <c r="N30" t="n">
-        <v>0.128253174079973</v>
+        <v>0.1282531740802902</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.2961131962401839</v>
+        <v>-0.29611319624158</v>
       </c>
       <c r="P30" t="n">
-        <v>16.28729671562621</v>
+        <v>16.28729671565749</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9830577539201565</v>
+        <v>0.9830577539242298</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01191508433337423</v>
+        <v>0.01191508433340097</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.00908168820024597</v>
+        <v>-0.009081688200316467</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1184927986803802</v>
+        <v>0.1184927986808056</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.3261226386362977</v>
+        <v>-0.3261226386376945</v>
       </c>
       <c r="V30" t="n">
-        <v>0.983163243548322</v>
+        <v>0.9831632435523956</v>
       </c>
       <c r="W30" t="n">
-        <v>-13.74971682084649</v>
+        <v>-13.74971682086599</v>
       </c>
       <c r="X30" t="n">
-        <v>0.01709782427089189</v>
+        <v>0.01709782427092434</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.128253174079973</v>
+        <v>0.1282531740802902</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.009077683545820888</v>
+        <v>0.009077683545891</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.2961131962401839</v>
+        <v>-0.29611319624158</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.9830577539201565</v>
+        <v>0.9830577539242298</v>
       </c>
       <c r="AC30" t="n">
-        <v>-16.28729671562621</v>
+        <v>-16.28729671565749</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.01191508433337423</v>
+        <v>0.01191508433340097</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.1184927986803802</v>
+        <v>0.1184927986808056</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.00908168820024597</v>
+        <v>0.009081688200316467</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.3261226386362977</v>
+        <v>-0.3261226386376945</v>
       </c>
       <c r="AH30" t="n">
-        <v>12.50052093761042</v>
+        <v>12.50052093763952</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.061241533179555</v>
+        <v>5.061241533242764</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-7.019509614552399</v>
+        <v>-7.019509614610334</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.02083464748759228</v>
+        <v>0.02083464748736136</v>
       </c>
       <c r="AL30" t="n">
-        <v>28.07581587500367</v>
+        <v>28.0758158752352</v>
       </c>
       <c r="AM30" t="n">
-        <v>36.90020666256169</v>
+        <v>36.90020666281453</v>
       </c>
       <c r="AN30" t="n">
-        <v>-12.50052093761042</v>
+        <v>-12.50052093763952</v>
       </c>
       <c r="AO30" t="n">
-        <v>-5.061241533179555</v>
+        <v>-5.061241533242764</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.019509614552399</v>
+        <v>7.019509614610334</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.02083464748759228</v>
+        <v>-0.02083464748736136</v>
       </c>
       <c r="AR30" t="n">
-        <v>28.08026104141551</v>
+        <v>28.08026104164746</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.589725602874751</v>
+        <v>3.5897256031285</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0006230945216358919</v>
+        <v>0.0006230945216323391</v>
       </c>
       <c r="G31" t="n">
-        <v>7.788681520448648e-05</v>
+        <v>7.788681520404239e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>73.83670081385318</v>
+        <v>73.83670081343219</v>
       </c>
       <c r="I31" t="n">
-        <v>15577.36304089729</v>
+        <v>15577.36304080848</v>
       </c>
       <c r="J31" t="n">
-        <v>16.28729671562621</v>
+        <v>16.28729671565749</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9830577539201565</v>
+        <v>0.9830577539242298</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01191508433337423</v>
+        <v>0.01191508433340097</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.00908168820024597</v>
+        <v>-0.009081688200316467</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1184927986803802</v>
+        <v>0.1184927986808056</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.3261226386362977</v>
+        <v>-0.3261226386376945</v>
       </c>
       <c r="P31" t="n">
-        <v>16.28791981014785</v>
+        <v>16.28791981017913</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1.457257327504276</v>
+        <v>-1.457257327510761</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.01193004232021133</v>
+        <v>-0.01193004232023791</v>
       </c>
       <c r="S31" t="n">
-        <v>0.01134630288189326</v>
+        <v>0.0113463028819652</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1105412483358429</v>
+        <v>0.1105412483363123</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2660564792319032</v>
+        <v>-0.2660564792332996</v>
       </c>
       <c r="V31" t="n">
-        <v>16.28729671562621</v>
+        <v>16.28729671565749</v>
       </c>
       <c r="W31" t="n">
-        <v>0.9830577539201565</v>
+        <v>0.9830577539242298</v>
       </c>
       <c r="X31" t="n">
-        <v>0.01191508433337423</v>
+        <v>0.01191508433340097</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.00908168820024597</v>
+        <v>-0.009081688200316467</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.1184927986803802</v>
+        <v>0.1184927986808056</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.3261226386362977</v>
+        <v>-0.3261226386376945</v>
       </c>
       <c r="AB31" t="n">
-        <v>16.28791981014785</v>
+        <v>16.28791981017913</v>
       </c>
       <c r="AC31" t="n">
-        <v>-1.457257327504276</v>
+        <v>-1.457257327510761</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.01193004232021133</v>
+        <v>-0.01193004232023791</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.01134630288189326</v>
+        <v>0.0113463028819652</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.1105412483358429</v>
+        <v>0.1105412483363123</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.2660564792319032</v>
+        <v>-0.2660564792332996</v>
       </c>
       <c r="AH31" t="n">
-        <v>-73.8367008138448</v>
+        <v>-73.83670081337914</v>
       </c>
       <c r="AI31" t="n">
-        <v>7.450730348091383</v>
+        <v>7.450730348027498</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-92.85403857811413</v>
+        <v>-92.85403857848101</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.04360590404072028</v>
+        <v>-0.04360590404102432</v>
       </c>
       <c r="AL31" t="n">
-        <v>375.8292647536747</v>
+        <v>375.8292647551177</v>
       </c>
       <c r="AM31" t="n">
-        <v>-3.533797077073132</v>
+        <v>-3.533797077329041</v>
       </c>
       <c r="AN31" t="n">
-        <v>73.8367008138448</v>
+        <v>73.83670081337914</v>
       </c>
       <c r="AO31" t="n">
-        <v>-7.450730348091383</v>
+        <v>-7.450730348027498</v>
       </c>
       <c r="AP31" t="n">
-        <v>92.85403857811413</v>
+        <v>92.85403857848101</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.04360590404072028</v>
+        <v>0.04360590404102432</v>
       </c>
       <c r="AR31" t="n">
-        <v>367.0030438712382</v>
+        <v>367.0030438727302</v>
       </c>
       <c r="AS31" t="n">
-        <v>63.13963986180471</v>
+        <v>63.13963986154931</v>
       </c>
     </row>
     <row r="32">
@@ -8173,112 +8173,112 @@
         <v>2832.776785338664</v>
       </c>
       <c r="J32" t="n">
-        <v>16.28791981014785</v>
+        <v>16.28791981017913</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.457257327504276</v>
+        <v>-1.457257327510761</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.01193004232021133</v>
+        <v>-0.01193004232023791</v>
       </c>
       <c r="M32" t="n">
-        <v>0.01134630288189326</v>
+        <v>0.0113463028819652</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1105412483358429</v>
+        <v>0.1105412483363123</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.2660564792319032</v>
+        <v>-0.2660564792332996</v>
       </c>
       <c r="P32" t="n">
-        <v>13.75040665788783</v>
+        <v>13.75040665790733</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.45737063857569</v>
+        <v>-1.457370638582175</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.01708286628405483</v>
+        <v>-0.01708286628408745</v>
       </c>
       <c r="S32" t="n">
-        <v>0.009916345241901936</v>
+        <v>0.009916345241963179</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1081508876107066</v>
+        <v>0.1081508876110224</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.3561669580448221</v>
+        <v>-0.3561669580462182</v>
       </c>
       <c r="V32" t="n">
-        <v>1.457257327504276</v>
+        <v>1.457257327510761</v>
       </c>
       <c r="W32" t="n">
-        <v>16.28791981014785</v>
+        <v>16.28791981017913</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.01193004232021133</v>
+        <v>-0.01193004232023791</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.1105412483358429</v>
+        <v>-0.1105412483363123</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.01134630288189326</v>
+        <v>0.0113463028819652</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.2660564792319032</v>
+        <v>-0.2660564792332996</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.45737063857569</v>
+        <v>1.457370638582175</v>
       </c>
       <c r="AC32" t="n">
-        <v>13.75040665788783</v>
+        <v>13.75040665790733</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.01708286628405483</v>
+        <v>-0.01708286628408745</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.1081508876107066</v>
+        <v>-0.1081508876110224</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.009916345241901936</v>
+        <v>0.009916345241963179</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.3561669580448221</v>
+        <v>-0.3561669580462182</v>
       </c>
       <c r="AH32" t="n">
         <v>-13.42736196250189</v>
       </c>
       <c r="AI32" t="n">
-        <v>-94.94054335937926</v>
+        <v>-94.9405433593156</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-8.314361537792287</v>
+        <v>-8.314361537847095</v>
       </c>
       <c r="AK32" t="n">
-        <v>-0.005102500778656233</v>
+        <v>-0.005102500778984165</v>
       </c>
       <c r="AL32" t="n">
-        <v>34.05107264136433</v>
+        <v>34.0510726415895</v>
       </c>
       <c r="AM32" t="n">
-        <v>-63.08419102967977</v>
+        <v>-63.08419102942511</v>
       </c>
       <c r="AN32" t="n">
         <v>13.42736196250189</v>
       </c>
       <c r="AO32" t="n">
-        <v>-105.0594566406207</v>
+        <v>-105.0594566406844</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.314361537792287</v>
+        <v>8.314361537847095</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.005102500778656233</v>
+        <v>0.005102500778984165</v>
       </c>
       <c r="AR32" t="n">
-        <v>32.46381966097396</v>
+        <v>32.46381966118725</v>
       </c>
       <c r="AS32" t="n">
-        <v>103.5598441546466</v>
+        <v>103.5598441549012</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0006898370413459531</v>
+        <v>0.0006898370413406241</v>
       </c>
       <c r="G33" t="n">
-        <v>8.622963016824414e-05</v>
+        <v>8.622963016757801e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>81.74568939949545</v>
+        <v>81.74568939886396</v>
       </c>
       <c r="I33" t="n">
-        <v>17245.92603364883</v>
+        <v>17245.9260335156</v>
       </c>
       <c r="J33" t="n">
-        <v>13.75040665788783</v>
+        <v>13.75040665790733</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.45737063857569</v>
+        <v>-1.457370638582175</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.01708286628405483</v>
+        <v>-0.01708286628408745</v>
       </c>
       <c r="M33" t="n">
-        <v>0.009916345241901936</v>
+        <v>0.009916345241963179</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1081508876107066</v>
+        <v>0.1081508876110224</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.3561669580448221</v>
+        <v>-0.3561669580462182</v>
       </c>
       <c r="P33" t="n">
-        <v>13.74971682084649</v>
+        <v>13.74971682086599</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.983163243548322</v>
+        <v>0.9831632435523956</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01709782427089189</v>
+        <v>0.01709782427092434</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.009077683545820888</v>
+        <v>-0.009077683545891</v>
       </c>
       <c r="T33" t="n">
-        <v>0.128253174079973</v>
+        <v>0.1282531740802902</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.2961131962401839</v>
+        <v>-0.29611319624158</v>
       </c>
       <c r="V33" t="n">
-        <v>-13.75040665788783</v>
+        <v>-13.75040665790733</v>
       </c>
       <c r="W33" t="n">
-        <v>-1.45737063857569</v>
+        <v>-1.457370638582175</v>
       </c>
       <c r="X33" t="n">
-        <v>0.01708286628405483</v>
+        <v>0.01708286628408745</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.009916345241901936</v>
+        <v>-0.009916345241963179</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1081508876107066</v>
+        <v>0.1081508876110224</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.3561669580448221</v>
+        <v>0.3561669580462182</v>
       </c>
       <c r="AB33" t="n">
-        <v>-13.74971682084649</v>
+        <v>-13.74971682086599</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.983163243548322</v>
+        <v>0.9831632435523956</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.01709782427089189</v>
+        <v>-0.01709782427092434</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.009077683545820888</v>
+        <v>0.009077683545891</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.128253174079973</v>
+        <v>0.1282531740802902</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.2961131962401839</v>
+        <v>0.29611319624158</v>
       </c>
       <c r="AH33" t="n">
-        <v>-81.74568939954042</v>
+        <v>-81.74568939884193</v>
       </c>
       <c r="AI33" t="n">
-        <v>17.54355711260374</v>
+        <v>17.54355711266726</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-94.84626256787126</v>
+        <v>-94.84626256812794</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.04054494606610064</v>
+        <v>-0.04054494606638104</v>
       </c>
       <c r="AL33" t="n">
-        <v>368.2282812810421</v>
+        <v>368.2282812820681</v>
       </c>
       <c r="AM33" t="n">
-        <v>103.504066251989</v>
+        <v>103.5040662522431</v>
       </c>
       <c r="AN33" t="n">
-        <v>81.74568939954042</v>
+        <v>81.74568939884193</v>
       </c>
       <c r="AO33" t="n">
-        <v>-17.54355711260374</v>
+        <v>-17.54355711266726</v>
       </c>
       <c r="AP33" t="n">
-        <v>94.84626256787126</v>
+        <v>94.84626256812794</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.04054494606610064</v>
+        <v>0.04054494606638104</v>
       </c>
       <c r="AR33" t="n">
-        <v>390.5418192619279</v>
+        <v>390.5418192629554</v>
       </c>
       <c r="AS33" t="n">
-        <v>36.84439064884054</v>
+        <v>36.84439064909469</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validation_frame_moment_release.xlsx
+++ b/outputs/validation_frame_moment_release.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>3.757925951556457</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1624422723423497</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.03630395006721086</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="I6" t="n">
-        <v>0.609806490401359</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.005111413036285996</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="K6" t="n">
-        <v>3.761445368299572</v>
+        <v>3.761445368295371</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3.723395957228697</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="F7" t="n">
-        <v>0.162336698264033</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.03628902410970122</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6753566419540323</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.03509421220940796</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="K7" t="n">
-        <v>3.726938275143084</v>
+        <v>3.726938275138332</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>3.723221883770459</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1923970678424733</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04214837918590374</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5925544959344536</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0251422011950651</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="K8" t="n">
-        <v>3.728194767159398</v>
+        <v>3.728194767154632</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>3.758983147796373</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1926264440291746</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05052610874615139</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6101246851589696</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.06503362791350591</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="K9" t="n">
-        <v>3.763925524843947</v>
+        <v>3.763925524839729</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>8.658378534746893</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5437220967409437</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01407909170155771</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.04556477868193153</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="I10" t="n">
-        <v>0.522665028634919</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1550967117146793</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="K10" t="n">
-        <v>8.675445279077797</v>
+        <v>8.67544527906699</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03693211710211</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5436509443454407</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="G11" t="n">
-        <v>0.009226541546905213</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.04561220557396294</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8629762354429026</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1753504665297493</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="K11" t="n">
-        <v>10.0516490090767</v>
+        <v>10.05164900906162</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>10.03855675064235</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7997579802044718</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.00930297481895709</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>10.07036846436655</v>
+        <v>10.07036846435135</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>8.659455021349791</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7997730185700033</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.01400265842950587</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0909672374775249</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5215719617308274</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2249576665799374</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="K13" t="n">
-        <v>8.696320729047185</v>
+        <v>8.696320729036229</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>12.10067564647184</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8556013782045796</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0164531041938184</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.02662802448665153</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3041205539618769</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2765021643933779</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="K14" t="n">
-        <v>12.13089755641106</v>
+        <v>12.1308975563951</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>14.61043109297521</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8554961959393073</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01137182782097141</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02661478979068704</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3475225990419422</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.306472075519195</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="K15" t="n">
-        <v>14.63546035430084</v>
+        <v>14.63546035427502</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>14.61196774740029</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.29941701569186</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.01139498107314529</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03319060518225687</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="I16" t="n">
-        <v>0.31823938176172</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2465744571357565</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="K16" t="n">
-        <v>14.6696358467867</v>
+        <v>14.66963584676064</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>12.10178926076199</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.29947267129122</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.01642995094164457</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03715388464313682</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3085318025524598</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3365693165715262</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="K17" t="n">
-        <v>12.17136814325386</v>
+        <v>12.17136814323758</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>13.74971682086599</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9831632435523956</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01709782427092434</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.009077683545891</v>
+        <v>-0.009077683545820888</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1282531740802902</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.29611319624158</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="K18" t="n">
-        <v>13.78483278654741</v>
+        <v>13.78483278652767</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>16.28729671565749</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9830577539242298</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01191508433340097</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.009081688200316467</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1184927986808056</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3261226386376945</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="K19" t="n">
-        <v>16.31694146648362</v>
+        <v>16.31694146645215</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>16.28791981017913</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.457257327510761</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.01193004232023791</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0113463028819652</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1105412483363123</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2660564792332996</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="K20" t="n">
-        <v>16.35298361117381</v>
+        <v>16.35298361114208</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>13.75040665790733</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.457370638582175</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.01708286628408745</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="H21" t="n">
-        <v>0.009916345241963179</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1081508876110224</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3561669580462182</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="K21" t="n">
-        <v>13.82743303221332</v>
+        <v>13.82743303219325</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>16.35298361117381</v>
+        <v>16.35298361114208</v>
       </c>
       <c r="D2" t="n">
-        <v>16.28791981017913</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.457257327510761</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01193004232023791</v>
+        <v>-0.01193004232021133</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>16.28791981017913</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="D3" t="n">
-        <v>16.28791981017913</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.457257327510761</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01193004232023791</v>
+        <v>-0.01193004232021133</v>
       </c>
     </row>
     <row r="4">
@@ -1289,16 +1289,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.457370638582175</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="D4" t="n">
-        <v>13.75040665790733</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.457370638582175</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01708286628408745</v>
+        <v>-0.01708286628405483</v>
       </c>
     </row>
     <row r="5">
@@ -1311,16 +1311,16 @@
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01709782427092434</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="D5" t="n">
-        <v>13.74971682086599</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9831632435523956</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01709782427092434</v>
+        <v>0.01709782427089189</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-475.6982651535872</v>
+        <v>-475.6982651531055</v>
       </c>
       <c r="C2" t="n">
-        <v>-13.20417079471022</v>
+        <v>-13.20417079465767</v>
       </c>
       <c r="D2" t="n">
-        <v>-1380.213673756154</v>
+        <v>-1380.213673753829</v>
       </c>
       <c r="E2" t="n">
-        <v>66.47743543386669</v>
+        <v>66.4774354336206</v>
       </c>
       <c r="F2" t="n">
-        <v>-1878.351598357767</v>
+        <v>-1878.351598355772</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0145478678725063</v>
+        <v>0.01454786787215924</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-418.6737544037614</v>
+        <v>-418.6737544032946</v>
       </c>
       <c r="C3" t="n">
-        <v>-13.18917439728258</v>
+        <v>-13.18917439722999</v>
       </c>
       <c r="D3" t="n">
-        <v>-977.1609122522647</v>
+        <v>-977.1609122504613</v>
       </c>
       <c r="E3" t="n">
-        <v>66.42140103302664</v>
+        <v>66.42140103278049</v>
       </c>
       <c r="F3" t="n">
-        <v>-1755.785178257268</v>
+        <v>-1755.785178255167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0998835270575457</v>
+        <v>0.0998835270571985</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-554.9044043385509</v>
+        <v>-554.9044043380102</v>
       </c>
       <c r="C4" t="n">
-        <v>16.26814280357464</v>
+        <v>16.26814280349655</v>
       </c>
       <c r="D4" t="n">
-        <v>979.0184522747155</v>
+        <v>979.0184522729362</v>
       </c>
       <c r="E4" t="n">
-        <v>-79.99422900829268</v>
+        <v>-79.99422900793247</v>
       </c>
       <c r="F4" t="n">
-        <v>-1953.203540007148</v>
+        <v>-1953.2035400049</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.07155857263210837</v>
+        <v>-0.07155857263245415</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-550.7235761054679</v>
+        <v>-550.7235761049859</v>
       </c>
       <c r="C5" t="n">
-        <v>10.12520238837771</v>
+        <v>10.12520238831702</v>
       </c>
       <c r="D5" t="n">
-        <v>1378.356133733707</v>
+        <v>1378.356133731357</v>
       </c>
       <c r="E5" t="n">
-        <v>-67.76492763728514</v>
+        <v>-67.76492763695965</v>
       </c>
       <c r="F5" t="n">
-        <v>-1953.662995334041</v>
+        <v>-1953.662995332046</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1850957102153629</v>
+        <v>0.1850957102150153</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001455921596789192</v>
+        <v>0.001455921596786739</v>
       </c>
       <c r="H2" t="n">
-        <v>1380.213673756154</v>
+        <v>1380.213673753829</v>
       </c>
       <c r="I2" t="n">
-        <v>291184.3193578384</v>
+        <v>291184.3193573478</v>
       </c>
       <c r="J2" t="n">
-        <v>-1380.213673756154</v>
+        <v>-1380.213673753829</v>
       </c>
       <c r="K2" t="n">
-        <v>-13.20417079471022</v>
+        <v>-13.20417079465767</v>
       </c>
       <c r="L2" t="n">
-        <v>475.6982651535872</v>
+        <v>475.6982651531055</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0145478678725063</v>
+        <v>0.01454786787215924</v>
       </c>
       <c r="N2" t="n">
-        <v>-1878.351598357767</v>
+        <v>-1878.351598355772</v>
       </c>
       <c r="O2" t="n">
-        <v>-66.47743543386669</v>
+        <v>-66.4774354336206</v>
       </c>
       <c r="P2" t="n">
-        <v>1380.213673756154</v>
+        <v>1380.213673753829</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.20417079471022</v>
+        <v>13.20417079465767</v>
       </c>
       <c r="R2" t="n">
-        <v>-475.6982651535872</v>
+        <v>-475.6982651531055</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0145478678725063</v>
+        <v>-0.01454786787215924</v>
       </c>
       <c r="T2" t="n">
-        <v>-975.8379925637557</v>
+        <v>-975.8379925628601</v>
       </c>
       <c r="U2" t="n">
-        <v>-12.74758933439462</v>
+        <v>-12.74758933432537</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001030760455962304</v>
+        <v>0.001030760455960402</v>
       </c>
       <c r="H3" t="n">
-        <v>977.1609122522644</v>
+        <v>977.1609122504611</v>
       </c>
       <c r="I3" t="n">
-        <v>206152.0911924609</v>
+        <v>206152.0911920804</v>
       </c>
       <c r="J3" t="n">
-        <v>-977.1609122522647</v>
+        <v>-977.1609122504613</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.18917439728258</v>
+        <v>-13.18917439722999</v>
       </c>
       <c r="L3" t="n">
-        <v>418.6737544037614</v>
+        <v>418.6737544032946</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0998835270575457</v>
+        <v>0.0998835270571985</v>
       </c>
       <c r="N3" t="n">
-        <v>-1755.785178257268</v>
+        <v>-1755.785178255167</v>
       </c>
       <c r="O3" t="n">
-        <v>-66.42140103302664</v>
+        <v>-66.42140103278049</v>
       </c>
       <c r="P3" t="n">
-        <v>977.1609122522647</v>
+        <v>977.1609122504613</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.18917439728258</v>
+        <v>13.18917439722999</v>
       </c>
       <c r="R3" t="n">
-        <v>-418.6737544037614</v>
+        <v>-418.6737544032946</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0998835270575457</v>
+        <v>-0.0998835270571985</v>
       </c>
       <c r="T3" t="n">
-        <v>-756.2573481653003</v>
+        <v>-756.2573481646002</v>
       </c>
       <c r="U3" t="n">
-        <v>-12.71364535066883</v>
+        <v>-12.71364535059946</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001032719886365733</v>
+        <v>-0.001032719886363857</v>
       </c>
       <c r="H4" t="n">
-        <v>-979.0184522747154</v>
+        <v>-979.018452272936</v>
       </c>
       <c r="I4" t="n">
-        <v>-206543.9772731467</v>
+        <v>-206543.9772727713</v>
       </c>
       <c r="J4" t="n">
-        <v>979.0184522747155</v>
+        <v>979.0184522729362</v>
       </c>
       <c r="K4" t="n">
-        <v>16.26814280357464</v>
+        <v>16.26814280349655</v>
       </c>
       <c r="L4" t="n">
-        <v>554.9044043385509</v>
+        <v>554.9044043380102</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07155857263210837</v>
+        <v>-0.07155857263245415</v>
       </c>
       <c r="N4" t="n">
-        <v>-1953.203540007148</v>
+        <v>-1953.2035400049</v>
       </c>
       <c r="O4" t="n">
-        <v>79.99422900829268</v>
+        <v>79.99422900793247</v>
       </c>
       <c r="P4" t="n">
-        <v>-979.0184522747155</v>
+        <v>-979.0184522729362</v>
       </c>
       <c r="Q4" t="n">
-        <v>-16.26814280357464</v>
+        <v>-16.26814280349655</v>
       </c>
       <c r="R4" t="n">
-        <v>-404.9044043385508</v>
+        <v>-404.9044043380101</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07155857263210837</v>
+        <v>0.07155857263245415</v>
       </c>
       <c r="T4" t="n">
-        <v>-926.2228860241569</v>
+        <v>-926.2228860231605</v>
       </c>
       <c r="U4" t="n">
-        <v>17.61462781315514</v>
+        <v>17.61462781304681</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001453962166385767</v>
+        <v>-0.001453962166383287</v>
       </c>
       <c r="H5" t="n">
-        <v>-1378.356133733707</v>
+        <v>-1378.356133731356</v>
       </c>
       <c r="I5" t="n">
-        <v>-290792.4332771534</v>
+        <v>-290792.4332766574</v>
       </c>
       <c r="J5" t="n">
-        <v>1378.356133733707</v>
+        <v>1378.356133731357</v>
       </c>
       <c r="K5" t="n">
-        <v>10.12520238837771</v>
+        <v>10.12520238831702</v>
       </c>
       <c r="L5" t="n">
-        <v>550.7235761054679</v>
+        <v>550.7235761049859</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1850957102153629</v>
+        <v>0.1850957102150153</v>
       </c>
       <c r="N5" t="n">
-        <v>-1953.662995334041</v>
+        <v>-1953.662995332046</v>
       </c>
       <c r="O5" t="n">
-        <v>67.76492763728514</v>
+        <v>67.76492763695965</v>
       </c>
       <c r="P5" t="n">
-        <v>-1378.356133733707</v>
+        <v>-1378.356133731357</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.12520238837771</v>
+        <v>-10.12520238831702</v>
       </c>
       <c r="R5" t="n">
-        <v>-400.7235761054679</v>
+        <v>-400.7235761049859</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1850957102153629</v>
+        <v>-0.1850957102150153</v>
       </c>
       <c r="T5" t="n">
-        <v>-900.6784612987663</v>
+        <v>-900.678461297869</v>
       </c>
       <c r="U5" t="n">
-        <v>-7.013713307018918</v>
+        <v>-7.013713307057571</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005343562120822556</v>
+        <v>0.005343562120812355</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008905936868037594</v>
+        <v>0.0008905936868020591</v>
       </c>
       <c r="H6" t="n">
-        <v>844.2828150899639</v>
+        <v>844.282815088352</v>
       </c>
       <c r="I6" t="n">
-        <v>178118.7373607519</v>
+        <v>178118.7373604118</v>
       </c>
       <c r="J6" t="n">
-        <v>-844.2828150899641</v>
+        <v>-844.2828150883522</v>
       </c>
       <c r="K6" t="n">
-        <v>-33.46616407728784</v>
+        <v>-33.46616407719057</v>
       </c>
       <c r="L6" t="n">
-        <v>370.7493797667951</v>
+        <v>370.7493797662693</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4268812347000424</v>
+        <v>0.4268812346987415</v>
       </c>
       <c r="N6" t="n">
-        <v>-1047.763457593219</v>
+        <v>-1047.763457591656</v>
       </c>
       <c r="O6" t="n">
-        <v>-107.2515054067568</v>
+        <v>-107.251505406429</v>
       </c>
       <c r="P6" t="n">
-        <v>844.2828150899641</v>
+        <v>844.2828150883522</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.46616407728784</v>
+        <v>33.46616407719057</v>
       </c>
       <c r="R6" t="n">
-        <v>-370.7493797667951</v>
+        <v>-370.7493797662693</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4268812347000424</v>
+        <v>-0.4268812346987415</v>
       </c>
       <c r="T6" t="n">
-        <v>-1176.732821007551</v>
+        <v>-1176.73282100596</v>
       </c>
       <c r="U6" t="n">
-        <v>-93.54547905697024</v>
+        <v>-93.54547905671429</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003041978811131388</v>
+        <v>0.003041978811124054</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005069964685218979</v>
+        <v>0.0005069964685206757</v>
       </c>
       <c r="H7" t="n">
-        <v>480.6326521587592</v>
+        <v>480.6326521576005</v>
       </c>
       <c r="I7" t="n">
-        <v>101399.2937043796</v>
+        <v>101399.2937041351</v>
       </c>
       <c r="J7" t="n">
-        <v>-480.6326521587592</v>
+        <v>-480.6326521576007</v>
       </c>
       <c r="K7" t="n">
-        <v>-33.45060406750243</v>
+        <v>-33.45060406740529</v>
       </c>
       <c r="L7" t="n">
-        <v>418.9725901617112</v>
+        <v>418.9725901611122</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3991908776809715</v>
+        <v>0.3991908776797221</v>
       </c>
       <c r="N7" t="n">
-        <v>-1395.756269666897</v>
+        <v>-1395.756269664567</v>
       </c>
       <c r="O7" t="n">
-        <v>-107.2509664860609</v>
+        <v>-107.2509664857333</v>
       </c>
       <c r="P7" t="n">
-        <v>480.6326521587592</v>
+        <v>480.6326521576007</v>
       </c>
       <c r="Q7" t="n">
-        <v>33.45060406750243</v>
+        <v>33.45060406740529</v>
       </c>
       <c r="R7" t="n">
-        <v>-418.9725901617112</v>
+        <v>-418.9725901611122</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3991908776809715</v>
+        <v>-0.3991908776797221</v>
       </c>
       <c r="T7" t="n">
-        <v>-1118.07927130337</v>
+        <v>-1118.079271302104</v>
       </c>
       <c r="U7" t="n">
-        <v>-93.45265791895361</v>
+        <v>-93.45265791869829</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.003106655500762689</v>
+        <v>-0.003106655500755174</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0005177759167937815</v>
+        <v>-0.000517775916792529</v>
       </c>
       <c r="H8" t="n">
-        <v>-490.8515691205048</v>
+        <v>-490.8515691193175</v>
       </c>
       <c r="I8" t="n">
-        <v>-103555.1833587563</v>
+        <v>-103555.1833585058</v>
       </c>
       <c r="J8" t="n">
-        <v>490.8515691205049</v>
+        <v>490.8515691193177</v>
       </c>
       <c r="K8" t="n">
-        <v>118.6258911183909</v>
+        <v>118.6258911179426</v>
       </c>
       <c r="L8" t="n">
-        <v>1194.29227350357</v>
+        <v>1194.292273501664</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07155857263210837</v>
+        <v>0.07155857263245415</v>
       </c>
       <c r="N8" t="n">
-        <v>-2994.386493519215</v>
+        <v>-2994.386493514121</v>
       </c>
       <c r="O8" t="n">
-        <v>324.6878727576038</v>
+        <v>324.687872756385</v>
       </c>
       <c r="P8" t="n">
-        <v>-490.8515691205049</v>
+        <v>-490.8515691193177</v>
       </c>
       <c r="Q8" t="n">
-        <v>-118.6258911183909</v>
+        <v>-118.6258911179426</v>
       </c>
       <c r="R8" t="n">
-        <v>-1044.29227350357</v>
+        <v>-1044.292273501664</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07155857263210837</v>
+        <v>-0.07155857263245415</v>
       </c>
       <c r="T8" t="n">
-        <v>-3721.367147502207</v>
+        <v>-3721.36714749586</v>
       </c>
       <c r="U8" t="n">
-        <v>387.0674739527414</v>
+        <v>387.0674739512706</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.005278885431191272</v>
+        <v>-0.005278885431181244</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0008798142385318787</v>
+        <v>-0.0008798142385302073</v>
       </c>
       <c r="H9" t="n">
-        <v>-834.063898128221</v>
+        <v>-834.0638981266366</v>
       </c>
       <c r="I9" t="n">
-        <v>-175962.8477063757</v>
+        <v>-175962.8477060414</v>
       </c>
       <c r="J9" t="n">
-        <v>834.0638981282214</v>
+        <v>834.0638981266368</v>
       </c>
       <c r="K9" t="n">
-        <v>45.0577455145506</v>
+        <v>45.05774551440441</v>
       </c>
       <c r="L9" t="n">
-        <v>446.3275434447266</v>
+        <v>446.3275434442011</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4551684177429204</v>
+        <v>0.4551684177415671</v>
       </c>
       <c r="N9" t="n">
-        <v>-1123.453614997354</v>
+        <v>-1123.453614995791</v>
       </c>
       <c r="O9" t="n">
-        <v>165.0996718048683</v>
+        <v>165.0996718042885</v>
       </c>
       <c r="P9" t="n">
-        <v>-834.0638981282214</v>
+        <v>-834.0638981266368</v>
       </c>
       <c r="Q9" t="n">
-        <v>-45.0577455145506</v>
+        <v>-45.05774551440441</v>
       </c>
       <c r="R9" t="n">
-        <v>-296.3275434447266</v>
+        <v>-296.3275434442011</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4551684177429204</v>
+        <v>-0.4551684177415671</v>
       </c>
       <c r="T9" t="n">
-        <v>-1104.511645671005</v>
+        <v>-1104.511645669415</v>
       </c>
       <c r="U9" t="n">
-        <v>105.2468012824354</v>
+        <v>105.246801282138</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002374012492260691</v>
+        <v>0.002374012492255152</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003956687487101151</v>
+        <v>0.0003956687487091919</v>
       </c>
       <c r="H10" t="n">
-        <v>375.0939737771891</v>
+        <v>375.0939737763139</v>
       </c>
       <c r="I10" t="n">
-        <v>79133.74974202301</v>
+        <v>79133.74974183837</v>
       </c>
       <c r="J10" t="n">
-        <v>-375.0939737771891</v>
+        <v>-375.0939737763142</v>
       </c>
       <c r="K10" t="n">
-        <v>-23.50754841627872</v>
+        <v>-23.50754841617129</v>
       </c>
       <c r="L10" t="n">
-        <v>237.2786231038581</v>
+        <v>237.2786231035455</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3455385960855267</v>
+        <v>0.3455385960838586</v>
       </c>
       <c r="N10" t="n">
-        <v>-550.1129580535226</v>
+        <v>-550.1129580527219</v>
       </c>
       <c r="O10" t="n">
-        <v>-56.50944714432887</v>
+        <v>-56.50944714402618</v>
       </c>
       <c r="P10" t="n">
-        <v>375.0939737771891</v>
+        <v>375.0939737763142</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.50754841627872</v>
+        <v>23.50754841617129</v>
       </c>
       <c r="R10" t="n">
-        <v>-237.2786231038581</v>
+        <v>-237.2786231035455</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3455385960855267</v>
+        <v>-0.3455385960838586</v>
       </c>
       <c r="T10" t="n">
-        <v>-873.558780569625</v>
+        <v>-873.5587805685493</v>
       </c>
       <c r="U10" t="n">
-        <v>-84.5358433533433</v>
+        <v>-84.53584335300144</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002145286274066197</v>
+        <v>0.002145286274060163</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003575477123443661</v>
+        <v>0.0003575477123433605</v>
       </c>
       <c r="H11" t="n">
-        <v>338.955231302459</v>
+        <v>338.9552313015058</v>
       </c>
       <c r="I11" t="n">
-        <v>71509.5424688732</v>
+        <v>71509.54246867209</v>
       </c>
       <c r="J11" t="n">
-        <v>-338.9552313024592</v>
+        <v>-338.9552313015058</v>
       </c>
       <c r="K11" t="n">
-        <v>-23.4738521566461</v>
+        <v>-23.4738521565387</v>
       </c>
       <c r="L11" t="n">
-        <v>232.3606098632458</v>
+        <v>232.360609862576</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3731922717391915</v>
+        <v>0.3731922717374728</v>
       </c>
       <c r="N11" t="n">
-        <v>-315.6461386530264</v>
+        <v>-315.6461386515213</v>
       </c>
       <c r="O11" t="n">
-        <v>-56.36346879031407</v>
+        <v>-56.36346879001178</v>
       </c>
       <c r="P11" t="n">
-        <v>338.9552313024592</v>
+        <v>338.9552313015058</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.4738521566461</v>
+        <v>23.4738521565387</v>
       </c>
       <c r="R11" t="n">
-        <v>-232.3606098632458</v>
+        <v>-232.360609862576</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3731922717391915</v>
+        <v>-0.3731922717374728</v>
       </c>
       <c r="T11" t="n">
-        <v>-1078.51752052645</v>
+        <v>-1078.517520523936</v>
       </c>
       <c r="U11" t="n">
-        <v>-84.47964414956243</v>
+        <v>-84.47964414922058</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.002092006254188197</v>
+        <v>-0.002092006254182372</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0003486677090313662</v>
+        <v>-0.0003486677090303953</v>
       </c>
       <c r="H12" t="n">
-        <v>-330.5369881617351</v>
+        <v>-330.5369881608148</v>
       </c>
       <c r="I12" t="n">
-        <v>-69733.54180627322</v>
+        <v>-69733.54180607905</v>
       </c>
       <c r="J12" t="n">
-        <v>330.5369881617353</v>
+        <v>330.5369881608146</v>
       </c>
       <c r="K12" t="n">
-        <v>98.68818091868567</v>
+        <v>98.68818091821899</v>
       </c>
       <c r="L12" t="n">
-        <v>967.6109033632856</v>
+        <v>967.6109033612859</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7017888395402301</v>
+        <v>0.7017888395369127</v>
       </c>
       <c r="N12" t="n">
-        <v>-2988.32985259353</v>
+        <v>-2988.329852586897</v>
       </c>
       <c r="O12" t="n">
-        <v>320.6255905909271</v>
+        <v>320.6255905894019</v>
       </c>
       <c r="P12" t="n">
-        <v>-330.5369881617353</v>
+        <v>-330.5369881608146</v>
       </c>
       <c r="Q12" t="n">
-        <v>-98.68818091868567</v>
+        <v>-98.68818091821899</v>
       </c>
       <c r="R12" t="n">
-        <v>-817.6109033632856</v>
+        <v>-817.6109033612859</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7017888395402301</v>
+        <v>-0.7017888395369127</v>
       </c>
       <c r="T12" t="n">
-        <v>-2367.335567586184</v>
+        <v>-2367.335567580818</v>
       </c>
       <c r="U12" t="n">
-        <v>271.5034949211869</v>
+        <v>271.503494919912</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002427292512138695</v>
+        <v>-0.002427292512132957</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0004045487520231159</v>
+        <v>-0.0004045487520221595</v>
       </c>
       <c r="H13" t="n">
-        <v>-383.5122169179139</v>
+        <v>-383.5122169170072</v>
       </c>
       <c r="I13" t="n">
-        <v>-80909.75040462318</v>
+        <v>-80909.75040443189</v>
       </c>
       <c r="J13" t="n">
-        <v>383.512216917914</v>
+        <v>383.5122169170072</v>
       </c>
       <c r="K13" t="n">
-        <v>28.44961730194387</v>
+        <v>28.44961730178392</v>
       </c>
       <c r="L13" t="n">
-        <v>309.8323268187096</v>
+        <v>309.8323268183962</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3176639268991371</v>
+        <v>0.3176639268975212</v>
       </c>
       <c r="N13" t="n">
-        <v>-621.847262664136</v>
+        <v>-621.8472626633337</v>
       </c>
       <c r="O13" t="n">
-        <v>45.52697080838436</v>
+        <v>45.52697080804194</v>
       </c>
       <c r="P13" t="n">
-        <v>-383.512216917914</v>
+        <v>-383.5122169170072</v>
       </c>
       <c r="Q13" t="n">
-        <v>-28.44961730194387</v>
+        <v>-28.44961730178392</v>
       </c>
       <c r="R13" t="n">
-        <v>-159.8323268187096</v>
+        <v>-159.8323268183962</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3176639268991371</v>
+        <v>-0.3176639268975212</v>
       </c>
       <c r="T13" t="n">
-        <v>-787.1466982481188</v>
+        <v>-787.1466982470427</v>
       </c>
       <c r="U13" t="n">
-        <v>125.1707330032788</v>
+        <v>125.1707330026616</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0006447200771059376</v>
+        <v>0.0006447200771039496</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001074533461843229</v>
+        <v>0.0001074533461839916</v>
       </c>
       <c r="H14" t="n">
-        <v>101.8657721827381</v>
+        <v>101.865772182424</v>
       </c>
       <c r="I14" t="n">
-        <v>21490.66923686459</v>
+        <v>21490.66923679832</v>
       </c>
       <c r="J14" t="n">
-        <v>-101.8657721827385</v>
+        <v>-101.8657721824238</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.043036175046467</v>
+        <v>-5.043036174986128</v>
       </c>
       <c r="L14" t="n">
-        <v>86.80693093268656</v>
+        <v>86.80693093240026</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05581601372180611</v>
+        <v>0.05581601372114864</v>
       </c>
       <c r="N14" t="n">
-        <v>-130.2789316856852</v>
+        <v>-130.2789316849898</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.141856228976621</v>
+        <v>-2.14185622884861</v>
       </c>
       <c r="P14" t="n">
-        <v>101.8657721827385</v>
+        <v>101.8657721824238</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.043036175046467</v>
+        <v>5.043036174986128</v>
       </c>
       <c r="R14" t="n">
-        <v>-86.80693093268656</v>
+        <v>-86.80693093240026</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.05581601372180611</v>
+        <v>-0.05581601372114864</v>
       </c>
       <c r="T14" t="n">
-        <v>-390.5626539104323</v>
+        <v>-390.5626539094091</v>
       </c>
       <c r="U14" t="n">
-        <v>-28.11636082130212</v>
+        <v>-28.11636082106827</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0005432565124295595</v>
+        <v>0.0005432565124276027</v>
       </c>
       <c r="G15" t="n">
-        <v>9.054275207159325e-05</v>
+        <v>9.054275207126712e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>85.8345289638704</v>
+        <v>85.83452896356123</v>
       </c>
       <c r="I15" t="n">
-        <v>18108.55041431865</v>
+        <v>18108.55041425342</v>
       </c>
       <c r="J15" t="n">
-        <v>-85.8345289638703</v>
+        <v>-85.8345289635613</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.049790589604982</v>
+        <v>-5.049790589544841</v>
       </c>
       <c r="L15" t="n">
-        <v>68.77545928012933</v>
+        <v>68.77545927978912</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05592852579880625</v>
+        <v>0.05592852579814611</v>
       </c>
       <c r="N15" t="n">
-        <v>-36.84432557314722</v>
+        <v>-36.84432557254138</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.174876591940688</v>
+        <v>-2.174876591812904</v>
       </c>
       <c r="P15" t="n">
-        <v>85.8345289638703</v>
+        <v>85.8345289635613</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.049790589604982</v>
+        <v>5.049790589544841</v>
       </c>
       <c r="R15" t="n">
-        <v>-68.77545928012933</v>
+        <v>-68.77545927978912</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.05592852579880625</v>
+        <v>-0.05592852579814611</v>
       </c>
       <c r="T15" t="n">
-        <v>-375.8084301076287</v>
+        <v>-375.8084301061951</v>
       </c>
       <c r="U15" t="n">
-        <v>-28.12386694568909</v>
+        <v>-28.12386694545614</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005350612470926223</v>
+        <v>-0.0005350612470906464</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.917687451543705e-05</v>
+        <v>-8.917687451510774e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>-84.53967704063432</v>
+        <v>-84.53967704032213</v>
       </c>
       <c r="I16" t="n">
-        <v>-17835.37490308741</v>
+        <v>-17835.37490302155</v>
       </c>
       <c r="J16" t="n">
-        <v>84.53967704063439</v>
+        <v>84.5396770403222</v>
       </c>
       <c r="K16" t="n">
-        <v>5.976631614471387</v>
+        <v>5.976631614420171</v>
       </c>
       <c r="L16" t="n">
-        <v>171.1038425462361</v>
+        <v>171.1038425458343</v>
       </c>
       <c r="M16" t="n">
-        <v>0.05544883212377627</v>
+        <v>0.05544883212311946</v>
       </c>
       <c r="N16" t="n">
-        <v>-209.6149089039063</v>
+        <v>-209.6149089029861</v>
       </c>
       <c r="O16" t="n">
-        <v>1.765111141198304</v>
+        <v>1.765111141116449</v>
       </c>
       <c r="P16" t="n">
-        <v>-84.53967704063439</v>
+        <v>-84.5396770403222</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.976631614471387</v>
+        <v>-5.976631614420171</v>
       </c>
       <c r="R16" t="n">
-        <v>-21.10384254623614</v>
+        <v>-21.10384254583424</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.05544883212377627</v>
+        <v>-0.05544883212311946</v>
       </c>
       <c r="T16" t="n">
-        <v>-367.0081463735096</v>
+        <v>-367.0081463720166</v>
       </c>
       <c r="U16" t="n">
-        <v>34.0946785456299</v>
+        <v>34.09467854540435</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.00065291534244288</v>
+        <v>-0.0006529153424409059</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.00010881922374048</v>
+        <v>-0.000108819223740151</v>
       </c>
       <c r="H17" t="n">
-        <v>-103.160624105975</v>
+        <v>-103.1606241056631</v>
       </c>
       <c r="I17" t="n">
-        <v>-21763.844748096</v>
+        <v>-21763.84474803019</v>
       </c>
       <c r="J17" t="n">
-        <v>103.1606241059749</v>
+        <v>103.1606241056634</v>
       </c>
       <c r="K17" t="n">
-        <v>4.116195150128135</v>
+        <v>4.116195150090789</v>
       </c>
       <c r="L17" t="n">
-        <v>173.3137672415419</v>
+        <v>173.3137672412556</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05577790265873905</v>
+        <v>0.05577790265808225</v>
       </c>
       <c r="N17" t="n">
-        <v>-221.6594246679597</v>
+        <v>-221.6594246672689</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.807193706483986</v>
+        <v>-7.807193706494331</v>
       </c>
       <c r="P17" t="n">
-        <v>-103.1606241059749</v>
+        <v>-103.1606241056634</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.116195150128135</v>
+        <v>-4.116195150090789</v>
       </c>
       <c r="R17" t="n">
-        <v>-23.31376724154188</v>
+        <v>-23.3137672412556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.05577790265873905</v>
+        <v>-0.05577790265808225</v>
       </c>
       <c r="T17" t="n">
-        <v>-368.2231787812889</v>
+        <v>-368.2231787802656</v>
       </c>
       <c r="U17" t="n">
-        <v>32.50436460725291</v>
+        <v>32.50436460703907</v>
       </c>
     </row>
     <row r="18">
@@ -2693,37 +2693,37 @@
         <v>12.51052828051979</v>
       </c>
       <c r="K18" t="n">
-        <v>-20.32886904325267</v>
+        <v>-20.32886904320844</v>
       </c>
       <c r="L18" t="n">
-        <v>-29.95136551383587</v>
+        <v>-29.95136551373676</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1399243619682065</v>
+        <v>-0.1399243619677715</v>
       </c>
       <c r="N18" t="n">
-        <v>119.8137459617613</v>
+        <v>119.8137459613649</v>
       </c>
       <c r="O18" t="n">
-        <v>-64.67502263192773</v>
+        <v>-64.67502263175106</v>
       </c>
       <c r="P18" t="n">
         <v>-12.51052828051979</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.32886904325267</v>
+        <v>20.32886904320844</v>
       </c>
       <c r="R18" t="n">
-        <v>29.95136551383587</v>
+        <v>29.95136551373676</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1399243619682065</v>
+        <v>0.1399243619677715</v>
       </c>
       <c r="T18" t="n">
-        <v>119.7971781489256</v>
+        <v>119.7971781485292</v>
       </c>
       <c r="U18" t="n">
-        <v>-97.95592971409337</v>
+        <v>-97.95592971391648</v>
       </c>
     </row>
     <row r="19">
@@ -2745,52 +2745,52 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0001740734582384995</v>
+        <v>-0.0001740734582367232</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.175918227981244e-05</v>
+        <v>-2.175918227959039e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-20.62770480126219</v>
+        <v>-20.62770480105169</v>
       </c>
       <c r="I19" t="n">
-        <v>-4351.836455962487</v>
+        <v>-4351.836455918078</v>
       </c>
       <c r="J19" t="n">
-        <v>20.62770480127074</v>
+        <v>20.62770480103791</v>
       </c>
       <c r="K19" t="n">
-        <v>32.77195795073811</v>
+        <v>32.77195795069392</v>
       </c>
       <c r="L19" t="n">
-        <v>-526.4796256073413</v>
+        <v>-526.4796256065976</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1674336878040798</v>
+        <v>-0.1674336878034616</v>
       </c>
       <c r="N19" t="n">
-        <v>2151.873693470231</v>
+        <v>2151.8736934672</v>
       </c>
       <c r="O19" t="n">
-        <v>97.65662236346988</v>
+        <v>97.65662236329339</v>
       </c>
       <c r="P19" t="n">
-        <v>-20.62770480127074</v>
+        <v>-20.62770480103791</v>
       </c>
       <c r="Q19" t="n">
-        <v>-32.77195795073811</v>
+        <v>-32.77195795069392</v>
       </c>
       <c r="R19" t="n">
-        <v>526.4796256073413</v>
+        <v>526.4796256065976</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1674336878040798</v>
+        <v>0.1674336878034616</v>
       </c>
       <c r="T19" t="n">
-        <v>2059.963311388499</v>
+        <v>2059.96331138558</v>
       </c>
       <c r="U19" t="n">
-        <v>164.519041242435</v>
+        <v>164.5190412422579</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0002293761867013244</v>
+        <v>0.0002293761867009914</v>
       </c>
       <c r="G20" t="n">
-        <v>2.867202333766555e-05</v>
+        <v>2.867202333762392e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>27.18107812410694</v>
+        <v>27.18107812406748</v>
       </c>
       <c r="I20" t="n">
-        <v>5734.40466753311</v>
+        <v>5734.404667524784</v>
       </c>
       <c r="J20" t="n">
-        <v>-27.18107812410744</v>
+        <v>-27.18107812406743</v>
       </c>
       <c r="K20" t="n">
-        <v>-120.3262129092477</v>
+        <v>-120.3262129092034</v>
       </c>
       <c r="L20" t="n">
-        <v>-38.31274245313044</v>
+        <v>-38.31274245297931</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0375055962292552</v>
+        <v>0.03750559622947636</v>
       </c>
       <c r="N20" t="n">
-        <v>148.6013299065843</v>
+        <v>148.6013299059929</v>
       </c>
       <c r="O20" t="n">
-        <v>-164.5905998150671</v>
+        <v>-164.5905998148902</v>
       </c>
       <c r="P20" t="n">
-        <v>27.18107812410744</v>
+        <v>27.18107812406743</v>
       </c>
       <c r="Q20" t="n">
-        <v>-79.67378709075228</v>
+        <v>-79.67378709079662</v>
       </c>
       <c r="R20" t="n">
-        <v>38.31274245313044</v>
+        <v>38.31274245297931</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0375055962292552</v>
+        <v>-0.03750559622947636</v>
       </c>
       <c r="T20" t="n">
-        <v>157.9006097184592</v>
+        <v>157.9006097178416</v>
       </c>
       <c r="U20" t="n">
-        <v>1.980896541085798</v>
+        <v>1.980896541263149</v>
       </c>
     </row>
     <row r="21">
@@ -2894,37 +2894,37 @@
         <v>-125.2777544300188</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.751465002060866</v>
+        <v>-7.751465002016882</v>
       </c>
       <c r="L21" t="n">
-        <v>-505.9794931523545</v>
+        <v>-505.9794931517395</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1853487793900617</v>
+        <v>-0.185348779389393</v>
       </c>
       <c r="N21" t="n">
-        <v>2024.094570699891</v>
+        <v>2024.094570697432</v>
       </c>
       <c r="O21" t="n">
-        <v>2.250969248613565</v>
+        <v>2.250969248789389</v>
       </c>
       <c r="P21" t="n">
         <v>125.2777544300188</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.751465002060866</v>
+        <v>7.751465002016882</v>
       </c>
       <c r="R21" t="n">
-        <v>505.9794931523545</v>
+        <v>505.9794931517395</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1853487793900617</v>
+        <v>0.185348779389393</v>
       </c>
       <c r="T21" t="n">
-        <v>2023.741374518944</v>
+        <v>2023.741374516484</v>
       </c>
       <c r="U21" t="n">
-        <v>-64.26268926510053</v>
+        <v>-64.26268926492449</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.115239550303798e-05</v>
+        <v>-7.115239550292696e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.894049437879747e-06</v>
+        <v>-8.89404943786587e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.431558867110001</v>
+        <v>-8.431558867096845</v>
       </c>
       <c r="I22" t="n">
-        <v>-1778.809887575949</v>
+        <v>-1778.809887573174</v>
       </c>
       <c r="J22" t="n">
-        <v>8.431558867116109</v>
+        <v>8.431558867094282</v>
       </c>
       <c r="K22" t="n">
-        <v>5.907094219596843</v>
+        <v>5.907094219625492</v>
       </c>
       <c r="L22" t="n">
-        <v>-37.44745119604755</v>
+        <v>-37.44745119590817</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7264335376093496</v>
+        <v>-0.7264335376073403</v>
       </c>
       <c r="N22" t="n">
-        <v>149.7634828591127</v>
+        <v>149.7634828585553</v>
       </c>
       <c r="O22" t="n">
-        <v>34.86921080075126</v>
+        <v>34.86921080087586</v>
       </c>
       <c r="P22" t="n">
-        <v>-8.431558867116109</v>
+        <v>-8.431558867094282</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.907094219596843</v>
+        <v>-5.907094219625492</v>
       </c>
       <c r="R22" t="n">
-        <v>37.44745119604755</v>
+        <v>37.44745119590817</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7264335376093496</v>
+        <v>0.7264335376073403</v>
       </c>
       <c r="T22" t="n">
-        <v>149.8161267092676</v>
+        <v>149.81612670871</v>
       </c>
       <c r="U22" t="n">
-        <v>12.38754295602348</v>
+        <v>12.38754295612807</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001624633540233233</v>
+        <v>0.00162463354023501</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0002030791925291542</v>
+        <v>0.0002030791925293762</v>
       </c>
       <c r="H23" t="n">
-        <v>192.5190745176382</v>
+        <v>192.5190745178487</v>
       </c>
       <c r="I23" t="n">
-        <v>40615.83850583083</v>
+        <v>40615.83850587524</v>
       </c>
       <c r="J23" t="n">
-        <v>-192.519074517535</v>
+        <v>-192.5190745177679</v>
       </c>
       <c r="K23" t="n">
-        <v>66.80885951796712</v>
+        <v>66.80885951768202</v>
       </c>
       <c r="L23" t="n">
-        <v>-357.2856302062857</v>
+        <v>-357.2856302055961</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.09736451574442088</v>
+        <v>-0.09736451574406163</v>
       </c>
       <c r="N23" t="n">
-        <v>1908.094331495953</v>
+        <v>1908.094331492271</v>
       </c>
       <c r="O23" t="n">
-        <v>169.9159291478577</v>
+        <v>169.9159291470286</v>
       </c>
       <c r="P23" t="n">
-        <v>192.519074517535</v>
+        <v>192.5190745177679</v>
       </c>
       <c r="Q23" t="n">
-        <v>-66.80885951796712</v>
+        <v>-66.80885951768202</v>
       </c>
       <c r="R23" t="n">
-        <v>357.2856302062857</v>
+        <v>357.2856302055961</v>
       </c>
       <c r="S23" t="n">
-        <v>0.09736451574442088</v>
+        <v>0.09736451574406163</v>
       </c>
       <c r="T23" t="n">
-        <v>950.1907101543316</v>
+        <v>950.1907101524979</v>
       </c>
       <c r="U23" t="n">
-        <v>364.5549469958794</v>
+        <v>364.5549469944276</v>
       </c>
     </row>
     <row r="24">
@@ -3080,52 +3080,52 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>1.503836553151672e-05</v>
+        <v>1.503836553162774e-05</v>
       </c>
       <c r="G24" t="n">
-        <v>1.87979569143959e-06</v>
+        <v>1.879795691453467e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>1.782046315484731</v>
+        <v>1.782046315497887</v>
       </c>
       <c r="I24" t="n">
-        <v>375.9591382879179</v>
+        <v>375.9591382906935</v>
       </c>
       <c r="J24" t="n">
         <v>-1.782046315493062</v>
       </c>
       <c r="K24" t="n">
-        <v>-50.12585500939213</v>
+        <v>-50.12585500958915</v>
       </c>
       <c r="L24" t="n">
-        <v>-37.37605177429701</v>
+        <v>-37.37605177413763</v>
       </c>
       <c r="M24" t="n">
-        <v>1.113355533694651</v>
+        <v>1.113355533693104</v>
       </c>
       <c r="N24" t="n">
-        <v>99.01739029716171</v>
+        <v>99.01739029673753</v>
       </c>
       <c r="O24" t="n">
-        <v>191.0147515809632</v>
+        <v>191.0147515798436</v>
       </c>
       <c r="P24" t="n">
         <v>1.782046315493062</v>
       </c>
       <c r="Q24" t="n">
-        <v>-149.8741449906079</v>
+        <v>-149.8741449904109</v>
       </c>
       <c r="R24" t="n">
-        <v>37.37605177429701</v>
+        <v>37.37605177413763</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.113355533694651</v>
+        <v>-1.113355533693104</v>
       </c>
       <c r="T24" t="n">
-        <v>199.9910238972143</v>
+        <v>199.9910238963635</v>
       </c>
       <c r="U24" t="n">
-        <v>207.9784083438993</v>
+        <v>207.9784083434427</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00107648660289783</v>
+        <v>0.001076486602899607</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001345608253622288</v>
+        <v>0.0001345608253624508</v>
       </c>
       <c r="H25" t="n">
-        <v>127.5636624433929</v>
+        <v>127.5636624436034</v>
       </c>
       <c r="I25" t="n">
-        <v>26912.16507244576</v>
+        <v>26912.16507249017</v>
       </c>
       <c r="J25" t="n">
-        <v>-127.5636624434264</v>
+        <v>-127.5636624436593</v>
       </c>
       <c r="K25" t="n">
-        <v>18.39017452808879</v>
+        <v>18.3901745281176</v>
       </c>
       <c r="L25" t="n">
-        <v>-431.7413901167282</v>
+        <v>-431.74139011613</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.291443342186532</v>
+        <v>-0.2914433421853525</v>
       </c>
       <c r="N25" t="n">
-        <v>1726.358908335142</v>
+        <v>1726.358908332749</v>
       </c>
       <c r="O25" t="n">
-        <v>112.3335280625733</v>
+        <v>112.3335280626782</v>
       </c>
       <c r="P25" t="n">
-        <v>127.5636624434264</v>
+        <v>127.5636624436593</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.39017452808879</v>
+        <v>-18.3901745281176</v>
       </c>
       <c r="R25" t="n">
-        <v>431.7413901167282</v>
+        <v>431.74139011613</v>
       </c>
       <c r="S25" t="n">
-        <v>0.291443342186532</v>
+        <v>0.2914433421853525</v>
       </c>
       <c r="T25" t="n">
-        <v>1727.572212598684</v>
+        <v>1727.57221259629</v>
       </c>
       <c r="U25" t="n">
-        <v>34.78786816213679</v>
+        <v>34.78786816226227</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0001051822652723411</v>
+        <v>-0.0001051822652722301</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.314778315904264e-05</v>
+        <v>-1.314778315902876e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.46409843477242</v>
+        <v>-12.46409843475926</v>
       </c>
       <c r="I26" t="n">
-        <v>-2629.556631808527</v>
+        <v>-2629.556631805752</v>
       </c>
       <c r="J26" t="n">
-        <v>12.46409843477886</v>
+        <v>12.46409843476431</v>
       </c>
       <c r="K26" t="n">
-        <v>18.50839878814895</v>
+        <v>18.50839878808893</v>
       </c>
       <c r="L26" t="n">
-        <v>-21.6335511203928</v>
+        <v>-21.63355112027549</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.09264667315167774</v>
+        <v>-0.0926466731507235</v>
       </c>
       <c r="N26" t="n">
-        <v>86.54154973783145</v>
+        <v>86.54154973736216</v>
       </c>
       <c r="O26" t="n">
-        <v>90.66689582742492</v>
+        <v>90.66689582718391</v>
       </c>
       <c r="P26" t="n">
-        <v>-12.46409843477886</v>
+        <v>-12.46409843476431</v>
       </c>
       <c r="Q26" t="n">
-        <v>-18.50839878814895</v>
+        <v>-18.50839878808893</v>
       </c>
       <c r="R26" t="n">
-        <v>21.6335511203928</v>
+        <v>21.63355112027549</v>
       </c>
       <c r="S26" t="n">
-        <v>0.09264667315167774</v>
+        <v>0.0926466731507235</v>
       </c>
       <c r="T26" t="n">
-        <v>86.52685922531087</v>
+        <v>86.52685922484176</v>
       </c>
       <c r="U26" t="n">
-        <v>57.4002944777676</v>
+        <v>57.40029447752659</v>
       </c>
     </row>
     <row r="27">
@@ -3281,52 +3281,52 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>0.001536654425073891</v>
+        <v>0.001536654425072115</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0001920818031342364</v>
+        <v>0.0001920818031340144</v>
       </c>
       <c r="H27" t="n">
-        <v>182.0935493712561</v>
+        <v>182.0935493710456</v>
       </c>
       <c r="I27" t="n">
-        <v>38416.36062684728</v>
+        <v>38416.36062680287</v>
       </c>
       <c r="J27" t="n">
-        <v>-182.0935493712313</v>
+        <v>-182.0935493709985</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.959963132255233</v>
+        <v>-5.959963132195512</v>
       </c>
       <c r="L27" t="n">
-        <v>-274.7542534589803</v>
+        <v>-274.7542534582191</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1276615161922457</v>
+        <v>-0.1276615161915826</v>
       </c>
       <c r="N27" t="n">
-        <v>1115.269199426445</v>
+        <v>1115.269199423327</v>
       </c>
       <c r="O27" t="n">
-        <v>-57.08303073182913</v>
+        <v>-57.08303073159067</v>
       </c>
       <c r="P27" t="n">
-        <v>182.0935493712313</v>
+        <v>182.0935493709985</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.959963132255233</v>
+        <v>5.959963132195512</v>
       </c>
       <c r="R27" t="n">
-        <v>274.7542534589803</v>
+        <v>274.7542534582191</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1276615161922457</v>
+        <v>0.1276615161915826</v>
       </c>
       <c r="T27" t="n">
-        <v>1082.764828245398</v>
+        <v>1082.764828242425</v>
       </c>
       <c r="U27" t="n">
-        <v>9.403325673787522</v>
+        <v>9.403325674026803</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>5.565559936049347e-05</v>
+        <v>5.565559936138165e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>6.956949920061684e-06</v>
+        <v>6.956949920172706e-06</v>
       </c>
       <c r="H28" t="n">
-        <v>6.595188524218476</v>
+        <v>6.595188524323725</v>
       </c>
       <c r="I28" t="n">
-        <v>1391.389984012337</v>
+        <v>1391.389984034541</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.595188524224795</v>
+        <v>-6.595188524341211</v>
       </c>
       <c r="K28" t="n">
-        <v>-81.51814703985838</v>
+        <v>-81.51814703991795</v>
       </c>
       <c r="L28" t="n">
-        <v>-28.75694233787942</v>
+        <v>-28.75694233772689</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02072194792745929</v>
+        <v>-0.0207219479267835</v>
       </c>
       <c r="N28" t="n">
-        <v>112.8281492507293</v>
+        <v>112.8281492501357</v>
       </c>
       <c r="O28" t="n">
-        <v>-9.458774505914647</v>
+        <v>-9.458774506152935</v>
       </c>
       <c r="P28" t="n">
-        <v>6.595188524224795</v>
+        <v>6.595188524341211</v>
       </c>
       <c r="Q28" t="n">
-        <v>-118.4818529601416</v>
+        <v>-118.4818529600821</v>
       </c>
       <c r="R28" t="n">
-        <v>28.75694233787942</v>
+        <v>28.75694233772689</v>
       </c>
       <c r="S28" t="n">
-        <v>0.02072194792745929</v>
+        <v>0.0207219479267835</v>
       </c>
       <c r="T28" t="n">
-        <v>117.227389452306</v>
+        <v>117.2273894516794</v>
       </c>
       <c r="U28" t="n">
-        <v>157.3135981870485</v>
+        <v>157.3135981868093</v>
       </c>
     </row>
     <row r="29">
@@ -3427,40 +3427,40 @@
         <v>27840.35725365008</v>
       </c>
       <c r="J29" t="n">
-        <v>-131.9632933824323</v>
+        <v>-131.9632933821995</v>
       </c>
       <c r="K29" t="n">
-        <v>30.92861067598463</v>
+        <v>30.92861067592477</v>
       </c>
       <c r="L29" t="n">
-        <v>-251.5946504740586</v>
+        <v>-251.5946504736163</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1361498444885867</v>
+        <v>-0.1361498444878597</v>
       </c>
       <c r="N29" t="n">
-        <v>1008.826844864008</v>
+        <v>1008.826844862238</v>
       </c>
       <c r="O29" t="n">
-        <v>157.0517121628106</v>
+        <v>157.0517121625711</v>
       </c>
       <c r="P29" t="n">
-        <v>131.9632933824323</v>
+        <v>131.9632933821995</v>
       </c>
       <c r="Q29" t="n">
-        <v>-30.92861067598463</v>
+        <v>-30.92861067592477</v>
       </c>
       <c r="R29" t="n">
-        <v>251.5946504740586</v>
+        <v>251.5946504736163</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1361498444885867</v>
+        <v>0.1361498444878597</v>
       </c>
       <c r="T29" t="n">
-        <v>1003.930358928461</v>
+        <v>1003.930358926692</v>
       </c>
       <c r="U29" t="n">
-        <v>90.37717324506605</v>
+        <v>90.37717324482674</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001054896281658113</v>
+        <v>-0.0001054896281654782</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.318620352072641e-05</v>
+        <v>-1.318620352068478e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.50052093764864</v>
+        <v>-12.50052093760917</v>
       </c>
       <c r="I30" t="n">
-        <v>-2637.240704145283</v>
+        <v>-2637.240704136956</v>
       </c>
       <c r="J30" t="n">
-        <v>12.50052093763952</v>
+        <v>12.50052093761042</v>
       </c>
       <c r="K30" t="n">
-        <v>5.061241533242764</v>
+        <v>5.061241533179555</v>
       </c>
       <c r="L30" t="n">
-        <v>-7.019509614610334</v>
+        <v>-7.019509614552399</v>
       </c>
       <c r="M30" t="n">
-        <v>0.02083464748736136</v>
+        <v>0.02083464748759228</v>
       </c>
       <c r="N30" t="n">
-        <v>28.0758158752352</v>
+        <v>28.07581587500367</v>
       </c>
       <c r="O30" t="n">
-        <v>36.90020666281453</v>
+        <v>36.90020666256169</v>
       </c>
       <c r="P30" t="n">
-        <v>-12.50052093763952</v>
+        <v>-12.50052093761042</v>
       </c>
       <c r="Q30" t="n">
-        <v>-5.061241533242764</v>
+        <v>-5.061241533179555</v>
       </c>
       <c r="R30" t="n">
-        <v>7.019509614610334</v>
+        <v>7.019509614552399</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.02083464748736136</v>
+        <v>-0.02083464748759228</v>
       </c>
       <c r="T30" t="n">
-        <v>28.08026104164746</v>
+        <v>28.08026104141551</v>
       </c>
       <c r="U30" t="n">
-        <v>3.5897256031285</v>
+        <v>3.589725602874751</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0006230945216323391</v>
+        <v>0.0006230945216358919</v>
       </c>
       <c r="G31" t="n">
-        <v>7.788681520404239e-05</v>
+        <v>7.788681520448648e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>73.83670081343219</v>
+        <v>73.83670081385318</v>
       </c>
       <c r="I31" t="n">
-        <v>15577.36304080848</v>
+        <v>15577.36304089729</v>
       </c>
       <c r="J31" t="n">
-        <v>-73.83670081337914</v>
+        <v>-73.8367008138448</v>
       </c>
       <c r="K31" t="n">
-        <v>7.450730348027498</v>
+        <v>7.450730348091383</v>
       </c>
       <c r="L31" t="n">
-        <v>-92.85403857848101</v>
+        <v>-92.85403857811413</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.04360590404102432</v>
+        <v>-0.04360590404072028</v>
       </c>
       <c r="N31" t="n">
-        <v>375.8292647551177</v>
+        <v>375.8292647536747</v>
       </c>
       <c r="O31" t="n">
-        <v>-3.533797077329041</v>
+        <v>-3.533797077073132</v>
       </c>
       <c r="P31" t="n">
-        <v>73.83670081337914</v>
+        <v>73.8367008138448</v>
       </c>
       <c r="Q31" t="n">
-        <v>-7.450730348027498</v>
+        <v>-7.450730348091383</v>
       </c>
       <c r="R31" t="n">
-        <v>92.85403857848101</v>
+        <v>92.85403857811413</v>
       </c>
       <c r="S31" t="n">
-        <v>0.04360590404102432</v>
+        <v>0.04360590404072028</v>
       </c>
       <c r="T31" t="n">
-        <v>367.0030438727302</v>
+        <v>367.0030438712382</v>
       </c>
       <c r="U31" t="n">
-        <v>63.13963986154931</v>
+        <v>63.13963986180471</v>
       </c>
     </row>
     <row r="32">
@@ -3631,37 +3631,37 @@
         <v>-13.42736196250189</v>
       </c>
       <c r="K32" t="n">
-        <v>-94.9405433593156</v>
+        <v>-94.94054335937926</v>
       </c>
       <c r="L32" t="n">
-        <v>-8.314361537847095</v>
+        <v>-8.314361537792287</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.005102500778984165</v>
+        <v>-0.005102500778656233</v>
       </c>
       <c r="N32" t="n">
-        <v>34.0510726415895</v>
+        <v>34.05107264136433</v>
       </c>
       <c r="O32" t="n">
-        <v>-63.08419102942511</v>
+        <v>-63.08419102967977</v>
       </c>
       <c r="P32" t="n">
         <v>13.42736196250189</v>
       </c>
       <c r="Q32" t="n">
-        <v>-105.0594566406844</v>
+        <v>-105.0594566406207</v>
       </c>
       <c r="R32" t="n">
-        <v>8.314361537847095</v>
+        <v>8.314361537792287</v>
       </c>
       <c r="S32" t="n">
-        <v>0.005102500778984165</v>
+        <v>0.005102500778656233</v>
       </c>
       <c r="T32" t="n">
-        <v>32.46381966118725</v>
+        <v>32.46381966097396</v>
       </c>
       <c r="U32" t="n">
-        <v>103.5598441549012</v>
+        <v>103.5598441546466</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0006898370413406241</v>
+        <v>0.0006898370413459531</v>
       </c>
       <c r="G33" t="n">
-        <v>8.622963016757801e-05</v>
+        <v>8.622963016824414e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>81.74568939886396</v>
+        <v>81.74568939949545</v>
       </c>
       <c r="I33" t="n">
-        <v>17245.9260335156</v>
+        <v>17245.92603364883</v>
       </c>
       <c r="J33" t="n">
-        <v>-81.74568939884193</v>
+        <v>-81.74568939954042</v>
       </c>
       <c r="K33" t="n">
-        <v>17.54355711266726</v>
+        <v>17.54355711260374</v>
       </c>
       <c r="L33" t="n">
-        <v>-94.84626256812794</v>
+        <v>-94.84626256787126</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.04054494606638104</v>
+        <v>-0.04054494606610064</v>
       </c>
       <c r="N33" t="n">
-        <v>368.2282812820681</v>
+        <v>368.2282812810421</v>
       </c>
       <c r="O33" t="n">
-        <v>103.5040662522431</v>
+        <v>103.504066251989</v>
       </c>
       <c r="P33" t="n">
-        <v>81.74568939884193</v>
+        <v>81.74568939954042</v>
       </c>
       <c r="Q33" t="n">
-        <v>-17.54355711266726</v>
+        <v>-17.54355711260374</v>
       </c>
       <c r="R33" t="n">
-        <v>94.84626256812794</v>
+        <v>94.84626256787126</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04054494606638104</v>
+        <v>0.04054494606610064</v>
       </c>
       <c r="T33" t="n">
-        <v>390.5418192629554</v>
+        <v>390.5418192619279</v>
       </c>
       <c r="U33" t="n">
-        <v>36.84439064909469</v>
+        <v>36.84439064884054</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001455921596789192</v>
+        <v>0.001455921596786739</v>
       </c>
       <c r="H2" t="n">
-        <v>1380.213673756154</v>
+        <v>1380.213673753829</v>
       </c>
       <c r="I2" t="n">
-        <v>291184.3193578384</v>
+        <v>291184.3193573478</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.757925951556457</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1624422723423497</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="R2" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03630395006721086</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="T2" t="n">
-        <v>0.609806490401359</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.005111413036285996</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1624422723423497</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3.757925951556457</v>
+        <v>-3.757925951552276</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.005111413036285996</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.609806490401359</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.03630395006721086</v>
+        <v>0.03630395006709138</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1380.213673756154</v>
+        <v>-1380.213673753829</v>
       </c>
       <c r="AI2" t="n">
-        <v>-13.20417079471022</v>
+        <v>-13.20417079465767</v>
       </c>
       <c r="AJ2" t="n">
-        <v>475.6982651535872</v>
+        <v>475.6982651531055</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0145478678725063</v>
+        <v>0.01454786787215924</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1878.351598357767</v>
+        <v>-1878.351598355772</v>
       </c>
       <c r="AM2" t="n">
-        <v>-66.47743543386669</v>
+        <v>-66.4774354336206</v>
       </c>
       <c r="AN2" t="n">
-        <v>1380.213673756154</v>
+        <v>1380.213673753829</v>
       </c>
       <c r="AO2" t="n">
-        <v>13.20417079471022</v>
+        <v>13.20417079465767</v>
       </c>
       <c r="AP2" t="n">
-        <v>-475.6982651535872</v>
+        <v>-475.6982651531055</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.0145478678725063</v>
+        <v>-0.01454786787215924</v>
       </c>
       <c r="AR2" t="n">
-        <v>-975.8379925637557</v>
+        <v>-975.8379925628601</v>
       </c>
       <c r="AS2" t="n">
-        <v>-12.74758933439462</v>
+        <v>-12.74758933432537</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001030760455962304</v>
+        <v>0.001030760455960402</v>
       </c>
       <c r="H3" t="n">
-        <v>977.1609122522644</v>
+        <v>977.1609122504611</v>
       </c>
       <c r="I3" t="n">
-        <v>206152.0911924609</v>
+        <v>206152.0911920804</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.723395957228697</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.162336698264033</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03628902410970122</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6753566419540323</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.03509421220940796</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.162336698264033</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="AD3" t="n">
-        <v>-3.723395957228697</v>
+        <v>-3.723395957223965</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.03509421220940796</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6753566419540323</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.03628902410970122</v>
+        <v>0.03628902410958178</v>
       </c>
       <c r="AH3" t="n">
-        <v>-977.1609122522647</v>
+        <v>-977.1609122504613</v>
       </c>
       <c r="AI3" t="n">
-        <v>-13.18917439728258</v>
+        <v>-13.18917439722999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>418.6737544037614</v>
+        <v>418.6737544032946</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0998835270575457</v>
+        <v>0.0998835270571985</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1755.785178257268</v>
+        <v>-1755.785178255167</v>
       </c>
       <c r="AM3" t="n">
-        <v>-66.42140103302664</v>
+        <v>-66.42140103278049</v>
       </c>
       <c r="AN3" t="n">
-        <v>977.1609122522647</v>
+        <v>977.1609122504613</v>
       </c>
       <c r="AO3" t="n">
-        <v>13.18917439728258</v>
+        <v>13.18917439722999</v>
       </c>
       <c r="AP3" t="n">
-        <v>-418.6737544037614</v>
+        <v>-418.6737544032946</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0998835270575457</v>
+        <v>-0.0998835270571985</v>
       </c>
       <c r="AR3" t="n">
-        <v>-756.2573481653003</v>
+        <v>-756.2573481646002</v>
       </c>
       <c r="AS3" t="n">
-        <v>-12.71364535066883</v>
+        <v>-12.71364535059946</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001032719886365733</v>
+        <v>-0.001032719886363857</v>
       </c>
       <c r="H4" t="n">
-        <v>-979.0184522747154</v>
+        <v>-979.018452272936</v>
       </c>
       <c r="I4" t="n">
-        <v>-206543.9772731467</v>
+        <v>-206543.9772727713</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.723221883770459</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1923970678424733</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04214837918590374</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5925544959344536</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0251422011950651</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.1923970678424733</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3.723221883770459</v>
+        <v>-3.723221883765729</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0251422011950651</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5925544959344536</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.04214837918590374</v>
+        <v>-0.04214837918573356</v>
       </c>
       <c r="AH4" t="n">
-        <v>979.0184522747155</v>
+        <v>979.0184522729362</v>
       </c>
       <c r="AI4" t="n">
-        <v>16.26814280357464</v>
+        <v>16.26814280349655</v>
       </c>
       <c r="AJ4" t="n">
-        <v>554.9044043385509</v>
+        <v>554.9044043380102</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.07155857263210837</v>
+        <v>-0.07155857263245415</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1953.203540007148</v>
+        <v>-1953.2035400049</v>
       </c>
       <c r="AM4" t="n">
-        <v>79.99422900829268</v>
+        <v>79.99422900793247</v>
       </c>
       <c r="AN4" t="n">
-        <v>-979.0184522747155</v>
+        <v>-979.0184522729362</v>
       </c>
       <c r="AO4" t="n">
-        <v>-16.26814280357464</v>
+        <v>-16.26814280349655</v>
       </c>
       <c r="AP4" t="n">
-        <v>-404.9044043385508</v>
+        <v>-404.9044043380101</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.07155857263210837</v>
+        <v>0.07155857263245415</v>
       </c>
       <c r="AR4" t="n">
-        <v>-926.2228860241569</v>
+        <v>-926.2228860231605</v>
       </c>
       <c r="AS4" t="n">
-        <v>17.61462781315514</v>
+        <v>17.61462781304681</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001453962166385767</v>
+        <v>-0.001453962166383287</v>
       </c>
       <c r="H5" t="n">
-        <v>-1378.356133733707</v>
+        <v>-1378.356133731356</v>
       </c>
       <c r="I5" t="n">
-        <v>-290792.4332771534</v>
+        <v>-290792.4332766574</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.758983147796373</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1926264440291746</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05052610874615139</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6101246851589696</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06503362791350591</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1926264440291746</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3.758983147796373</v>
+        <v>-3.758983147792192</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.06503362791350591</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6101246851589696</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.05052610874615139</v>
+        <v>-0.05052610874595759</v>
       </c>
       <c r="AH5" t="n">
-        <v>1378.356133733707</v>
+        <v>1378.356133731357</v>
       </c>
       <c r="AI5" t="n">
-        <v>10.12520238837771</v>
+        <v>10.12520238831702</v>
       </c>
       <c r="AJ5" t="n">
-        <v>550.7235761054679</v>
+        <v>550.7235761049859</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1850957102153629</v>
+        <v>0.1850957102150153</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1953.662995334041</v>
+        <v>-1953.662995332046</v>
       </c>
       <c r="AM5" t="n">
-        <v>67.76492763728514</v>
+        <v>67.76492763695965</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1378.356133733707</v>
+        <v>-1378.356133731357</v>
       </c>
       <c r="AO5" t="n">
-        <v>-10.12520238837771</v>
+        <v>-10.12520238831702</v>
       </c>
       <c r="AP5" t="n">
-        <v>-400.7235761054679</v>
+        <v>-400.7235761049859</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.1850957102153629</v>
+        <v>-0.1850957102150153</v>
       </c>
       <c r="AR5" t="n">
-        <v>-900.6784612987663</v>
+        <v>-900.678461297869</v>
       </c>
       <c r="AS5" t="n">
-        <v>-7.013713307018918</v>
+        <v>-7.013713307057571</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005343562120822556</v>
+        <v>0.005343562120812355</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008905936868037594</v>
+        <v>0.0008905936868020591</v>
       </c>
       <c r="H6" t="n">
-        <v>844.2828150899639</v>
+        <v>844.282815088352</v>
       </c>
       <c r="I6" t="n">
-        <v>178118.7373607519</v>
+        <v>178118.7373604118</v>
       </c>
       <c r="J6" t="n">
-        <v>3.757925951556457</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1624422723423497</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03630395006721086</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="N6" t="n">
-        <v>0.609806490401359</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.005111413036285996</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="P6" t="n">
-        <v>8.658378534746893</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5437220967409437</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01407909170155771</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.04556477868193153</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="T6" t="n">
-        <v>0.522665028634919</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1550967117146793</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1624422723423497</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.757925951556457</v>
+        <v>-3.757925951552276</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.005111413036285996</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.609806490401359</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03630395006721086</v>
+        <v>0.03630395006709138</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01407909170155771</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5437220967409437</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="AD6" t="n">
-        <v>-8.658378534746893</v>
+        <v>-8.658378534736178</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.1550967117146793</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.522665028634919</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.04556477868193153</v>
+        <v>0.04556477868176344</v>
       </c>
       <c r="AH6" t="n">
-        <v>-844.2828150899641</v>
+        <v>-844.2828150883522</v>
       </c>
       <c r="AI6" t="n">
-        <v>-33.46616407728784</v>
+        <v>-33.46616407719057</v>
       </c>
       <c r="AJ6" t="n">
-        <v>370.7493797667951</v>
+        <v>370.7493797662693</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.4268812347000424</v>
+        <v>0.4268812346987415</v>
       </c>
       <c r="AL6" t="n">
-        <v>-1047.763457593219</v>
+        <v>-1047.763457591656</v>
       </c>
       <c r="AM6" t="n">
-        <v>-107.2515054067568</v>
+        <v>-107.251505406429</v>
       </c>
       <c r="AN6" t="n">
-        <v>844.2828150899641</v>
+        <v>844.2828150883522</v>
       </c>
       <c r="AO6" t="n">
-        <v>33.46616407728784</v>
+        <v>33.46616407719057</v>
       </c>
       <c r="AP6" t="n">
-        <v>-370.7493797667951</v>
+        <v>-370.7493797662693</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.4268812347000424</v>
+        <v>-0.4268812346987415</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1176.732821007551</v>
+        <v>-1176.73282100596</v>
       </c>
       <c r="AS6" t="n">
-        <v>-93.54547905697024</v>
+        <v>-93.54547905671429</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003041978811131388</v>
+        <v>0.003041978811124054</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005069964685218979</v>
+        <v>0.0005069964685206757</v>
       </c>
       <c r="H7" t="n">
-        <v>480.6326521587592</v>
+        <v>480.6326521576005</v>
       </c>
       <c r="I7" t="n">
-        <v>101399.2937043796</v>
+        <v>101399.2937041351</v>
       </c>
       <c r="J7" t="n">
-        <v>3.723395957228697</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="K7" t="n">
-        <v>0.162336698264033</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03628902410970122</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6753566419540323</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.03509421220940796</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="P7" t="n">
-        <v>10.03693211710211</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5436509443454407</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009226541546905213</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.04561220557396294</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8629762354429026</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1753504665297493</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="V7" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="W7" t="n">
-        <v>0.162336698264033</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.723395957228697</v>
+        <v>-3.723395957223965</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.03509421220940796</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6753566419540323</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03628902410970122</v>
+        <v>0.03628902410958178</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.009226541546905213</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5436509443454407</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="AD7" t="n">
-        <v>-10.03693211710211</v>
+        <v>-10.03693211708712</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.1753504665297493</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.8629762354429026</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.04561220557396294</v>
+        <v>0.04561220557379464</v>
       </c>
       <c r="AH7" t="n">
-        <v>-480.6326521587592</v>
+        <v>-480.6326521576007</v>
       </c>
       <c r="AI7" t="n">
-        <v>-33.45060406750243</v>
+        <v>-33.45060406740529</v>
       </c>
       <c r="AJ7" t="n">
-        <v>418.9725901617112</v>
+        <v>418.9725901611122</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.3991908776809715</v>
+        <v>0.3991908776797221</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1395.756269666897</v>
+        <v>-1395.756269664567</v>
       </c>
       <c r="AM7" t="n">
-        <v>-107.2509664860609</v>
+        <v>-107.2509664857333</v>
       </c>
       <c r="AN7" t="n">
-        <v>480.6326521587592</v>
+        <v>480.6326521576007</v>
       </c>
       <c r="AO7" t="n">
-        <v>33.45060406750243</v>
+        <v>33.45060406740529</v>
       </c>
       <c r="AP7" t="n">
-        <v>-418.9725901617112</v>
+        <v>-418.9725901611122</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.3991908776809715</v>
+        <v>-0.3991908776797221</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1118.07927130337</v>
+        <v>-1118.079271302104</v>
       </c>
       <c r="AS7" t="n">
-        <v>-93.45265791895361</v>
+        <v>-93.45265791869829</v>
       </c>
     </row>
     <row r="8">
@@ -4825,43 +4825,43 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.003106655500762689</v>
+        <v>-0.003106655500755174</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0005177759167937815</v>
+        <v>-0.000517775916792529</v>
       </c>
       <c r="H8" t="n">
-        <v>-490.8515691205048</v>
+        <v>-490.8515691193175</v>
       </c>
       <c r="I8" t="n">
-        <v>-103555.1833587563</v>
+        <v>-103555.1833585058</v>
       </c>
       <c r="J8" t="n">
-        <v>3.723221883770459</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1923970678424733</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04214837918590374</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5925544959344536</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0251422011950651</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="P8" t="n">
-        <v>10.03855675064235</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.7997579802044718</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.00930297481895709</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -4873,31 +4873,31 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1923970678424733</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.723221883770459</v>
+        <v>-3.723221883765729</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0251422011950651</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5925544959344536</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.04214837918590374</v>
+        <v>-0.04214837918573356</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.00930297481895709</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.7997579802044718</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="AD8" t="n">
-        <v>-10.03855675064235</v>
+        <v>-10.03855675062735</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -4909,40 +4909,40 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>490.8515691205049</v>
+        <v>490.8515691193177</v>
       </c>
       <c r="AI8" t="n">
-        <v>118.6258911183909</v>
+        <v>118.6258911179426</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1194.29227350357</v>
+        <v>1194.292273501664</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.07155857263210837</v>
+        <v>0.07155857263245415</v>
       </c>
       <c r="AL8" t="n">
-        <v>-2994.386493519215</v>
+        <v>-2994.386493514121</v>
       </c>
       <c r="AM8" t="n">
-        <v>324.6878727576038</v>
+        <v>324.687872756385</v>
       </c>
       <c r="AN8" t="n">
-        <v>-490.8515691205049</v>
+        <v>-490.8515691193177</v>
       </c>
       <c r="AO8" t="n">
-        <v>-118.6258911183909</v>
+        <v>-118.6258911179426</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1044.29227350357</v>
+        <v>-1044.292273501664</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.07155857263210837</v>
+        <v>-0.07155857263245415</v>
       </c>
       <c r="AR8" t="n">
-        <v>-3721.367147502207</v>
+        <v>-3721.36714749586</v>
       </c>
       <c r="AS8" t="n">
-        <v>387.0674739527414</v>
+        <v>387.0674739512706</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.005278885431191272</v>
+        <v>-0.005278885431181244</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0008798142385318787</v>
+        <v>-0.0008798142385302073</v>
       </c>
       <c r="H9" t="n">
-        <v>-834.063898128221</v>
+        <v>-834.0638981266366</v>
       </c>
       <c r="I9" t="n">
-        <v>-175962.8477063757</v>
+        <v>-175962.8477060414</v>
       </c>
       <c r="J9" t="n">
-        <v>3.758983147796373</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1926264440291746</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05052610874615139</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6101246851589696</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06503362791350591</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="P9" t="n">
-        <v>8.659455021349791</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.7997730185700033</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.01400265842950587</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0909672374775249</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5215719617308274</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2249576665799374</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1926264440291746</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.758983147796373</v>
+        <v>-3.758983147792192</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.06503362791350591</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6101246851589696</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.05052610874615139</v>
+        <v>-0.05052610874595759</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.01400265842950587</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.7997730185700033</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="AD9" t="n">
-        <v>-8.659455021349791</v>
+        <v>-8.659455021339078</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.2249576665799374</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.5215719617308274</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.0909672374775249</v>
+        <v>-0.09096723747714046</v>
       </c>
       <c r="AH9" t="n">
-        <v>834.0638981282214</v>
+        <v>834.0638981266368</v>
       </c>
       <c r="AI9" t="n">
-        <v>45.0577455145506</v>
+        <v>45.05774551440441</v>
       </c>
       <c r="AJ9" t="n">
-        <v>446.3275434447266</v>
+        <v>446.3275434442011</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.4551684177429204</v>
+        <v>0.4551684177415671</v>
       </c>
       <c r="AL9" t="n">
-        <v>-1123.453614997354</v>
+        <v>-1123.453614995791</v>
       </c>
       <c r="AM9" t="n">
-        <v>165.0996718048683</v>
+        <v>165.0996718042885</v>
       </c>
       <c r="AN9" t="n">
-        <v>-834.0638981282214</v>
+        <v>-834.0638981266368</v>
       </c>
       <c r="AO9" t="n">
-        <v>-45.0577455145506</v>
+        <v>-45.05774551440441</v>
       </c>
       <c r="AP9" t="n">
-        <v>-296.3275434447266</v>
+        <v>-296.3275434442011</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.4551684177429204</v>
+        <v>-0.4551684177415671</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1104.511645671005</v>
+        <v>-1104.511645669415</v>
       </c>
       <c r="AS9" t="n">
-        <v>105.2468012824354</v>
+        <v>105.246801282138</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002374012492260691</v>
+        <v>0.002374012492255152</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003956687487101151</v>
+        <v>0.0003956687487091919</v>
       </c>
       <c r="H10" t="n">
-        <v>375.0939737771891</v>
+        <v>375.0939737763139</v>
       </c>
       <c r="I10" t="n">
-        <v>79133.74974202301</v>
+        <v>79133.74974183837</v>
       </c>
       <c r="J10" t="n">
-        <v>8.658378534746893</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5437220967409437</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01407909170155771</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04556477868193153</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="N10" t="n">
-        <v>0.522665028634919</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1550967117146793</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="P10" t="n">
-        <v>12.10067564647184</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8556013782045796</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0164531041938184</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02662802448665153</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3041205539618769</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2765021643933779</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01407909170155771</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5437220967409437</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.658378534746893</v>
+        <v>-8.658378534736178</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.1550967117146793</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.522665028634919</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04556477868193153</v>
+        <v>0.04556477868176344</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0164531041938184</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.8556013782045796</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="AD10" t="n">
-        <v>-12.10067564647184</v>
+        <v>-12.10067564645607</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.2765021643933779</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3041205539618769</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.02662802448665153</v>
+        <v>0.02662802448650984</v>
       </c>
       <c r="AH10" t="n">
-        <v>-375.0939737771891</v>
+        <v>-375.0939737763142</v>
       </c>
       <c r="AI10" t="n">
-        <v>-23.50754841627872</v>
+        <v>-23.50754841617129</v>
       </c>
       <c r="AJ10" t="n">
-        <v>237.2786231038581</v>
+        <v>237.2786231035455</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.3455385960855267</v>
+        <v>0.3455385960838586</v>
       </c>
       <c r="AL10" t="n">
-        <v>-550.1129580535226</v>
+        <v>-550.1129580527219</v>
       </c>
       <c r="AM10" t="n">
-        <v>-56.50944714432887</v>
+        <v>-56.50944714402618</v>
       </c>
       <c r="AN10" t="n">
-        <v>375.0939737771891</v>
+        <v>375.0939737763142</v>
       </c>
       <c r="AO10" t="n">
-        <v>23.50754841627872</v>
+        <v>23.50754841617129</v>
       </c>
       <c r="AP10" t="n">
-        <v>-237.2786231038581</v>
+        <v>-237.2786231035455</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.3455385960855267</v>
+        <v>-0.3455385960838586</v>
       </c>
       <c r="AR10" t="n">
-        <v>-873.558780569625</v>
+        <v>-873.5587805685493</v>
       </c>
       <c r="AS10" t="n">
-        <v>-84.5358433533433</v>
+        <v>-84.53584335300144</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002145286274066197</v>
+        <v>0.002145286274060163</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003575477123443661</v>
+        <v>0.0003575477123433605</v>
       </c>
       <c r="H11" t="n">
-        <v>338.955231302459</v>
+        <v>338.9552313015058</v>
       </c>
       <c r="I11" t="n">
-        <v>71509.5424688732</v>
+        <v>71509.54246867209</v>
       </c>
       <c r="J11" t="n">
-        <v>10.03693211710211</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5436509443454407</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009226541546905213</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.04561220557396294</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8629762354429026</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1753504665297493</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="P11" t="n">
-        <v>14.61043109297521</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8554961959393073</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01137182782097141</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02661478979068704</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3475225990419422</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.306472075519195</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="V11" t="n">
-        <v>0.009226541546905213</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5436509443454407</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.03693211710211</v>
+        <v>-10.03693211708712</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.1753504665297493</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.8629762354429026</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.04561220557396294</v>
+        <v>0.04561220557379464</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01137182782097141</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8554961959393073</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="AD11" t="n">
-        <v>-14.61043109297521</v>
+        <v>-14.61043109294954</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.306472075519195</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.3475225990419422</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02661478979068704</v>
+        <v>0.02661478979054551</v>
       </c>
       <c r="AH11" t="n">
-        <v>-338.9552313024592</v>
+        <v>-338.9552313015058</v>
       </c>
       <c r="AI11" t="n">
-        <v>-23.4738521566461</v>
+        <v>-23.4738521565387</v>
       </c>
       <c r="AJ11" t="n">
-        <v>232.3606098632458</v>
+        <v>232.360609862576</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.3731922717391915</v>
+        <v>0.3731922717374728</v>
       </c>
       <c r="AL11" t="n">
-        <v>-315.6461386530264</v>
+        <v>-315.6461386515213</v>
       </c>
       <c r="AM11" t="n">
-        <v>-56.36346879031407</v>
+        <v>-56.36346879001178</v>
       </c>
       <c r="AN11" t="n">
-        <v>338.9552313024592</v>
+        <v>338.9552313015058</v>
       </c>
       <c r="AO11" t="n">
-        <v>23.4738521566461</v>
+        <v>23.4738521565387</v>
       </c>
       <c r="AP11" t="n">
-        <v>-232.3606098632458</v>
+        <v>-232.360609862576</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.3731922717391915</v>
+        <v>-0.3731922717374728</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1078.51752052645</v>
+        <v>-1078.517520523936</v>
       </c>
       <c r="AS11" t="n">
-        <v>-84.47964414956243</v>
+        <v>-84.47964414922058</v>
       </c>
     </row>
     <row r="12">
@@ -5381,25 +5381,25 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.002092006254188197</v>
+        <v>-0.002092006254182372</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0003486677090313662</v>
+        <v>-0.0003486677090303953</v>
       </c>
       <c r="H12" t="n">
-        <v>-330.5369881617351</v>
+        <v>-330.5369881608148</v>
       </c>
       <c r="I12" t="n">
-        <v>-69733.54180627322</v>
+        <v>-69733.54180607905</v>
       </c>
       <c r="J12" t="n">
-        <v>10.03855675064235</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7997579802044718</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.00930297481895709</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -5411,31 +5411,31 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14.61196774740029</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.29941701569186</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.01139498107314529</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="S12" t="n">
-        <v>0.03319060518225687</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="T12" t="n">
-        <v>0.31823938176172</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2465744571357565</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.00930297481895709</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7997579802044718</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.03855675064235</v>
+        <v>-10.03855675062735</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -5447,58 +5447,58 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.01139498107314529</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.29941701569186</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="AD12" t="n">
-        <v>-14.61196774740029</v>
+        <v>-14.61196774737462</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.2465744571357565</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.31823938176172</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.03319060518225687</v>
+        <v>-0.03319060518208777</v>
       </c>
       <c r="AH12" t="n">
-        <v>330.5369881617353</v>
+        <v>330.5369881608146</v>
       </c>
       <c r="AI12" t="n">
-        <v>98.68818091868567</v>
+        <v>98.68818091821899</v>
       </c>
       <c r="AJ12" t="n">
-        <v>967.6109033632856</v>
+        <v>967.6109033612859</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.7017888395402301</v>
+        <v>0.7017888395369127</v>
       </c>
       <c r="AL12" t="n">
-        <v>-2988.32985259353</v>
+        <v>-2988.329852586897</v>
       </c>
       <c r="AM12" t="n">
-        <v>320.6255905909271</v>
+        <v>320.6255905894019</v>
       </c>
       <c r="AN12" t="n">
-        <v>-330.5369881617353</v>
+        <v>-330.5369881608146</v>
       </c>
       <c r="AO12" t="n">
-        <v>-98.68818091868567</v>
+        <v>-98.68818091821899</v>
       </c>
       <c r="AP12" t="n">
-        <v>-817.6109033632856</v>
+        <v>-817.6109033612859</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.7017888395402301</v>
+        <v>-0.7017888395369127</v>
       </c>
       <c r="AR12" t="n">
-        <v>-2367.335567586184</v>
+        <v>-2367.335567580818</v>
       </c>
       <c r="AS12" t="n">
-        <v>271.5034949211869</v>
+        <v>271.503494919912</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002427292512138695</v>
+        <v>-0.002427292512132957</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0004045487520231159</v>
+        <v>-0.0004045487520221595</v>
       </c>
       <c r="H13" t="n">
-        <v>-383.5122169179139</v>
+        <v>-383.5122169170072</v>
       </c>
       <c r="I13" t="n">
-        <v>-80909.75040462318</v>
+        <v>-80909.75040443189</v>
       </c>
       <c r="J13" t="n">
-        <v>8.659455021349791</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7997730185700033</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.01400265842950587</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0909672374775249</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5215719617308274</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2249576665799374</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="P13" t="n">
-        <v>12.10178926076199</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.29947267129122</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.01642995094164457</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03715388464313682</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3085318025524598</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3365693165715262</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.01400265842950587</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.7997730185700033</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.659455021349791</v>
+        <v>-8.659455021339078</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.2249576665799374</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.5215719617308274</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.0909672374775249</v>
+        <v>-0.09096723747714046</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.01642995094164457</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.29947267129122</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="AD13" t="n">
-        <v>-12.10178926076199</v>
+        <v>-12.10178926074621</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.3365693165715262</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.3085318025524598</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.03715388464313682</v>
+        <v>-0.03715388464293796</v>
       </c>
       <c r="AH13" t="n">
-        <v>383.512216917914</v>
+        <v>383.5122169170072</v>
       </c>
       <c r="AI13" t="n">
-        <v>28.44961730194387</v>
+        <v>28.44961730178392</v>
       </c>
       <c r="AJ13" t="n">
-        <v>309.8323268187096</v>
+        <v>309.8323268183962</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.3176639268991371</v>
+        <v>0.3176639268975212</v>
       </c>
       <c r="AL13" t="n">
-        <v>-621.847262664136</v>
+        <v>-621.8472626633337</v>
       </c>
       <c r="AM13" t="n">
-        <v>45.52697080838436</v>
+        <v>45.52697080804194</v>
       </c>
       <c r="AN13" t="n">
-        <v>-383.512216917914</v>
+        <v>-383.5122169170072</v>
       </c>
       <c r="AO13" t="n">
-        <v>-28.44961730194387</v>
+        <v>-28.44961730178392</v>
       </c>
       <c r="AP13" t="n">
-        <v>-159.8323268187096</v>
+        <v>-159.8323268183962</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.3176639268991371</v>
+        <v>-0.3176639268975212</v>
       </c>
       <c r="AR13" t="n">
-        <v>-787.1466982481188</v>
+        <v>-787.1466982470427</v>
       </c>
       <c r="AS13" t="n">
-        <v>125.1707330032788</v>
+        <v>125.1707330026616</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0006447200771059376</v>
+        <v>0.0006447200771039496</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001074533461843229</v>
+        <v>0.0001074533461839916</v>
       </c>
       <c r="H14" t="n">
-        <v>101.8657721827381</v>
+        <v>101.865772182424</v>
       </c>
       <c r="I14" t="n">
-        <v>21490.66923686459</v>
+        <v>21490.66923679832</v>
       </c>
       <c r="J14" t="n">
-        <v>12.10067564647184</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8556013782045796</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0164531041938184</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.02662802448665153</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3041205539618769</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2765021643933779</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="P14" t="n">
-        <v>13.74971682086599</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9831632435523956</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01709782427092434</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.009077683545891</v>
+        <v>-0.009077683545820888</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1282531740802902</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.29611319624158</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0164531041938184</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8556013782045796</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.10067564647184</v>
+        <v>-12.10067564645607</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.2765021643933779</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.3041205539618769</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.02662802448665153</v>
+        <v>0.02662802448650984</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.01709782427092434</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.9831632435523956</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="AD14" t="n">
-        <v>-13.74971682086599</v>
+        <v>-13.74971682084649</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.29611319624158</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1282531740802902</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.009077683545891</v>
+        <v>0.009077683545820888</v>
       </c>
       <c r="AH14" t="n">
-        <v>-101.8657721827385</v>
+        <v>-101.8657721824238</v>
       </c>
       <c r="AI14" t="n">
-        <v>-5.043036175046467</v>
+        <v>-5.043036174986128</v>
       </c>
       <c r="AJ14" t="n">
-        <v>86.80693093268656</v>
+        <v>86.80693093240026</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.05581601372180611</v>
+        <v>0.05581601372114864</v>
       </c>
       <c r="AL14" t="n">
-        <v>-130.2789316856852</v>
+        <v>-130.2789316849898</v>
       </c>
       <c r="AM14" t="n">
-        <v>-2.141856228976621</v>
+        <v>-2.14185622884861</v>
       </c>
       <c r="AN14" t="n">
-        <v>101.8657721827385</v>
+        <v>101.8657721824238</v>
       </c>
       <c r="AO14" t="n">
-        <v>5.043036175046467</v>
+        <v>5.043036174986128</v>
       </c>
       <c r="AP14" t="n">
-        <v>-86.80693093268656</v>
+        <v>-86.80693093240026</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.05581601372180611</v>
+        <v>-0.05581601372114864</v>
       </c>
       <c r="AR14" t="n">
-        <v>-390.5626539104323</v>
+        <v>-390.5626539094091</v>
       </c>
       <c r="AS14" t="n">
-        <v>-28.11636082130212</v>
+        <v>-28.11636082106827</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0005432565124295595</v>
+        <v>0.0005432565124276027</v>
       </c>
       <c r="G15" t="n">
-        <v>9.054275207159325e-05</v>
+        <v>9.054275207126712e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>85.8345289638704</v>
+        <v>85.83452896356123</v>
       </c>
       <c r="I15" t="n">
-        <v>18108.55041431865</v>
+        <v>18108.55041425342</v>
       </c>
       <c r="J15" t="n">
-        <v>14.61043109297521</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8554961959393073</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01137182782097141</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.02661478979068704</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3475225990419422</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.306472075519195</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="P15" t="n">
-        <v>16.28729671565749</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9830577539242298</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01191508433340097</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.009081688200316467</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1184927986808056</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3261226386376945</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01137182782097141</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8554961959393073</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="X15" t="n">
-        <v>-14.61043109297521</v>
+        <v>-14.61043109294954</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.306472075519195</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.3475225990419422</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.02661478979068704</v>
+        <v>0.02661478979054551</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.01191508433340097</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9830577539242298</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="AD15" t="n">
-        <v>-16.28729671565749</v>
+        <v>-16.28729671562621</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.3261226386376945</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1184927986808056</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.009081688200316467</v>
+        <v>0.00908168820024597</v>
       </c>
       <c r="AH15" t="n">
-        <v>-85.8345289638703</v>
+        <v>-85.8345289635613</v>
       </c>
       <c r="AI15" t="n">
-        <v>-5.049790589604982</v>
+        <v>-5.049790589544841</v>
       </c>
       <c r="AJ15" t="n">
-        <v>68.77545928012933</v>
+        <v>68.77545927978912</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.05592852579880625</v>
+        <v>0.05592852579814611</v>
       </c>
       <c r="AL15" t="n">
-        <v>-36.84432557314722</v>
+        <v>-36.84432557254138</v>
       </c>
       <c r="AM15" t="n">
-        <v>-2.174876591940688</v>
+        <v>-2.174876591812904</v>
       </c>
       <c r="AN15" t="n">
-        <v>85.8345289638703</v>
+        <v>85.8345289635613</v>
       </c>
       <c r="AO15" t="n">
-        <v>5.049790589604982</v>
+        <v>5.049790589544841</v>
       </c>
       <c r="AP15" t="n">
-        <v>-68.77545928012933</v>
+        <v>-68.77545927978912</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.05592852579880625</v>
+        <v>-0.05592852579814611</v>
       </c>
       <c r="AR15" t="n">
-        <v>-375.8084301076287</v>
+        <v>-375.8084301061951</v>
       </c>
       <c r="AS15" t="n">
-        <v>-28.12386694568909</v>
+        <v>-28.12386694545614</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0005350612470926223</v>
+        <v>-0.0005350612470906464</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.917687451543705e-05</v>
+        <v>-8.917687451510774e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>-84.53967704063432</v>
+        <v>-84.53967704032213</v>
       </c>
       <c r="I16" t="n">
-        <v>-17835.37490308741</v>
+        <v>-17835.37490302155</v>
       </c>
       <c r="J16" t="n">
-        <v>14.61196774740029</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.29941701569186</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.01139498107314529</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03319060518225687</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="N16" t="n">
-        <v>0.31823938176172</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2465744571357565</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="P16" t="n">
-        <v>16.28791981017913</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.457257327510761</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.01193004232023791</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0113463028819652</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1105412483363123</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2660564792332996</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.01139498107314529</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.29941701569186</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="X16" t="n">
-        <v>-14.61196774740029</v>
+        <v>-14.61196774737462</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.2465744571357565</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.31823938176172</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.03319060518225687</v>
+        <v>-0.03319060518208777</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.01193004232023791</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="AC16" t="n">
-        <v>-1.457257327510761</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="AD16" t="n">
-        <v>-16.28791981017913</v>
+        <v>-16.28791981014785</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.2660564792332996</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1105412483363123</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.0113463028819652</v>
+        <v>-0.01134630288189326</v>
       </c>
       <c r="AH16" t="n">
-        <v>84.53967704063439</v>
+        <v>84.5396770403222</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.976631614471387</v>
+        <v>5.976631614420171</v>
       </c>
       <c r="AJ16" t="n">
-        <v>171.1038425462361</v>
+        <v>171.1038425458343</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.05544883212377627</v>
+        <v>0.05544883212311946</v>
       </c>
       <c r="AL16" t="n">
-        <v>-209.6149089039063</v>
+        <v>-209.6149089029861</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.765111141198304</v>
+        <v>1.765111141116449</v>
       </c>
       <c r="AN16" t="n">
-        <v>-84.53967704063439</v>
+        <v>-84.5396770403222</v>
       </c>
       <c r="AO16" t="n">
-        <v>-5.976631614471387</v>
+        <v>-5.976631614420171</v>
       </c>
       <c r="AP16" t="n">
-        <v>-21.10384254623614</v>
+        <v>-21.10384254583424</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.05544883212377627</v>
+        <v>-0.05544883212311946</v>
       </c>
       <c r="AR16" t="n">
-        <v>-367.0081463735096</v>
+        <v>-367.0081463720166</v>
       </c>
       <c r="AS16" t="n">
-        <v>34.0946785456299</v>
+        <v>34.09467854540435</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.00065291534244288</v>
+        <v>-0.0006529153424409059</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.00010881922374048</v>
+        <v>-0.000108819223740151</v>
       </c>
       <c r="H17" t="n">
-        <v>-103.160624105975</v>
+        <v>-103.1606241056631</v>
       </c>
       <c r="I17" t="n">
-        <v>-21763.844748096</v>
+        <v>-21763.84474803019</v>
       </c>
       <c r="J17" t="n">
-        <v>12.10178926076199</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.29947267129122</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01642995094164457</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="M17" t="n">
-        <v>0.03715388464313682</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3085318025524598</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3365693165715262</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="P17" t="n">
-        <v>13.75040665790733</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.457370638582175</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.01708286628408745</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="S17" t="n">
-        <v>0.009916345241963179</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1081508876110224</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3561669580462182</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.01642995094164457</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.29947267129122</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="X17" t="n">
-        <v>-12.10178926076199</v>
+        <v>-12.10178926074621</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0.3365693165715262</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.3085318025524598</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.03715388464313682</v>
+        <v>-0.03715388464293796</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.01708286628408745</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.457370638582175</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="AD17" t="n">
-        <v>-13.75040665790733</v>
+        <v>-13.75040665788783</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.3561669580462182</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1081508876110224</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.009916345241963179</v>
+        <v>-0.009916345241901936</v>
       </c>
       <c r="AH17" t="n">
-        <v>103.1606241059749</v>
+        <v>103.1606241056634</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.116195150128135</v>
+        <v>4.116195150090789</v>
       </c>
       <c r="AJ17" t="n">
-        <v>173.3137672415419</v>
+        <v>173.3137672412556</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.05577790265873905</v>
+        <v>0.05577790265808225</v>
       </c>
       <c r="AL17" t="n">
-        <v>-221.6594246679597</v>
+        <v>-221.6594246672689</v>
       </c>
       <c r="AM17" t="n">
-        <v>-7.807193706483986</v>
+        <v>-7.807193706494331</v>
       </c>
       <c r="AN17" t="n">
-        <v>-103.1606241059749</v>
+        <v>-103.1606241056634</v>
       </c>
       <c r="AO17" t="n">
-        <v>-4.116195150128135</v>
+        <v>-4.116195150090789</v>
       </c>
       <c r="AP17" t="n">
-        <v>-23.31376724154188</v>
+        <v>-23.3137672412556</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0.05577790265873905</v>
+        <v>-0.05577790265808225</v>
       </c>
       <c r="AR17" t="n">
-        <v>-368.2231787812889</v>
+        <v>-368.2231787802656</v>
       </c>
       <c r="AS17" t="n">
-        <v>32.50436460725291</v>
+        <v>32.50436460703907</v>
       </c>
     </row>
     <row r="18">
@@ -6227,112 +6227,112 @@
         <v>-2639.351957915703</v>
       </c>
       <c r="J18" t="n">
-        <v>3.757925951556457</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1624422723423497</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="L18" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.03630395006721086</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="N18" t="n">
-        <v>0.609806490401359</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.005111413036285996</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="P18" t="n">
-        <v>3.723395957228697</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.162336698264033</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.03628902410970122</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6753566419540323</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.03509421220940796</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1624422723423497</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="W18" t="n">
-        <v>-3.757925951556457</v>
+        <v>-3.757925951552276</v>
       </c>
       <c r="X18" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.609806490401359</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.03630395006721086</v>
+        <v>0.03630395006709138</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.005111413036285996</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.162336698264033</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.723395957228697</v>
+        <v>-3.723395957223965</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.6753566419540323</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.03628902410970122</v>
+        <v>0.03628902410958178</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.03509421220940796</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="AH18" t="n">
         <v>12.51052828051979</v>
       </c>
       <c r="AI18" t="n">
-        <v>-20.32886904325267</v>
+        <v>-20.32886904320844</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-29.95136551383587</v>
+        <v>-29.95136551373676</v>
       </c>
       <c r="AK18" t="n">
-        <v>-0.1399243619682065</v>
+        <v>-0.1399243619677715</v>
       </c>
       <c r="AL18" t="n">
-        <v>119.8137459617613</v>
+        <v>119.8137459613649</v>
       </c>
       <c r="AM18" t="n">
-        <v>-64.67502263192773</v>
+        <v>-64.67502263175106</v>
       </c>
       <c r="AN18" t="n">
         <v>-12.51052828051979</v>
       </c>
       <c r="AO18" t="n">
-        <v>20.32886904325267</v>
+        <v>20.32886904320844</v>
       </c>
       <c r="AP18" t="n">
-        <v>29.95136551383587</v>
+        <v>29.95136551373676</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.1399243619682065</v>
+        <v>0.1399243619677715</v>
       </c>
       <c r="AR18" t="n">
-        <v>119.7971781489256</v>
+        <v>119.7971781485292</v>
       </c>
       <c r="AS18" t="n">
-        <v>-97.95592971409337</v>
+        <v>-97.95592971391648</v>
       </c>
     </row>
     <row r="19">
@@ -6354,124 +6354,124 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0001740734582384995</v>
+        <v>-0.0001740734582367232</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.175918227981244e-05</v>
+        <v>-2.175918227959039e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-20.62770480126219</v>
+        <v>-20.62770480105169</v>
       </c>
       <c r="I19" t="n">
-        <v>-4351.836455962487</v>
+        <v>-4351.836455918078</v>
       </c>
       <c r="J19" t="n">
-        <v>3.723395957228697</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="K19" t="n">
-        <v>0.162336698264033</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="L19" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.03628902410970122</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6753566419540323</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.03509421220940796</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="P19" t="n">
-        <v>3.723221883770459</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1923970678424733</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="S19" t="n">
-        <v>0.04214837918590374</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5925544959344536</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0251422011950651</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="V19" t="n">
-        <v>3.723395957228697</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="W19" t="n">
-        <v>0.162336698264033</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="X19" t="n">
-        <v>0.006184562735773826</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.03628902410970122</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.6753566419540323</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.03509421220940796</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.723221883770459</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.1923970678424733</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.04214837918590374</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5925544959344536</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.0251422011950651</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="AH19" t="n">
-        <v>20.62770480127074</v>
+        <v>20.62770480103791</v>
       </c>
       <c r="AI19" t="n">
-        <v>32.77195795073811</v>
+        <v>32.77195795069392</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-526.4796256073413</v>
+        <v>-526.4796256065976</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.1674336878040798</v>
+        <v>-0.1674336878034616</v>
       </c>
       <c r="AL19" t="n">
-        <v>2151.873693470231</v>
+        <v>2151.8736934672</v>
       </c>
       <c r="AM19" t="n">
-        <v>97.65662236346988</v>
+        <v>97.65662236329339</v>
       </c>
       <c r="AN19" t="n">
-        <v>-20.62770480127074</v>
+        <v>-20.62770480103791</v>
       </c>
       <c r="AO19" t="n">
-        <v>-32.77195795073811</v>
+        <v>-32.77195795069392</v>
       </c>
       <c r="AP19" t="n">
-        <v>526.4796256073413</v>
+        <v>526.4796256065976</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.1674336878040798</v>
+        <v>0.1674336878034616</v>
       </c>
       <c r="AR19" t="n">
-        <v>2059.963311388499</v>
+        <v>2059.96331138558</v>
       </c>
       <c r="AS19" t="n">
-        <v>164.519041242435</v>
+        <v>164.5190412422579</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0002293761867013244</v>
+        <v>0.0002293761867009914</v>
       </c>
       <c r="G20" t="n">
-        <v>2.867202333766555e-05</v>
+        <v>2.867202333762392e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>27.18107812410694</v>
+        <v>27.18107812406748</v>
       </c>
       <c r="I20" t="n">
-        <v>5734.40466753311</v>
+        <v>5734.404667524784</v>
       </c>
       <c r="J20" t="n">
-        <v>3.723221883770459</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1923970678424733</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="M20" t="n">
-        <v>0.04214837918590374</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5925544959344536</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0251422011950651</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="P20" t="n">
-        <v>3.758983147796373</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1926264440291746</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="S20" t="n">
-        <v>0.05052610874615139</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6101246851589696</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06503362791350591</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1923970678424733</v>
+        <v>0.1923970678416461</v>
       </c>
       <c r="W20" t="n">
-        <v>3.723221883770459</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.006196319318194401</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.5925544959344536</v>
+        <v>-0.5925544959336078</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.04214837918590374</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.0251422011950651</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1926264440291746</v>
+        <v>0.1926264440283471</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.758983147796373</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.6101246851589696</v>
+        <v>-0.6101246851582274</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.05052610874615139</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.06503362791350591</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="AH20" t="n">
-        <v>-27.18107812410744</v>
+        <v>-27.18107812406743</v>
       </c>
       <c r="AI20" t="n">
-        <v>-120.3262129092477</v>
+        <v>-120.3262129092034</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-38.31274245313044</v>
+        <v>-38.31274245297931</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.0375055962292552</v>
+        <v>0.03750559622947636</v>
       </c>
       <c r="AL20" t="n">
-        <v>148.6013299065843</v>
+        <v>148.6013299059929</v>
       </c>
       <c r="AM20" t="n">
-        <v>-164.5905998150671</v>
+        <v>-164.5905998148902</v>
       </c>
       <c r="AN20" t="n">
-        <v>27.18107812410744</v>
+        <v>27.18107812406743</v>
       </c>
       <c r="AO20" t="n">
-        <v>-79.67378709075228</v>
+        <v>-79.67378709079662</v>
       </c>
       <c r="AP20" t="n">
-        <v>38.31274245313044</v>
+        <v>38.31274245297931</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.0375055962292552</v>
+        <v>-0.03750559622947636</v>
       </c>
       <c r="AR20" t="n">
-        <v>157.9006097184592</v>
+        <v>157.9006097178416</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.980896541085798</v>
+        <v>1.980896541263149</v>
       </c>
     </row>
     <row r="21">
@@ -6644,112 +6644,112 @@
         <v>26429.90599789341</v>
       </c>
       <c r="J21" t="n">
-        <v>3.758983147796373</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1926264440291746</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.008723772998314602</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="M21" t="n">
-        <v>0.05052610874615139</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6101246851589696</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.06503362791350591</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="P21" t="n">
-        <v>3.757925951556457</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1624422723423497</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="R21" t="n">
-        <v>0.008735529580735151</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.03630395006721086</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="T21" t="n">
-        <v>0.609806490401359</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.005111413036285996</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.758983147796373</v>
+        <v>-3.758983147792192</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1926264440291746</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="X21" t="n">
-        <v>0.008723772998314602</v>
+        <v>0.008723772998299724</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.05052610874615139</v>
+        <v>-0.05052610874595759</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.6101246851589696</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.06503362791350591</v>
+        <v>0.06503362791338377</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.757925951556457</v>
+        <v>-3.757925951552276</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.1624422723423497</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.008735529580735151</v>
+        <v>-0.008735529580720434</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.03630395006721086</v>
+        <v>0.03630395006709138</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.609806490401359</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.005111413036285996</v>
+        <v>0.005111413036164057</v>
       </c>
       <c r="AH21" t="n">
         <v>-125.2777544300188</v>
       </c>
       <c r="AI21" t="n">
-        <v>-7.751465002060866</v>
+        <v>-7.751465002016882</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-505.9794931523545</v>
+        <v>-505.9794931517395</v>
       </c>
       <c r="AK21" t="n">
-        <v>-0.1853487793900617</v>
+        <v>-0.185348779389393</v>
       </c>
       <c r="AL21" t="n">
-        <v>2024.094570699891</v>
+        <v>2024.094570697432</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.250969248613565</v>
+        <v>2.250969248789389</v>
       </c>
       <c r="AN21" t="n">
         <v>125.2777544300188</v>
       </c>
       <c r="AO21" t="n">
-        <v>7.751465002060866</v>
+        <v>7.751465002016882</v>
       </c>
       <c r="AP21" t="n">
-        <v>505.9794931523545</v>
+        <v>505.9794931517395</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.1853487793900617</v>
+        <v>0.185348779389393</v>
       </c>
       <c r="AR21" t="n">
-        <v>2023.741374518944</v>
+        <v>2023.741374516484</v>
       </c>
       <c r="AS21" t="n">
-        <v>-64.26268926510053</v>
+        <v>-64.26268926492449</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.115239550303798e-05</v>
+        <v>-7.115239550292696e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.894049437879747e-06</v>
+        <v>-8.89404943786587e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.431558867110001</v>
+        <v>-8.431558867096845</v>
       </c>
       <c r="I22" t="n">
-        <v>-1778.809887575949</v>
+        <v>-1778.809887573174</v>
       </c>
       <c r="J22" t="n">
-        <v>8.658378534746893</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5437220967409437</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01407909170155771</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.04556477868193153</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="N22" t="n">
-        <v>0.522665028634919</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1550967117146793</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="P22" t="n">
-        <v>10.03693211710211</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.5436509443454407</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="R22" t="n">
-        <v>0.009226541546905213</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.04561220557396294</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8629762354429026</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1753504665297493</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5437220967409437</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="W22" t="n">
-        <v>-8.658378534746893</v>
+        <v>-8.658378534736178</v>
       </c>
       <c r="X22" t="n">
-        <v>0.01407909170155771</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.522665028634919</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.04556477868193153</v>
+        <v>0.04556477868176344</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.1550967117146793</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.5436509443454407</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="AC22" t="n">
-        <v>-10.03693211710211</v>
+        <v>-10.03693211708712</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.009226541546905213</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.8629762354429026</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.04561220557396294</v>
+        <v>0.04561220557379464</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.1753504665297493</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="AH22" t="n">
-        <v>8.431558867116109</v>
+        <v>8.431558867094282</v>
       </c>
       <c r="AI22" t="n">
-        <v>5.907094219596843</v>
+        <v>5.907094219625492</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-37.44745119604755</v>
+        <v>-37.44745119590817</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.7264335376093496</v>
+        <v>-0.7264335376073403</v>
       </c>
       <c r="AL22" t="n">
-        <v>149.7634828591127</v>
+        <v>149.7634828585553</v>
       </c>
       <c r="AM22" t="n">
-        <v>34.86921080075126</v>
+        <v>34.86921080087586</v>
       </c>
       <c r="AN22" t="n">
-        <v>-8.431558867116109</v>
+        <v>-8.431558867094282</v>
       </c>
       <c r="AO22" t="n">
-        <v>-5.907094219596843</v>
+        <v>-5.907094219625492</v>
       </c>
       <c r="AP22" t="n">
-        <v>37.44745119604755</v>
+        <v>37.44745119590817</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.7264335376093496</v>
+        <v>0.7264335376073403</v>
       </c>
       <c r="AR22" t="n">
-        <v>149.8161267092676</v>
+        <v>149.81612670871</v>
       </c>
       <c r="AS22" t="n">
-        <v>12.38754295602348</v>
+        <v>12.38754295612807</v>
       </c>
     </row>
     <row r="23">
@@ -6910,43 +6910,43 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001624633540233233</v>
+        <v>0.00162463354023501</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0002030791925291542</v>
+        <v>0.0002030791925293762</v>
       </c>
       <c r="H23" t="n">
-        <v>192.5190745176382</v>
+        <v>192.5190745178487</v>
       </c>
       <c r="I23" t="n">
-        <v>40615.83850583083</v>
+        <v>40615.83850587524</v>
       </c>
       <c r="J23" t="n">
-        <v>10.03693211710211</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5436509443454407</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="L23" t="n">
-        <v>0.009226541546905213</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.04561220557396294</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8629762354429026</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1753504665297493</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="P23" t="n">
-        <v>10.03855675064235</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.7997579802044718</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.00930297481895709</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -6958,31 +6958,31 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>10.03693211710211</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5436509443454407</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="X23" t="n">
-        <v>0.009226541546905213</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.04561220557396294</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.8629762354429026</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.1753504665297493</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.03855675064235</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.7997579802044718</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.00930297481895709</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -6994,40 +6994,40 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>-192.519074517535</v>
+        <v>-192.5190745177679</v>
       </c>
       <c r="AI23" t="n">
-        <v>66.80885951796712</v>
+        <v>66.80885951768202</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-357.2856302062857</v>
+        <v>-357.2856302055961</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.09736451574442088</v>
+        <v>-0.09736451574406163</v>
       </c>
       <c r="AL23" t="n">
-        <v>1908.094331495953</v>
+        <v>1908.094331492271</v>
       </c>
       <c r="AM23" t="n">
-        <v>169.9159291478577</v>
+        <v>169.9159291470286</v>
       </c>
       <c r="AN23" t="n">
-        <v>192.519074517535</v>
+        <v>192.5190745177679</v>
       </c>
       <c r="AO23" t="n">
-        <v>-66.80885951796712</v>
+        <v>-66.80885951768202</v>
       </c>
       <c r="AP23" t="n">
-        <v>357.2856302062857</v>
+        <v>357.2856302055961</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.09736451574442088</v>
+        <v>0.09736451574406163</v>
       </c>
       <c r="AR23" t="n">
-        <v>950.1907101543316</v>
+        <v>950.1907101524979</v>
       </c>
       <c r="AS23" t="n">
-        <v>364.5549469958794</v>
+        <v>364.5549469944276</v>
       </c>
     </row>
     <row r="24">
@@ -7049,25 +7049,25 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>1.503836553151672e-05</v>
+        <v>1.503836553162774e-05</v>
       </c>
       <c r="G24" t="n">
-        <v>1.87979569143959e-06</v>
+        <v>1.879795691453467e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>1.782046315484731</v>
+        <v>1.782046315497887</v>
       </c>
       <c r="I24" t="n">
-        <v>375.9591382879179</v>
+        <v>375.9591382906935</v>
       </c>
       <c r="J24" t="n">
-        <v>10.03855675064235</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7997579802044718</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.00930297481895709</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -7079,31 +7079,31 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>8.659455021349791</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.7997730185700033</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.01400265842950587</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0909672374775249</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5215719617308274</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2249576665799374</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7997579802044718</v>
+        <v>0.7997579802013167</v>
       </c>
       <c r="W24" t="n">
-        <v>10.03855675064235</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.00930297481895709</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -7115,58 +7115,58 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.7997730185700033</v>
+        <v>0.7997730185668483</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.659455021349791</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.01400265842950587</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.5215719617308274</v>
+        <v>-0.5215719617301026</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0909672374775249</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.2249576665799374</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="AH24" t="n">
         <v>-1.782046315493062</v>
       </c>
       <c r="AI24" t="n">
-        <v>-50.12585500939213</v>
+        <v>-50.12585500958915</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-37.37605177429701</v>
+        <v>-37.37605177413763</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.113355533694651</v>
+        <v>1.113355533693104</v>
       </c>
       <c r="AL24" t="n">
-        <v>99.01739029716171</v>
+        <v>99.01739029673753</v>
       </c>
       <c r="AM24" t="n">
-        <v>191.0147515809632</v>
+        <v>191.0147515798436</v>
       </c>
       <c r="AN24" t="n">
         <v>1.782046315493062</v>
       </c>
       <c r="AO24" t="n">
-        <v>-149.8741449906079</v>
+        <v>-149.8741449904109</v>
       </c>
       <c r="AP24" t="n">
-        <v>37.37605177429701</v>
+        <v>37.37605177413763</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-1.113355533694651</v>
+        <v>-1.113355533693104</v>
       </c>
       <c r="AR24" t="n">
-        <v>199.9910238972143</v>
+        <v>199.9910238963635</v>
       </c>
       <c r="AS24" t="n">
-        <v>207.9784083438993</v>
+        <v>207.9784083434427</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00107648660289783</v>
+        <v>0.001076486602899607</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001345608253622288</v>
+        <v>0.0001345608253624508</v>
       </c>
       <c r="H25" t="n">
-        <v>127.5636624433929</v>
+        <v>127.5636624436034</v>
       </c>
       <c r="I25" t="n">
-        <v>26912.16507244576</v>
+        <v>26912.16507249017</v>
       </c>
       <c r="J25" t="n">
-        <v>8.659455021349791</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7997730185700033</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.01400265842950587</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0909672374775249</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5215719617308274</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2249576665799374</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="P25" t="n">
-        <v>8.658378534746893</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5437220967409437</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="R25" t="n">
-        <v>0.01407909170155771</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.04556477868193153</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="T25" t="n">
-        <v>0.522665028634919</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1550967117146793</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="V25" t="n">
-        <v>-8.659455021349791</v>
+        <v>-8.659455021339078</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.7997730185700033</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="X25" t="n">
-        <v>0.01400265842950587</v>
+        <v>0.01400265842948097</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.0909672374775249</v>
+        <v>-0.09096723747714046</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.5215719617308274</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.2249576665799374</v>
+        <v>0.2249576665793398</v>
       </c>
       <c r="AB25" t="n">
-        <v>-8.658378534746893</v>
+        <v>-8.658378534736178</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.5437220967409437</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.01407909170155771</v>
+        <v>-0.01407909170153279</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.04556477868193153</v>
+        <v>0.04556477868176344</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.522665028634919</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.1550967117146793</v>
+        <v>0.1550967117141002</v>
       </c>
       <c r="AH25" t="n">
-        <v>-127.5636624434264</v>
+        <v>-127.5636624436593</v>
       </c>
       <c r="AI25" t="n">
-        <v>18.39017452808879</v>
+        <v>18.3901745281176</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-431.7413901167282</v>
+        <v>-431.74139011613</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.291443342186532</v>
+        <v>-0.2914433421853525</v>
       </c>
       <c r="AL25" t="n">
-        <v>1726.358908335142</v>
+        <v>1726.358908332749</v>
       </c>
       <c r="AM25" t="n">
-        <v>112.3335280625733</v>
+        <v>112.3335280626782</v>
       </c>
       <c r="AN25" t="n">
-        <v>127.5636624434264</v>
+        <v>127.5636624436593</v>
       </c>
       <c r="AO25" t="n">
-        <v>-18.39017452808879</v>
+        <v>-18.3901745281176</v>
       </c>
       <c r="AP25" t="n">
-        <v>431.7413901167282</v>
+        <v>431.74139011613</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.291443342186532</v>
+        <v>0.2914433421853525</v>
       </c>
       <c r="AR25" t="n">
-        <v>1727.572212598684</v>
+        <v>1727.57221259629</v>
       </c>
       <c r="AS25" t="n">
-        <v>34.78786816213679</v>
+        <v>34.78786816226227</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0001051822652723411</v>
+        <v>-0.0001051822652722301</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.314778315904264e-05</v>
+        <v>-1.314778315902876e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.46409843477242</v>
+        <v>-12.46409843475926</v>
       </c>
       <c r="I26" t="n">
-        <v>-2629.556631808527</v>
+        <v>-2629.556631805752</v>
       </c>
       <c r="J26" t="n">
-        <v>12.10067564647184</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8556013782045796</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0164531041938184</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.02662802448665153</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3041205539618769</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2765021643933779</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="P26" t="n">
-        <v>14.61043109297521</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8554961959393073</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="R26" t="n">
-        <v>0.01137182782097141</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.02661478979068704</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3475225990419422</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.306472075519195</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="V26" t="n">
-        <v>0.8556013782045796</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="W26" t="n">
-        <v>-12.10067564647184</v>
+        <v>-12.10067564645607</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0164531041938184</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.3041205539618769</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.02662802448665153</v>
+        <v>0.02662802448650984</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.2765021643933779</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.8554961959393073</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="AC26" t="n">
-        <v>-14.61043109297521</v>
+        <v>-14.61043109294954</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.01137182782097141</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.3475225990419422</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.02661478979068704</v>
+        <v>0.02661478979054551</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.306472075519195</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="AH26" t="n">
-        <v>12.46409843477886</v>
+        <v>12.46409843476431</v>
       </c>
       <c r="AI26" t="n">
-        <v>18.50839878814895</v>
+        <v>18.50839878808893</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-21.6335511203928</v>
+        <v>-21.63355112027549</v>
       </c>
       <c r="AK26" t="n">
-        <v>-0.09264667315167774</v>
+        <v>-0.0926466731507235</v>
       </c>
       <c r="AL26" t="n">
-        <v>86.54154973783145</v>
+        <v>86.54154973736216</v>
       </c>
       <c r="AM26" t="n">
-        <v>90.66689582742492</v>
+        <v>90.66689582718391</v>
       </c>
       <c r="AN26" t="n">
-        <v>-12.46409843477886</v>
+        <v>-12.46409843476431</v>
       </c>
       <c r="AO26" t="n">
-        <v>-18.50839878814895</v>
+        <v>-18.50839878808893</v>
       </c>
       <c r="AP26" t="n">
-        <v>21.6335511203928</v>
+        <v>21.63355112027549</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.09264667315167774</v>
+        <v>0.0926466731507235</v>
       </c>
       <c r="AR26" t="n">
-        <v>86.52685922531087</v>
+        <v>86.52685922484176</v>
       </c>
       <c r="AS26" t="n">
-        <v>57.4002944777676</v>
+        <v>57.40029447752659</v>
       </c>
     </row>
     <row r="27">
@@ -7466,124 +7466,124 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>0.001536654425073891</v>
+        <v>0.001536654425072115</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0001920818031342364</v>
+        <v>0.0001920818031340144</v>
       </c>
       <c r="H27" t="n">
-        <v>182.0935493712561</v>
+        <v>182.0935493710456</v>
       </c>
       <c r="I27" t="n">
-        <v>38416.36062684728</v>
+        <v>38416.36062680287</v>
       </c>
       <c r="J27" t="n">
-        <v>14.61043109297521</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8554961959393073</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01137182782097141</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.02661478979068704</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3475225990419422</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.306472075519195</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="P27" t="n">
-        <v>14.61196774740029</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.29941701569186</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.01139498107314529</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="S27" t="n">
-        <v>0.03319060518225687</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="T27" t="n">
-        <v>0.31823938176172</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2465744571357565</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="V27" t="n">
-        <v>14.61043109297521</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="W27" t="n">
-        <v>0.8554961959393073</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="X27" t="n">
-        <v>0.01137182782097141</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.02661478979068704</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.3475225990419422</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.306472075519195</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.61196774740029</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="AC27" t="n">
-        <v>-1.29941701569186</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.01139498107314529</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.03319060518225687</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.31823938176172</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.2465744571357565</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="AH27" t="n">
-        <v>-182.0935493712313</v>
+        <v>-182.0935493709985</v>
       </c>
       <c r="AI27" t="n">
-        <v>-5.959963132255233</v>
+        <v>-5.959963132195512</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-274.7542534589803</v>
+        <v>-274.7542534582191</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.1276615161922457</v>
+        <v>-0.1276615161915826</v>
       </c>
       <c r="AL27" t="n">
-        <v>1115.269199426445</v>
+        <v>1115.269199423327</v>
       </c>
       <c r="AM27" t="n">
-        <v>-57.08303073182913</v>
+        <v>-57.08303073159067</v>
       </c>
       <c r="AN27" t="n">
-        <v>182.0935493712313</v>
+        <v>182.0935493709985</v>
       </c>
       <c r="AO27" t="n">
-        <v>5.959963132255233</v>
+        <v>5.959963132195512</v>
       </c>
       <c r="AP27" t="n">
-        <v>274.7542534589803</v>
+        <v>274.7542534582191</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.1276615161922457</v>
+        <v>0.1276615161915826</v>
       </c>
       <c r="AR27" t="n">
-        <v>1082.764828245398</v>
+        <v>1082.764828242425</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.403325673787522</v>
+        <v>9.403325674026803</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>5.565559936049347e-05</v>
+        <v>5.565559936138165e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>6.956949920061684e-06</v>
+        <v>6.956949920172706e-06</v>
       </c>
       <c r="H28" t="n">
-        <v>6.595188524218476</v>
+        <v>6.595188524323725</v>
       </c>
       <c r="I28" t="n">
-        <v>1391.389984012337</v>
+        <v>1391.389984034541</v>
       </c>
       <c r="J28" t="n">
-        <v>14.61196774740029</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.29941701569186</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.01139498107314529</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="M28" t="n">
-        <v>0.03319060518225687</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="N28" t="n">
-        <v>0.31823938176172</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.2465744571357565</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="P28" t="n">
-        <v>12.10178926076199</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.29947267129122</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.01642995094164457</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="S28" t="n">
-        <v>0.03715388464313682</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3085318025524598</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3365693165715262</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29941701569186</v>
+        <v>1.299417015686306</v>
       </c>
       <c r="W28" t="n">
-        <v>14.61196774740029</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.01139498107314529</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.31823938176172</v>
+        <v>-0.3182393817608644</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.03319060518225687</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.2465744571357565</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.29947267129122</v>
+        <v>1.299472671285667</v>
       </c>
       <c r="AC28" t="n">
-        <v>12.10178926076199</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.01642995094164457</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.3085318025524598</v>
+        <v>-0.3085318025519207</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.03715388464313682</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.3365693165715262</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="AH28" t="n">
-        <v>-6.595188524224795</v>
+        <v>-6.595188524341211</v>
       </c>
       <c r="AI28" t="n">
-        <v>-81.51814703985838</v>
+        <v>-81.51814703991795</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-28.75694233787942</v>
+        <v>-28.75694233772689</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.02072194792745929</v>
+        <v>-0.0207219479267835</v>
       </c>
       <c r="AL28" t="n">
-        <v>112.8281492507293</v>
+        <v>112.8281492501357</v>
       </c>
       <c r="AM28" t="n">
-        <v>-9.458774505914647</v>
+        <v>-9.458774506152935</v>
       </c>
       <c r="AN28" t="n">
-        <v>6.595188524224795</v>
+        <v>6.595188524341211</v>
       </c>
       <c r="AO28" t="n">
-        <v>-118.4818529601416</v>
+        <v>-118.4818529600821</v>
       </c>
       <c r="AP28" t="n">
-        <v>28.75694233787942</v>
+        <v>28.75694233772689</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.02072194792745929</v>
+        <v>0.0207219479267835</v>
       </c>
       <c r="AR28" t="n">
-        <v>117.227389452306</v>
+        <v>117.2273894516794</v>
       </c>
       <c r="AS28" t="n">
-        <v>157.3135981870485</v>
+        <v>157.3135981868093</v>
       </c>
     </row>
     <row r="29">
@@ -7756,112 +7756,112 @@
         <v>27840.35725365008</v>
       </c>
       <c r="J29" t="n">
-        <v>12.10178926076199</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.29947267129122</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01642995094164457</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="M29" t="n">
-        <v>0.03715388464313682</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3085318025524598</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.3365693165715262</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="P29" t="n">
-        <v>12.10067564647184</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8556013782045796</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0164531041938184</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.02662802448665153</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3041205539618769</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.2765021643933779</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="V29" t="n">
-        <v>-12.10178926076199</v>
+        <v>-12.10178926074621</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.29947267129122</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01642995094164457</v>
+        <v>0.01642995094161392</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.03715388464313682</v>
+        <v>-0.03715388464293796</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.3085318025524598</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.3365693165715262</v>
+        <v>0.3365693165703608</v>
       </c>
       <c r="AB29" t="n">
-        <v>-12.10067564647184</v>
+        <v>-12.10067564645607</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.8556013782045796</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.0164531041938184</v>
+        <v>-0.01645310419378794</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.02662802448665153</v>
+        <v>0.02662802448650984</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.3041205539618769</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2765021643933779</v>
+        <v>0.2765021643922128</v>
       </c>
       <c r="AH29" t="n">
-        <v>-131.9632933824323</v>
+        <v>-131.9632933821995</v>
       </c>
       <c r="AI29" t="n">
-        <v>30.92861067598463</v>
+        <v>30.92861067592477</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-251.5946504740586</v>
+        <v>-251.5946504736163</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.1361498444885867</v>
+        <v>-0.1361498444878597</v>
       </c>
       <c r="AL29" t="n">
-        <v>1008.826844864008</v>
+        <v>1008.826844862238</v>
       </c>
       <c r="AM29" t="n">
-        <v>157.0517121628106</v>
+        <v>157.0517121625711</v>
       </c>
       <c r="AN29" t="n">
-        <v>131.9632933824323</v>
+        <v>131.9632933821995</v>
       </c>
       <c r="AO29" t="n">
-        <v>-30.92861067598463</v>
+        <v>-30.92861067592477</v>
       </c>
       <c r="AP29" t="n">
-        <v>251.5946504740586</v>
+        <v>251.5946504736163</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.1361498444885867</v>
+        <v>0.1361498444878597</v>
       </c>
       <c r="AR29" t="n">
-        <v>1003.930358928461</v>
+        <v>1003.930358926692</v>
       </c>
       <c r="AS29" t="n">
-        <v>90.37717324506605</v>
+        <v>90.37717324482674</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001054896281658113</v>
+        <v>-0.0001054896281654782</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.318620352072641e-05</v>
+        <v>-1.318620352068478e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>-12.50052093764864</v>
+        <v>-12.50052093760917</v>
       </c>
       <c r="I30" t="n">
-        <v>-2637.240704145283</v>
+        <v>-2637.240704136956</v>
       </c>
       <c r="J30" t="n">
-        <v>13.74971682086599</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9831632435523956</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01709782427092434</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.009077683545891</v>
+        <v>-0.009077683545820888</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1282531740802902</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.29611319624158</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="P30" t="n">
-        <v>16.28729671565749</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9830577539242298</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01191508433340097</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.009081688200316467</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1184927986808056</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.3261226386376945</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="V30" t="n">
-        <v>0.9831632435523956</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="W30" t="n">
-        <v>-13.74971682086599</v>
+        <v>-13.74971682084649</v>
       </c>
       <c r="X30" t="n">
-        <v>0.01709782427092434</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1282531740802902</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.009077683545891</v>
+        <v>0.009077683545820888</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.29611319624158</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.9830577539242298</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="AC30" t="n">
-        <v>-16.28729671565749</v>
+        <v>-16.28729671562621</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.01191508433340097</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.1184927986808056</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.009081688200316467</v>
+        <v>0.00908168820024597</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.3261226386376945</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="AH30" t="n">
-        <v>12.50052093763952</v>
+        <v>12.50052093761042</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.061241533242764</v>
+        <v>5.061241533179555</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-7.019509614610334</v>
+        <v>-7.019509614552399</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.02083464748736136</v>
+        <v>0.02083464748759228</v>
       </c>
       <c r="AL30" t="n">
-        <v>28.0758158752352</v>
+        <v>28.07581587500367</v>
       </c>
       <c r="AM30" t="n">
-        <v>36.90020666281453</v>
+        <v>36.90020666256169</v>
       </c>
       <c r="AN30" t="n">
-        <v>-12.50052093763952</v>
+        <v>-12.50052093761042</v>
       </c>
       <c r="AO30" t="n">
-        <v>-5.061241533242764</v>
+        <v>-5.061241533179555</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.019509614610334</v>
+        <v>7.019509614552399</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.02083464748736136</v>
+        <v>-0.02083464748759228</v>
       </c>
       <c r="AR30" t="n">
-        <v>28.08026104164746</v>
+        <v>28.08026104141551</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.5897256031285</v>
+        <v>3.589725602874751</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0006230945216323391</v>
+        <v>0.0006230945216358919</v>
       </c>
       <c r="G31" t="n">
-        <v>7.788681520404239e-05</v>
+        <v>7.788681520448648e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>73.83670081343219</v>
+        <v>73.83670081385318</v>
       </c>
       <c r="I31" t="n">
-        <v>15577.36304080848</v>
+        <v>15577.36304089729</v>
       </c>
       <c r="J31" t="n">
-        <v>16.28729671565749</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9830577539242298</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01191508433340097</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.009081688200316467</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1184927986808056</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.3261226386376945</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="P31" t="n">
-        <v>16.28791981017913</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1.457257327510761</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.01193004232023791</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0113463028819652</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1105412483363123</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2660564792332996</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="V31" t="n">
-        <v>16.28729671565749</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="W31" t="n">
-        <v>0.9830577539242298</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="X31" t="n">
-        <v>0.01191508433340097</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.009081688200316467</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.1184927986808056</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.3261226386376945</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="AB31" t="n">
-        <v>16.28791981017913</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="AC31" t="n">
-        <v>-1.457257327510761</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.01193004232023791</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.0113463028819652</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.1105412483363123</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.2660564792332996</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="AH31" t="n">
-        <v>-73.83670081337914</v>
+        <v>-73.8367008138448</v>
       </c>
       <c r="AI31" t="n">
-        <v>7.450730348027498</v>
+        <v>7.450730348091383</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-92.85403857848101</v>
+        <v>-92.85403857811413</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.04360590404102432</v>
+        <v>-0.04360590404072028</v>
       </c>
       <c r="AL31" t="n">
-        <v>375.8292647551177</v>
+        <v>375.8292647536747</v>
       </c>
       <c r="AM31" t="n">
-        <v>-3.533797077329041</v>
+        <v>-3.533797077073132</v>
       </c>
       <c r="AN31" t="n">
-        <v>73.83670081337914</v>
+        <v>73.8367008138448</v>
       </c>
       <c r="AO31" t="n">
-        <v>-7.450730348027498</v>
+        <v>-7.450730348091383</v>
       </c>
       <c r="AP31" t="n">
-        <v>92.85403857848101</v>
+        <v>92.85403857811413</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.04360590404102432</v>
+        <v>0.04360590404072028</v>
       </c>
       <c r="AR31" t="n">
-        <v>367.0030438727302</v>
+        <v>367.0030438712382</v>
       </c>
       <c r="AS31" t="n">
-        <v>63.13963986154931</v>
+        <v>63.13963986180471</v>
       </c>
     </row>
     <row r="32">
@@ -8173,112 +8173,112 @@
         <v>2832.776785338664</v>
       </c>
       <c r="J32" t="n">
-        <v>16.28791981017913</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.457257327510761</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.01193004232023791</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0113463028819652</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1105412483363123</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.2660564792332996</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="P32" t="n">
-        <v>13.75040665790733</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.457370638582175</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.01708286628408745</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="S32" t="n">
-        <v>0.009916345241963179</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1081508876110224</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.3561669580462182</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="V32" t="n">
-        <v>1.457257327510761</v>
+        <v>1.457257327504276</v>
       </c>
       <c r="W32" t="n">
-        <v>16.28791981017913</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.01193004232023791</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.1105412483363123</v>
+        <v>-0.1105412483358429</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.0113463028819652</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.2660564792332996</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.457370638582175</v>
+        <v>1.45737063857569</v>
       </c>
       <c r="AC32" t="n">
-        <v>13.75040665790733</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.01708286628408745</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.1081508876110224</v>
+        <v>-0.1081508876107066</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.009916345241963179</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.3561669580462182</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="AH32" t="n">
         <v>-13.42736196250189</v>
       </c>
       <c r="AI32" t="n">
-        <v>-94.9405433593156</v>
+        <v>-94.94054335937926</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-8.314361537847095</v>
+        <v>-8.314361537792287</v>
       </c>
       <c r="AK32" t="n">
-        <v>-0.005102500778984165</v>
+        <v>-0.005102500778656233</v>
       </c>
       <c r="AL32" t="n">
-        <v>34.0510726415895</v>
+        <v>34.05107264136433</v>
       </c>
       <c r="AM32" t="n">
-        <v>-63.08419102942511</v>
+        <v>-63.08419102967977</v>
       </c>
       <c r="AN32" t="n">
         <v>13.42736196250189</v>
       </c>
       <c r="AO32" t="n">
-        <v>-105.0594566406844</v>
+        <v>-105.0594566406207</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.314361537847095</v>
+        <v>8.314361537792287</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.005102500778984165</v>
+        <v>0.005102500778656233</v>
       </c>
       <c r="AR32" t="n">
-        <v>32.46381966118725</v>
+        <v>32.46381966097396</v>
       </c>
       <c r="AS32" t="n">
-        <v>103.5598441549012</v>
+        <v>103.5598441546466</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0006898370413406241</v>
+        <v>0.0006898370413459531</v>
       </c>
       <c r="G33" t="n">
-        <v>8.622963016757801e-05</v>
+        <v>8.622963016824414e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>81.74568939886396</v>
+        <v>81.74568939949545</v>
       </c>
       <c r="I33" t="n">
-        <v>17245.9260335156</v>
+        <v>17245.92603364883</v>
       </c>
       <c r="J33" t="n">
-        <v>13.75040665790733</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.457370638582175</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.01708286628408745</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="M33" t="n">
-        <v>0.009916345241963179</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1081508876110224</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.3561669580462182</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="P33" t="n">
-        <v>13.74971682086599</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9831632435523956</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01709782427092434</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.009077683545891</v>
+        <v>-0.009077683545820888</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1282531740802902</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.29611319624158</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="V33" t="n">
-        <v>-13.75040665790733</v>
+        <v>-13.75040665788783</v>
       </c>
       <c r="W33" t="n">
-        <v>-1.457370638582175</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="X33" t="n">
-        <v>0.01708286628408745</v>
+        <v>0.01708286628405483</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.009916345241963179</v>
+        <v>-0.009916345241901936</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1081508876110224</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.3561669580462182</v>
+        <v>0.3561669580448221</v>
       </c>
       <c r="AB33" t="n">
-        <v>-13.74971682086599</v>
+        <v>-13.74971682084649</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.9831632435523956</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.01709782427092434</v>
+        <v>-0.01709782427089189</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.009077683545891</v>
+        <v>0.009077683545820888</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.1282531740802902</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.29611319624158</v>
+        <v>0.2961131962401839</v>
       </c>
       <c r="AH33" t="n">
-        <v>-81.74568939884193</v>
+        <v>-81.74568939954042</v>
       </c>
       <c r="AI33" t="n">
-        <v>17.54355711266726</v>
+        <v>17.54355711260374</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-94.84626256812794</v>
+        <v>-94.84626256787126</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.04054494606638104</v>
+        <v>-0.04054494606610064</v>
       </c>
       <c r="AL33" t="n">
-        <v>368.2282812820681</v>
+        <v>368.2282812810421</v>
       </c>
       <c r="AM33" t="n">
-        <v>103.5040662522431</v>
+        <v>103.504066251989</v>
       </c>
       <c r="AN33" t="n">
-        <v>81.74568939884193</v>
+        <v>81.74568939954042</v>
       </c>
       <c r="AO33" t="n">
-        <v>-17.54355711266726</v>
+        <v>-17.54355711260374</v>
       </c>
       <c r="AP33" t="n">
-        <v>94.84626256812794</v>
+        <v>94.84626256787126</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.04054494606638104</v>
+        <v>0.04054494606610064</v>
       </c>
       <c r="AR33" t="n">
-        <v>390.5418192629554</v>
+        <v>390.5418192619279</v>
       </c>
       <c r="AS33" t="n">
-        <v>36.84439064909469</v>
+        <v>36.84439064884054</v>
       </c>
     </row>
   </sheetData>
